--- a/data/courses.xlsx
+++ b/data/courses.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\박준철\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\박준철\Desktop\임승원(20241101~)\gemini-chat-app\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E2DEFCB3-994E-4713-87CF-FDB12827F234}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B4FFC79-6B29-42B0-B898-F2E1024E4A28}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="11400" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -9010,9 +9010,6 @@
     <t>오픈소스이며 스마트폰을 위한 완벽한 컴포넌트를 제공해 주는 안드로이드를 이해하고, 앱개발을 위한 다양한 핵심기술(위젯, 스레드, 애니메이션, 데이터베이스, 멀티미디어, 근거리통신/센서 등)을 학습한다. 이를 바탕으로 새로운 앱을 설계하여 개발한다.</t>
   </si>
   <si>
-    <t>정보보안전공(평캠)</t>
-  </si>
-  <si>
     <t>파이썬을 활용하여 데이터 호출, 전처리, 시각화 및 분석하는 방법에 대해서 학습힌다. 또한 실제 활용되는 빅데이터를 통해 프로젝트를 진행하여 빅데이터로부터 새로운 가치를 창출하고 식별하는 방법에 대해 경험한다.</t>
   </si>
   <si>
@@ -9860,10 +9857,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>정보보안전공(평캠)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>유아특수보육학전공(평캠)</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -9925,6 +9918,14 @@
   </si>
   <si>
     <t>에너지변환은 전기, 기계, 화학, Bio 등 다양한 에너지를 수요자가 원하는 형태의 에너지로 상호 변환 하는 기술과 이들의 각각 에너지를 다양한 형태로 저장하는 기술로 구성된다. 본 교과목에서는 전자계 원리를 이용한 전자기 에너지변환기술을 주로 학습한다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>정보보안전공</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>정보보안전공</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -32108,7 +32109,7 @@
       </c>
       <c r="H807" s="12"/>
       <c r="I807" s="12" t="s">
-        <v>3225</v>
+        <v>3224</v>
       </c>
     </row>
     <row r="808" spans="1:9" x14ac:dyDescent="0.3">
@@ -34408,7 +34409,7 @@
     </row>
     <row r="893" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A893" s="8" t="s">
-        <v>2985</v>
+        <v>3272</v>
       </c>
       <c r="B893" s="5" t="s">
         <v>2774</v>
@@ -34435,7 +34436,7 @@
     </row>
     <row r="894" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A894" s="8" t="s">
-        <v>2985</v>
+        <v>3272</v>
       </c>
       <c r="B894" s="5" t="s">
         <v>2774</v>
@@ -34462,7 +34463,7 @@
     </row>
     <row r="895" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A895" s="8" t="s">
-        <v>2985</v>
+        <v>3272</v>
       </c>
       <c r="B895" s="5" t="s">
         <v>2774</v>
@@ -34489,7 +34490,7 @@
     </row>
     <row r="896" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A896" s="8" t="s">
-        <v>2985</v>
+        <v>3272</v>
       </c>
       <c r="B896" s="5" t="s">
         <v>2774</v>
@@ -34516,7 +34517,7 @@
     </row>
     <row r="897" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A897" s="8" t="s">
-        <v>2985</v>
+        <v>3272</v>
       </c>
       <c r="B897" s="5" t="s">
         <v>2774</v>
@@ -34543,7 +34544,7 @@
     </row>
     <row r="898" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A898" s="8" t="s">
-        <v>2985</v>
+        <v>3272</v>
       </c>
       <c r="B898" s="5" t="s">
         <v>2774</v>
@@ -34570,7 +34571,7 @@
     </row>
     <row r="899" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A899" s="8" t="s">
-        <v>2985</v>
+        <v>3272</v>
       </c>
       <c r="B899" s="5" t="s">
         <v>2774</v>
@@ -34597,7 +34598,7 @@
     </row>
     <row r="900" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A900" s="8" t="s">
-        <v>2985</v>
+        <v>3272</v>
       </c>
       <c r="B900" s="5" t="s">
         <v>2774</v>
@@ -34624,7 +34625,7 @@
     </row>
     <row r="901" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A901" s="8" t="s">
-        <v>2985</v>
+        <v>3272</v>
       </c>
       <c r="B901" s="5" t="s">
         <v>2774</v>
@@ -34651,7 +34652,7 @@
     </row>
     <row r="902" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A902" s="8" t="s">
-        <v>2985</v>
+        <v>3272</v>
       </c>
       <c r="B902" s="5" t="s">
         <v>2774</v>
@@ -34673,12 +34674,12 @@
       </c>
       <c r="H902" s="12"/>
       <c r="I902" s="12" t="s">
-        <v>2986</v>
+        <v>2985</v>
       </c>
     </row>
     <row r="903" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A903" s="8" t="s">
-        <v>2985</v>
+        <v>3272</v>
       </c>
       <c r="B903" s="5" t="s">
         <v>2774</v>
@@ -34705,7 +34706,7 @@
     </row>
     <row r="904" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A904" s="8" t="s">
-        <v>2985</v>
+        <v>3272</v>
       </c>
       <c r="B904" s="5" t="s">
         <v>2774</v>
@@ -34732,7 +34733,7 @@
     </row>
     <row r="905" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A905" s="8" t="s">
-        <v>2985</v>
+        <v>3272</v>
       </c>
       <c r="B905" s="5" t="s">
         <v>2774</v>
@@ -34759,7 +34760,7 @@
     </row>
     <row r="906" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A906" s="8" t="s">
-        <v>2985</v>
+        <v>3272</v>
       </c>
       <c r="B906" s="5" t="s">
         <v>2774</v>
@@ -34786,7 +34787,7 @@
     </row>
     <row r="907" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A907" s="8" t="s">
-        <v>2985</v>
+        <v>3272</v>
       </c>
       <c r="B907" s="5" t="s">
         <v>2774</v>
@@ -34813,7 +34814,7 @@
     </row>
     <row r="908" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A908" s="8" t="s">
-        <v>2985</v>
+        <v>3272</v>
       </c>
       <c r="B908" s="5" t="s">
         <v>2774</v>
@@ -34840,7 +34841,7 @@
     </row>
     <row r="909" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A909" s="8" t="s">
-        <v>2985</v>
+        <v>3272</v>
       </c>
       <c r="B909" s="5" t="s">
         <v>2774</v>
@@ -34867,7 +34868,7 @@
     </row>
     <row r="910" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A910" s="8" t="s">
-        <v>2985</v>
+        <v>3272</v>
       </c>
       <c r="B910" s="5" t="s">
         <v>2774</v>
@@ -34894,7 +34895,7 @@
     </row>
     <row r="911" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A911" s="8" t="s">
-        <v>2985</v>
+        <v>3272</v>
       </c>
       <c r="B911" s="5" t="s">
         <v>2774</v>
@@ -34921,7 +34922,7 @@
     </row>
     <row r="912" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A912" s="8" t="s">
-        <v>2985</v>
+        <v>3272</v>
       </c>
       <c r="B912" s="5" t="s">
         <v>2774</v>
@@ -34948,7 +34949,7 @@
     </row>
     <row r="913" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A913" s="8" t="s">
-        <v>2985</v>
+        <v>3272</v>
       </c>
       <c r="B913" s="5" t="s">
         <v>2774</v>
@@ -34975,7 +34976,7 @@
     </row>
     <row r="914" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A914" s="8" t="s">
-        <v>2985</v>
+        <v>3272</v>
       </c>
       <c r="B914" s="5" t="s">
         <v>2774</v>
@@ -35002,7 +35003,7 @@
     </row>
     <row r="915" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A915" s="8" t="s">
-        <v>2985</v>
+        <v>3272</v>
       </c>
       <c r="B915" s="5" t="s">
         <v>2774</v>
@@ -35029,7 +35030,7 @@
     </row>
     <row r="916" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A916" s="8" t="s">
-        <v>2985</v>
+        <v>3272</v>
       </c>
       <c r="B916" s="5" t="s">
         <v>2774</v>
@@ -35056,7 +35057,7 @@
     </row>
     <row r="917" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A917" s="8" t="s">
-        <v>2985</v>
+        <v>3272</v>
       </c>
       <c r="B917" s="5" t="s">
         <v>2774</v>
@@ -35083,7 +35084,7 @@
     </row>
     <row r="918" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A918" s="8" t="s">
-        <v>2985</v>
+        <v>3272</v>
       </c>
       <c r="B918" s="5" t="s">
         <v>2774</v>
@@ -35110,7 +35111,7 @@
     </row>
     <row r="919" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A919" s="8" t="s">
-        <v>2985</v>
+        <v>3272</v>
       </c>
       <c r="B919" s="5" t="s">
         <v>2774</v>
@@ -35132,12 +35133,12 @@
       </c>
       <c r="H919" s="12"/>
       <c r="I919" s="12" t="s">
-        <v>2987</v>
+        <v>2986</v>
       </c>
     </row>
     <row r="920" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A920" s="8" t="s">
-        <v>2985</v>
+        <v>3272</v>
       </c>
       <c r="B920" s="5" t="s">
         <v>2774</v>
@@ -35159,12 +35160,12 @@
       </c>
       <c r="H920" s="12"/>
       <c r="I920" s="12" t="s">
-        <v>2988</v>
+        <v>2987</v>
       </c>
     </row>
     <row r="921" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A921" s="8" t="s">
-        <v>2985</v>
+        <v>3272</v>
       </c>
       <c r="B921" s="5" t="s">
         <v>2774</v>
@@ -35191,7 +35192,7 @@
     </row>
     <row r="922" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A922" s="8" t="s">
-        <v>2985</v>
+        <v>3272</v>
       </c>
       <c r="B922" s="5" t="s">
         <v>2774</v>
@@ -35218,7 +35219,7 @@
     </row>
     <row r="923" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A923" s="8" t="s">
-        <v>2985</v>
+        <v>3272</v>
       </c>
       <c r="B923" s="5" t="s">
         <v>2774</v>
@@ -35245,7 +35246,7 @@
     </row>
     <row r="924" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A924" s="8" t="s">
-        <v>2985</v>
+        <v>3272</v>
       </c>
       <c r="B924" s="5" t="s">
         <v>2774</v>
@@ -35272,7 +35273,7 @@
     </row>
     <row r="925" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A925" s="8" t="s">
-        <v>2985</v>
+        <v>3272</v>
       </c>
       <c r="B925" s="5" t="s">
         <v>2774</v>
@@ -35294,12 +35295,12 @@
       </c>
       <c r="H925" s="12"/>
       <c r="I925" s="12" t="s">
-        <v>2988</v>
+        <v>2987</v>
       </c>
     </row>
     <row r="926" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A926" s="8" t="s">
-        <v>2985</v>
+        <v>3272</v>
       </c>
       <c r="B926" s="5" t="s">
         <v>2774</v>
@@ -36050,7 +36051,7 @@
       </c>
       <c r="H953" s="12"/>
       <c r="I953" s="12" t="s">
-        <v>2989</v>
+        <v>2988</v>
       </c>
     </row>
     <row r="954" spans="1:9" x14ac:dyDescent="0.3">
@@ -36124,7 +36125,7 @@
         <v>2775</v>
       </c>
       <c r="F956" s="3" t="s">
-        <v>2990</v>
+        <v>2989</v>
       </c>
       <c r="G956" s="3">
         <v>3</v>
@@ -37474,7 +37475,7 @@
         <v>2775</v>
       </c>
       <c r="F1006" s="3" t="s">
-        <v>2991</v>
+        <v>2990</v>
       </c>
       <c r="G1006" s="3">
         <v>3</v>
@@ -37589,7 +37590,7 @@
       </c>
       <c r="H1010" s="12"/>
       <c r="I1010" s="12" t="s">
-        <v>2992</v>
+        <v>2991</v>
       </c>
     </row>
     <row r="1011" spans="1:9" x14ac:dyDescent="0.3">
@@ -38505,7 +38506,7 @@
       </c>
       <c r="H1044" s="12"/>
       <c r="I1044" s="12" t="s">
-        <v>2993</v>
+        <v>2992</v>
       </c>
     </row>
     <row r="1045" spans="1:9" x14ac:dyDescent="0.3">
@@ -38613,7 +38614,7 @@
       </c>
       <c r="H1048" s="12"/>
       <c r="I1048" s="12" t="s">
-        <v>2993</v>
+        <v>2992</v>
       </c>
     </row>
     <row r="1049" spans="1:9" x14ac:dyDescent="0.3">
@@ -38795,7 +38796,7 @@
         <v>2779</v>
       </c>
       <c r="F1055" s="3" t="s">
-        <v>2994</v>
+        <v>2993</v>
       </c>
       <c r="G1055" s="3">
         <v>3</v>
@@ -38883,7 +38884,7 @@
       </c>
       <c r="H1058" s="12"/>
       <c r="I1058" s="12" t="s">
-        <v>2995</v>
+        <v>2994</v>
       </c>
     </row>
     <row r="1059" spans="1:9" x14ac:dyDescent="0.3">
@@ -38991,7 +38992,7 @@
       </c>
       <c r="H1062" s="12"/>
       <c r="I1062" s="12" t="s">
-        <v>2995</v>
+        <v>2994</v>
       </c>
     </row>
     <row r="1063" spans="1:9" x14ac:dyDescent="0.3">
@@ -39551,7 +39552,7 @@
         <v>2775</v>
       </c>
       <c r="F1083" s="3" t="s">
-        <v>2996</v>
+        <v>2995</v>
       </c>
       <c r="G1083" s="3">
         <v>3</v>
@@ -39605,14 +39606,14 @@
         <v>2775</v>
       </c>
       <c r="F1085" s="3" t="s">
-        <v>2997</v>
+        <v>2996</v>
       </c>
       <c r="G1085" s="3">
         <v>3</v>
       </c>
       <c r="H1085" s="12"/>
       <c r="I1085" s="12" t="s">
-        <v>2998</v>
+        <v>2997</v>
       </c>
     </row>
     <row r="1086" spans="1:9" x14ac:dyDescent="0.3">
@@ -41048,7 +41049,7 @@
     </row>
     <row r="1139" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1139" s="8" t="s">
-        <v>2999</v>
+        <v>2998</v>
       </c>
       <c r="B1139" s="5" t="s">
         <v>2774</v>
@@ -41075,7 +41076,7 @@
     </row>
     <row r="1140" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1140" s="8" t="s">
-        <v>2999</v>
+        <v>2998</v>
       </c>
       <c r="B1140" s="5" t="s">
         <v>2774</v>
@@ -41102,7 +41103,7 @@
     </row>
     <row r="1141" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1141" s="8" t="s">
-        <v>2999</v>
+        <v>2998</v>
       </c>
       <c r="B1141" s="5" t="s">
         <v>2774</v>
@@ -41129,7 +41130,7 @@
     </row>
     <row r="1142" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1142" s="8" t="s">
-        <v>2999</v>
+        <v>2998</v>
       </c>
       <c r="B1142" s="5" t="s">
         <v>2774</v>
@@ -41156,7 +41157,7 @@
     </row>
     <row r="1143" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1143" s="8" t="s">
-        <v>2999</v>
+        <v>2998</v>
       </c>
       <c r="B1143" s="5" t="s">
         <v>2774</v>
@@ -41183,7 +41184,7 @@
     </row>
     <row r="1144" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1144" s="8" t="s">
-        <v>2999</v>
+        <v>2998</v>
       </c>
       <c r="B1144" s="5" t="s">
         <v>2774</v>
@@ -41210,7 +41211,7 @@
     </row>
     <row r="1145" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1145" s="8" t="s">
-        <v>2999</v>
+        <v>2998</v>
       </c>
       <c r="B1145" s="5" t="s">
         <v>2774</v>
@@ -41237,7 +41238,7 @@
     </row>
     <row r="1146" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1146" s="8" t="s">
-        <v>2999</v>
+        <v>2998</v>
       </c>
       <c r="B1146" s="5" t="s">
         <v>2774</v>
@@ -41264,7 +41265,7 @@
     </row>
     <row r="1147" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1147" s="8" t="s">
-        <v>2999</v>
+        <v>2998</v>
       </c>
       <c r="B1147" s="5" t="s">
         <v>2774</v>
@@ -41291,7 +41292,7 @@
     </row>
     <row r="1148" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1148" s="8" t="s">
-        <v>2999</v>
+        <v>2998</v>
       </c>
       <c r="B1148" s="5" t="s">
         <v>2774</v>
@@ -41318,7 +41319,7 @@
     </row>
     <row r="1149" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1149" s="8" t="s">
-        <v>2999</v>
+        <v>2998</v>
       </c>
       <c r="B1149" s="5" t="s">
         <v>2774</v>
@@ -41345,7 +41346,7 @@
     </row>
     <row r="1150" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1150" s="8" t="s">
-        <v>2999</v>
+        <v>2998</v>
       </c>
       <c r="B1150" s="5" t="s">
         <v>2774</v>
@@ -41372,7 +41373,7 @@
     </row>
     <row r="1151" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1151" s="8" t="s">
-        <v>2999</v>
+        <v>2998</v>
       </c>
       <c r="B1151" s="5" t="s">
         <v>2774</v>
@@ -41399,7 +41400,7 @@
     </row>
     <row r="1152" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1152" s="8" t="s">
-        <v>2999</v>
+        <v>2998</v>
       </c>
       <c r="B1152" s="5" t="s">
         <v>2774</v>
@@ -41426,7 +41427,7 @@
     </row>
     <row r="1153" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1153" s="8" t="s">
-        <v>2999</v>
+        <v>2998</v>
       </c>
       <c r="B1153" s="5" t="s">
         <v>2774</v>
@@ -41453,7 +41454,7 @@
     </row>
     <row r="1154" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1154" s="8" t="s">
-        <v>2999</v>
+        <v>2998</v>
       </c>
       <c r="B1154" s="5" t="s">
         <v>2774</v>
@@ -41480,7 +41481,7 @@
     </row>
     <row r="1155" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1155" s="8" t="s">
-        <v>2999</v>
+        <v>2998</v>
       </c>
       <c r="B1155" s="5" t="s">
         <v>2774</v>
@@ -41507,7 +41508,7 @@
     </row>
     <row r="1156" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1156" s="8" t="s">
-        <v>2999</v>
+        <v>2998</v>
       </c>
       <c r="B1156" s="5" t="s">
         <v>2774</v>
@@ -41534,7 +41535,7 @@
     </row>
     <row r="1157" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1157" s="8" t="s">
-        <v>2999</v>
+        <v>2998</v>
       </c>
       <c r="B1157" s="5" t="s">
         <v>2774</v>
@@ -41561,7 +41562,7 @@
     </row>
     <row r="1158" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1158" s="8" t="s">
-        <v>2999</v>
+        <v>2998</v>
       </c>
       <c r="B1158" s="5" t="s">
         <v>2774</v>
@@ -41588,7 +41589,7 @@
     </row>
     <row r="1159" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1159" s="8" t="s">
-        <v>2999</v>
+        <v>2998</v>
       </c>
       <c r="B1159" s="5" t="s">
         <v>2774</v>
@@ -41615,7 +41616,7 @@
     </row>
     <row r="1160" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1160" s="8" t="s">
-        <v>2999</v>
+        <v>2998</v>
       </c>
       <c r="B1160" s="5" t="s">
         <v>2774</v>
@@ -41642,7 +41643,7 @@
     </row>
     <row r="1161" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1161" s="8" t="s">
-        <v>2999</v>
+        <v>2998</v>
       </c>
       <c r="B1161" s="5" t="s">
         <v>2774</v>
@@ -41669,7 +41670,7 @@
     </row>
     <row r="1162" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1162" s="8" t="s">
-        <v>2999</v>
+        <v>2998</v>
       </c>
       <c r="B1162" s="5" t="s">
         <v>2774</v>
@@ -41696,7 +41697,7 @@
     </row>
     <row r="1163" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1163" s="8" t="s">
-        <v>2999</v>
+        <v>2998</v>
       </c>
       <c r="B1163" s="5" t="s">
         <v>2774</v>
@@ -41723,7 +41724,7 @@
     </row>
     <row r="1164" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1164" s="8" t="s">
-        <v>2999</v>
+        <v>2998</v>
       </c>
       <c r="B1164" s="5" t="s">
         <v>2774</v>
@@ -41750,7 +41751,7 @@
     </row>
     <row r="1165" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1165" s="8" t="s">
-        <v>2999</v>
+        <v>2998</v>
       </c>
       <c r="B1165" s="5" t="s">
         <v>2774</v>
@@ -41777,7 +41778,7 @@
     </row>
     <row r="1166" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1166" s="8" t="s">
-        <v>2999</v>
+        <v>2998</v>
       </c>
       <c r="B1166" s="5" t="s">
         <v>2774</v>
@@ -41804,7 +41805,7 @@
     </row>
     <row r="1167" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1167" s="8" t="s">
-        <v>2999</v>
+        <v>2998</v>
       </c>
       <c r="B1167" s="5" t="s">
         <v>2774</v>
@@ -41831,7 +41832,7 @@
     </row>
     <row r="1168" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1168" s="8" t="s">
-        <v>2999</v>
+        <v>2998</v>
       </c>
       <c r="B1168" s="5" t="s">
         <v>2774</v>
@@ -41858,7 +41859,7 @@
     </row>
     <row r="1169" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1169" s="8" t="s">
-        <v>2999</v>
+        <v>2998</v>
       </c>
       <c r="B1169" s="5" t="s">
         <v>2774</v>
@@ -41885,7 +41886,7 @@
     </row>
     <row r="1170" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1170" s="8" t="s">
-        <v>2999</v>
+        <v>2998</v>
       </c>
       <c r="B1170" s="5" t="s">
         <v>2774</v>
@@ -41912,7 +41913,7 @@
     </row>
     <row r="1171" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1171" s="8" t="s">
-        <v>2999</v>
+        <v>2998</v>
       </c>
       <c r="B1171" s="5" t="s">
         <v>2774</v>
@@ -41939,7 +41940,7 @@
     </row>
     <row r="1172" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1172" s="8" t="s">
-        <v>2999</v>
+        <v>2998</v>
       </c>
       <c r="B1172" s="5" t="s">
         <v>2774</v>
@@ -41966,7 +41967,7 @@
     </row>
     <row r="1173" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1173" s="8" t="s">
-        <v>2999</v>
+        <v>2998</v>
       </c>
       <c r="B1173" s="5" t="s">
         <v>2774</v>
@@ -41993,7 +41994,7 @@
     </row>
     <row r="1174" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1174" s="8" t="s">
-        <v>2999</v>
+        <v>2998</v>
       </c>
       <c r="B1174" s="5" t="s">
         <v>2774</v>
@@ -42020,7 +42021,7 @@
     </row>
     <row r="1175" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1175" s="8" t="s">
-        <v>2999</v>
+        <v>2998</v>
       </c>
       <c r="B1175" s="5" t="s">
         <v>2774</v>
@@ -42047,7 +42048,7 @@
     </row>
     <row r="1176" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1176" s="8" t="s">
-        <v>2999</v>
+        <v>2998</v>
       </c>
       <c r="B1176" s="5" t="s">
         <v>2774</v>
@@ -42074,7 +42075,7 @@
     </row>
     <row r="1177" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1177" s="8" t="s">
-        <v>2999</v>
+        <v>2998</v>
       </c>
       <c r="B1177" s="5" t="s">
         <v>2774</v>
@@ -42101,7 +42102,7 @@
     </row>
     <row r="1178" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1178" s="8" t="s">
-        <v>2999</v>
+        <v>2998</v>
       </c>
       <c r="B1178" s="5" t="s">
         <v>2774</v>
@@ -42128,7 +42129,7 @@
     </row>
     <row r="1179" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1179" s="8" t="s">
-        <v>2999</v>
+        <v>2998</v>
       </c>
       <c r="B1179" s="5" t="s">
         <v>2774</v>
@@ -42143,7 +42144,7 @@
         <v>2779</v>
       </c>
       <c r="F1179" s="3" t="s">
-        <v>3000</v>
+        <v>2999</v>
       </c>
       <c r="G1179" s="3">
         <v>6</v>
@@ -42155,7 +42156,7 @@
     </row>
     <row r="1180" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1180" s="8" t="s">
-        <v>2999</v>
+        <v>2998</v>
       </c>
       <c r="B1180" s="5" t="s">
         <v>2774</v>
@@ -42182,7 +42183,7 @@
     </row>
     <row r="1181" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1181" s="8" t="s">
-        <v>2999</v>
+        <v>2998</v>
       </c>
       <c r="B1181" s="5" t="s">
         <v>2774</v>
@@ -42209,7 +42210,7 @@
     </row>
     <row r="1182" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1182" s="8" t="s">
-        <v>2999</v>
+        <v>2998</v>
       </c>
       <c r="B1182" s="5" t="s">
         <v>2774</v>
@@ -42236,7 +42237,7 @@
     </row>
     <row r="1183" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1183" s="8" t="s">
-        <v>2999</v>
+        <v>2998</v>
       </c>
       <c r="B1183" s="5" t="s">
         <v>2774</v>
@@ -42251,7 +42252,7 @@
         <v>2775</v>
       </c>
       <c r="F1183" s="3" t="s">
-        <v>3001</v>
+        <v>3000</v>
       </c>
       <c r="G1183" s="3">
         <v>6</v>
@@ -42467,7 +42468,7 @@
         <v>2775</v>
       </c>
       <c r="F1191" s="3" t="s">
-        <v>3002</v>
+        <v>3001</v>
       </c>
       <c r="G1191" s="3">
         <v>3</v>
@@ -42627,14 +42628,14 @@
         <v>2775</v>
       </c>
       <c r="F1197" s="3" t="s">
-        <v>3003</v>
+        <v>3002</v>
       </c>
       <c r="G1197" s="3">
         <v>3</v>
       </c>
       <c r="H1197" s="12"/>
       <c r="I1197" s="12" t="s">
-        <v>3004</v>
+        <v>3003</v>
       </c>
     </row>
     <row r="1198" spans="1:9" x14ac:dyDescent="0.3">
@@ -42735,7 +42736,7 @@
         <v>2775</v>
       </c>
       <c r="F1201" s="3" t="s">
-        <v>3005</v>
+        <v>3004</v>
       </c>
       <c r="G1201" s="3">
         <v>3</v>
@@ -42868,7 +42869,7 @@
         <v>2775</v>
       </c>
       <c r="F1206" s="3" t="s">
-        <v>3006</v>
+        <v>3005</v>
       </c>
       <c r="G1206" s="3">
         <v>3</v>
@@ -42956,7 +42957,7 @@
       </c>
       <c r="H1209" s="12"/>
       <c r="I1209" s="12" t="s">
-        <v>3007</v>
+        <v>3006</v>
       </c>
     </row>
     <row r="1210" spans="1:9" x14ac:dyDescent="0.3">
@@ -42976,7 +42977,7 @@
         <v>2775</v>
       </c>
       <c r="F1210" s="3" t="s">
-        <v>3008</v>
+        <v>3007</v>
       </c>
       <c r="G1210" s="3">
         <v>3</v>
@@ -43037,7 +43038,7 @@
       </c>
       <c r="H1212" s="12"/>
       <c r="I1212" s="12" t="s">
-        <v>3007</v>
+        <v>3006</v>
       </c>
     </row>
     <row r="1213" spans="1:9" x14ac:dyDescent="0.3">
@@ -43361,7 +43362,7 @@
       </c>
       <c r="H1224" s="12"/>
       <c r="I1224" s="12" t="s">
-        <v>3009</v>
+        <v>3008</v>
       </c>
     </row>
     <row r="1225" spans="1:9" x14ac:dyDescent="0.3">
@@ -43489,14 +43490,14 @@
         <v>2775</v>
       </c>
       <c r="F1229" s="3" t="s">
-        <v>3010</v>
+        <v>3009</v>
       </c>
       <c r="G1229" s="3">
         <v>3</v>
       </c>
       <c r="H1229" s="12"/>
       <c r="I1229" s="12" t="s">
-        <v>3011</v>
+        <v>3010</v>
       </c>
     </row>
     <row r="1230" spans="1:9" x14ac:dyDescent="0.3">
@@ -44947,7 +44948,7 @@
         <v>2775</v>
       </c>
       <c r="F1283" s="3" t="s">
-        <v>3012</v>
+        <v>3011</v>
       </c>
       <c r="G1283" s="3">
         <v>3</v>
@@ -45548,7 +45549,7 @@
       </c>
       <c r="H1305" s="12"/>
       <c r="I1305" s="12" t="s">
-        <v>3013</v>
+        <v>3012</v>
       </c>
     </row>
     <row r="1306" spans="1:9" x14ac:dyDescent="0.3">
@@ -45580,7 +45581,7 @@
     </row>
     <row r="1307" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1307" s="8" t="s">
-        <v>3014</v>
+        <v>3013</v>
       </c>
       <c r="B1307" s="5" t="s">
         <v>2774</v>
@@ -45607,34 +45608,34 @@
     </row>
     <row r="1308" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1308" s="8" t="s">
+        <v>3013</v>
+      </c>
+      <c r="B1308" s="5" t="s">
+        <v>2774</v>
+      </c>
+      <c r="C1308" s="6">
+        <v>1</v>
+      </c>
+      <c r="D1308" s="6">
+        <v>1</v>
+      </c>
+      <c r="E1308" s="7" t="s">
+        <v>2775</v>
+      </c>
+      <c r="F1308" s="3" t="s">
         <v>3014</v>
-      </c>
-      <c r="B1308" s="5" t="s">
-        <v>2774</v>
-      </c>
-      <c r="C1308" s="6">
-        <v>1</v>
-      </c>
-      <c r="D1308" s="6">
-        <v>1</v>
-      </c>
-      <c r="E1308" s="7" t="s">
-        <v>2775</v>
-      </c>
-      <c r="F1308" s="3" t="s">
-        <v>3015</v>
       </c>
       <c r="G1308" s="3">
         <v>2</v>
       </c>
       <c r="H1308" s="12"/>
       <c r="I1308" s="12" t="s">
-        <v>3016</v>
+        <v>3015</v>
       </c>
     </row>
     <row r="1309" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1309" s="8" t="s">
-        <v>3014</v>
+        <v>3013</v>
       </c>
       <c r="B1309" s="5" t="s">
         <v>2774</v>
@@ -45661,7 +45662,7 @@
     </row>
     <row r="1310" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1310" s="8" t="s">
-        <v>3014</v>
+        <v>3013</v>
       </c>
       <c r="B1310" s="5" t="s">
         <v>2774</v>
@@ -45688,7 +45689,7 @@
     </row>
     <row r="1311" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1311" s="8" t="s">
-        <v>3014</v>
+        <v>3013</v>
       </c>
       <c r="B1311" s="5" t="s">
         <v>2774</v>
@@ -45703,19 +45704,19 @@
         <v>2775</v>
       </c>
       <c r="F1311" s="3" t="s">
-        <v>3017</v>
+        <v>3016</v>
       </c>
       <c r="G1311" s="3">
         <v>2</v>
       </c>
       <c r="H1311" s="12"/>
       <c r="I1311" s="12" t="s">
-        <v>3016</v>
+        <v>3015</v>
       </c>
     </row>
     <row r="1312" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1312" s="8" t="s">
-        <v>3014</v>
+        <v>3013</v>
       </c>
       <c r="B1312" s="5" t="s">
         <v>2774</v>
@@ -45742,7 +45743,7 @@
     </row>
     <row r="1313" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1313" s="8" t="s">
-        <v>3014</v>
+        <v>3013</v>
       </c>
       <c r="B1313" s="5" t="s">
         <v>2774</v>
@@ -45769,7 +45770,7 @@
     </row>
     <row r="1314" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1314" s="8" t="s">
-        <v>3014</v>
+        <v>3013</v>
       </c>
       <c r="B1314" s="5" t="s">
         <v>2774</v>
@@ -45796,7 +45797,7 @@
     </row>
     <row r="1315" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1315" s="8" t="s">
-        <v>3014</v>
+        <v>3013</v>
       </c>
       <c r="B1315" s="5" t="s">
         <v>2774</v>
@@ -45823,7 +45824,7 @@
     </row>
     <row r="1316" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1316" s="8" t="s">
-        <v>3014</v>
+        <v>3013</v>
       </c>
       <c r="B1316" s="5" t="s">
         <v>2774</v>
@@ -45838,19 +45839,19 @@
         <v>2775</v>
       </c>
       <c r="F1316" s="3" t="s">
-        <v>3018</v>
+        <v>3017</v>
       </c>
       <c r="G1316" s="3">
         <v>3</v>
       </c>
       <c r="H1316" s="12"/>
       <c r="I1316" s="12" t="s">
-        <v>3019</v>
+        <v>3018</v>
       </c>
     </row>
     <row r="1317" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1317" s="8" t="s">
-        <v>3014</v>
+        <v>3013</v>
       </c>
       <c r="B1317" s="5" t="s">
         <v>2774</v>
@@ -45865,19 +45866,19 @@
         <v>2775</v>
       </c>
       <c r="F1317" s="3" t="s">
-        <v>3020</v>
+        <v>3019</v>
       </c>
       <c r="G1317" s="3">
         <v>3</v>
       </c>
       <c r="H1317" s="12"/>
       <c r="I1317" s="12" t="s">
-        <v>3021</v>
+        <v>3020</v>
       </c>
     </row>
     <row r="1318" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1318" s="8" t="s">
-        <v>3014</v>
+        <v>3013</v>
       </c>
       <c r="B1318" s="5" t="s">
         <v>2774</v>
@@ -45904,7 +45905,7 @@
     </row>
     <row r="1319" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1319" s="8" t="s">
-        <v>3014</v>
+        <v>3013</v>
       </c>
       <c r="B1319" s="5" t="s">
         <v>2774</v>
@@ -45931,7 +45932,7 @@
     </row>
     <row r="1320" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1320" s="8" t="s">
-        <v>3014</v>
+        <v>3013</v>
       </c>
       <c r="B1320" s="5" t="s">
         <v>2774</v>
@@ -45958,7 +45959,7 @@
     </row>
     <row r="1321" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1321" s="8" t="s">
-        <v>3014</v>
+        <v>3013</v>
       </c>
       <c r="B1321" s="5" t="s">
         <v>2774</v>
@@ -45985,7 +45986,7 @@
     </row>
     <row r="1322" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1322" s="8" t="s">
-        <v>3014</v>
+        <v>3013</v>
       </c>
       <c r="B1322" s="5" t="s">
         <v>2774</v>
@@ -46012,7 +46013,7 @@
     </row>
     <row r="1323" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1323" s="8" t="s">
-        <v>3014</v>
+        <v>3013</v>
       </c>
       <c r="B1323" s="5" t="s">
         <v>2774</v>
@@ -46039,7 +46040,7 @@
     </row>
     <row r="1324" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1324" s="8" t="s">
-        <v>3014</v>
+        <v>3013</v>
       </c>
       <c r="B1324" s="5" t="s">
         <v>2774</v>
@@ -46066,7 +46067,7 @@
     </row>
     <row r="1325" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1325" s="8" t="s">
-        <v>3014</v>
+        <v>3013</v>
       </c>
       <c r="B1325" s="5" t="s">
         <v>2774</v>
@@ -46093,7 +46094,7 @@
     </row>
     <row r="1326" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1326" s="8" t="s">
-        <v>3014</v>
+        <v>3013</v>
       </c>
       <c r="B1326" s="5" t="s">
         <v>2774</v>
@@ -46120,7 +46121,7 @@
     </row>
     <row r="1327" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1327" s="8" t="s">
-        <v>3014</v>
+        <v>3013</v>
       </c>
       <c r="B1327" s="5" t="s">
         <v>2774</v>
@@ -46147,7 +46148,7 @@
     </row>
     <row r="1328" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1328" s="8" t="s">
-        <v>3014</v>
+        <v>3013</v>
       </c>
       <c r="B1328" s="5" t="s">
         <v>2774</v>
@@ -46174,7 +46175,7 @@
     </row>
     <row r="1329" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1329" s="8" t="s">
-        <v>3014</v>
+        <v>3013</v>
       </c>
       <c r="B1329" s="5" t="s">
         <v>2774</v>
@@ -46201,7 +46202,7 @@
     </row>
     <row r="1330" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1330" s="8" t="s">
-        <v>3014</v>
+        <v>3013</v>
       </c>
       <c r="B1330" s="5" t="s">
         <v>2774</v>
@@ -46223,12 +46224,12 @@
       </c>
       <c r="H1330" s="12"/>
       <c r="I1330" s="12" t="s">
-        <v>3022</v>
+        <v>3021</v>
       </c>
     </row>
     <row r="1331" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1331" s="8" t="s">
-        <v>3014</v>
+        <v>3013</v>
       </c>
       <c r="B1331" s="5" t="s">
         <v>2774</v>
@@ -46255,7 +46256,7 @@
     </row>
     <row r="1332" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1332" s="8" t="s">
-        <v>3014</v>
+        <v>3013</v>
       </c>
       <c r="B1332" s="5" t="s">
         <v>2774</v>
@@ -46282,7 +46283,7 @@
     </row>
     <row r="1333" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1333" s="8" t="s">
-        <v>3014</v>
+        <v>3013</v>
       </c>
       <c r="B1333" s="5" t="s">
         <v>2774</v>
@@ -46309,7 +46310,7 @@
     </row>
     <row r="1334" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1334" s="8" t="s">
-        <v>3014</v>
+        <v>3013</v>
       </c>
       <c r="B1334" s="5" t="s">
         <v>2774</v>
@@ -46336,7 +46337,7 @@
     </row>
     <row r="1335" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1335" s="8" t="s">
-        <v>3014</v>
+        <v>3013</v>
       </c>
       <c r="B1335" s="5" t="s">
         <v>2774</v>
@@ -46363,7 +46364,7 @@
     </row>
     <row r="1336" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1336" s="8" t="s">
-        <v>3014</v>
+        <v>3013</v>
       </c>
       <c r="B1336" s="5" t="s">
         <v>2774</v>
@@ -46385,12 +46386,12 @@
       </c>
       <c r="H1336" s="12"/>
       <c r="I1336" s="12" t="s">
-        <v>3022</v>
+        <v>3021</v>
       </c>
     </row>
     <row r="1337" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1337" s="8" t="s">
-        <v>3014</v>
+        <v>3013</v>
       </c>
       <c r="B1337" s="5" t="s">
         <v>2774</v>
@@ -46417,7 +46418,7 @@
     </row>
     <row r="1338" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1338" s="8" t="s">
-        <v>3014</v>
+        <v>3013</v>
       </c>
       <c r="B1338" s="5" t="s">
         <v>2774</v>
@@ -46444,7 +46445,7 @@
     </row>
     <row r="1339" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1339" s="8" t="s">
-        <v>3014</v>
+        <v>3013</v>
       </c>
       <c r="B1339" s="5" t="s">
         <v>2774</v>
@@ -46471,7 +46472,7 @@
     </row>
     <row r="1340" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1340" s="8" t="s">
-        <v>3014</v>
+        <v>3013</v>
       </c>
       <c r="B1340" s="5" t="s">
         <v>2774</v>
@@ -46498,7 +46499,7 @@
     </row>
     <row r="1341" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1341" s="8" t="s">
-        <v>3014</v>
+        <v>3013</v>
       </c>
       <c r="B1341" s="5" t="s">
         <v>2774</v>
@@ -46525,7 +46526,7 @@
     </row>
     <row r="1342" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1342" s="8" t="s">
-        <v>3014</v>
+        <v>3013</v>
       </c>
       <c r="B1342" s="5" t="s">
         <v>2774</v>
@@ -46552,7 +46553,7 @@
     </row>
     <row r="1343" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1343" s="8" t="s">
-        <v>3014</v>
+        <v>3013</v>
       </c>
       <c r="B1343" s="5" t="s">
         <v>2774</v>
@@ -46579,7 +46580,7 @@
     </row>
     <row r="1344" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1344" s="8" t="s">
-        <v>3014</v>
+        <v>3013</v>
       </c>
       <c r="B1344" s="5" t="s">
         <v>2774</v>
@@ -46606,7 +46607,7 @@
     </row>
     <row r="1345" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1345" s="8" t="s">
-        <v>3014</v>
+        <v>3013</v>
       </c>
       <c r="B1345" s="5" t="s">
         <v>2774</v>
@@ -46621,19 +46622,19 @@
         <v>2775</v>
       </c>
       <c r="F1345" s="3" t="s">
-        <v>3023</v>
+        <v>3022</v>
       </c>
       <c r="G1345" s="3">
         <v>3</v>
       </c>
       <c r="H1345" s="12"/>
       <c r="I1345" s="12" t="s">
-        <v>3024</v>
+        <v>3023</v>
       </c>
     </row>
     <row r="1346" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1346" s="8" t="s">
-        <v>3014</v>
+        <v>3013</v>
       </c>
       <c r="B1346" s="5" t="s">
         <v>2774</v>
@@ -46660,7 +46661,7 @@
     </row>
     <row r="1347" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1347" s="8" t="s">
-        <v>3025</v>
+        <v>3024</v>
       </c>
       <c r="B1347" s="5" t="s">
         <v>2774</v>
@@ -46687,7 +46688,7 @@
     </row>
     <row r="1348" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1348" s="8" t="s">
-        <v>3025</v>
+        <v>3024</v>
       </c>
       <c r="B1348" s="5" t="s">
         <v>2774</v>
@@ -46714,7 +46715,7 @@
     </row>
     <row r="1349" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1349" s="8" t="s">
-        <v>3025</v>
+        <v>3024</v>
       </c>
       <c r="B1349" s="5" t="s">
         <v>2774</v>
@@ -46729,19 +46730,19 @@
         <v>2779</v>
       </c>
       <c r="F1349" s="3" t="s">
-        <v>3026</v>
+        <v>3025</v>
       </c>
       <c r="G1349" s="3">
         <v>1</v>
       </c>
       <c r="H1349" s="12"/>
       <c r="I1349" s="12" t="s">
-        <v>3027</v>
+        <v>3026</v>
       </c>
     </row>
     <row r="1350" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1350" s="8" t="s">
-        <v>3025</v>
+        <v>3024</v>
       </c>
       <c r="B1350" s="5" t="s">
         <v>2774</v>
@@ -46768,7 +46769,7 @@
     </row>
     <row r="1351" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1351" s="8" t="s">
-        <v>3025</v>
+        <v>3024</v>
       </c>
       <c r="B1351" s="5" t="s">
         <v>2774</v>
@@ -46795,7 +46796,7 @@
     </row>
     <row r="1352" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1352" s="8" t="s">
-        <v>3025</v>
+        <v>3024</v>
       </c>
       <c r="B1352" s="5" t="s">
         <v>2774</v>
@@ -46810,19 +46811,19 @@
         <v>2779</v>
       </c>
       <c r="F1352" s="3" t="s">
-        <v>3028</v>
+        <v>3027</v>
       </c>
       <c r="G1352" s="3">
         <v>1</v>
       </c>
       <c r="H1352" s="12"/>
       <c r="I1352" s="12" t="s">
-        <v>3029</v>
+        <v>3028</v>
       </c>
     </row>
     <row r="1353" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1353" s="8" t="s">
-        <v>3025</v>
+        <v>3024</v>
       </c>
       <c r="B1353" s="5" t="s">
         <v>2774</v>
@@ -46849,7 +46850,7 @@
     </row>
     <row r="1354" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1354" s="8" t="s">
-        <v>3025</v>
+        <v>3024</v>
       </c>
       <c r="B1354" s="5" t="s">
         <v>2774</v>
@@ -46864,19 +46865,19 @@
         <v>2775</v>
       </c>
       <c r="F1354" s="3" t="s">
-        <v>3030</v>
+        <v>3029</v>
       </c>
       <c r="G1354" s="3">
         <v>3</v>
       </c>
       <c r="H1354" s="12"/>
       <c r="I1354" s="12" t="s">
-        <v>3031</v>
+        <v>3030</v>
       </c>
     </row>
     <row r="1355" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1355" s="8" t="s">
-        <v>3025</v>
+        <v>3024</v>
       </c>
       <c r="B1355" s="5" t="s">
         <v>2774</v>
@@ -46891,19 +46892,19 @@
         <v>2779</v>
       </c>
       <c r="F1355" s="3" t="s">
-        <v>3032</v>
+        <v>3031</v>
       </c>
       <c r="G1355" s="3">
         <v>1</v>
       </c>
       <c r="H1355" s="12"/>
       <c r="I1355" s="12" t="s">
-        <v>3033</v>
+        <v>3032</v>
       </c>
     </row>
     <row r="1356" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1356" s="8" t="s">
-        <v>3025</v>
+        <v>3024</v>
       </c>
       <c r="B1356" s="5" t="s">
         <v>2774</v>
@@ -46930,7 +46931,7 @@
     </row>
     <row r="1357" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1357" s="8" t="s">
-        <v>3025</v>
+        <v>3024</v>
       </c>
       <c r="B1357" s="5" t="s">
         <v>2774</v>
@@ -46957,7 +46958,7 @@
     </row>
     <row r="1358" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1358" s="8" t="s">
-        <v>3025</v>
+        <v>3024</v>
       </c>
       <c r="B1358" s="5" t="s">
         <v>2774</v>
@@ -46984,7 +46985,7 @@
     </row>
     <row r="1359" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1359" s="8" t="s">
-        <v>3025</v>
+        <v>3024</v>
       </c>
       <c r="B1359" s="5" t="s">
         <v>2774</v>
@@ -47011,7 +47012,7 @@
     </row>
     <row r="1360" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1360" s="8" t="s">
-        <v>3025</v>
+        <v>3024</v>
       </c>
       <c r="B1360" s="5" t="s">
         <v>2774</v>
@@ -47038,7 +47039,7 @@
     </row>
     <row r="1361" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1361" s="8" t="s">
-        <v>3025</v>
+        <v>3024</v>
       </c>
       <c r="B1361" s="5" t="s">
         <v>2774</v>
@@ -47065,7 +47066,7 @@
     </row>
     <row r="1362" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1362" s="8" t="s">
-        <v>3025</v>
+        <v>3024</v>
       </c>
       <c r="B1362" s="5" t="s">
         <v>2774</v>
@@ -47080,7 +47081,7 @@
         <v>2775</v>
       </c>
       <c r="F1362" s="3" t="s">
-        <v>3034</v>
+        <v>3033</v>
       </c>
       <c r="G1362" s="3">
         <v>3</v>
@@ -47092,7 +47093,7 @@
     </row>
     <row r="1363" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1363" s="8" t="s">
-        <v>3025</v>
+        <v>3024</v>
       </c>
       <c r="B1363" s="5" t="s">
         <v>2774</v>
@@ -47119,7 +47120,7 @@
     </row>
     <row r="1364" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1364" s="8" t="s">
-        <v>3025</v>
+        <v>3024</v>
       </c>
       <c r="B1364" s="5" t="s">
         <v>2774</v>
@@ -47146,7 +47147,7 @@
     </row>
     <row r="1365" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1365" s="8" t="s">
-        <v>3025</v>
+        <v>3024</v>
       </c>
       <c r="B1365" s="5" t="s">
         <v>2774</v>
@@ -47173,7 +47174,7 @@
     </row>
     <row r="1366" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1366" s="8" t="s">
-        <v>3025</v>
+        <v>3024</v>
       </c>
       <c r="B1366" s="5" t="s">
         <v>2774</v>
@@ -47188,7 +47189,7 @@
         <v>2775</v>
       </c>
       <c r="F1366" s="3" t="s">
-        <v>3035</v>
+        <v>3034</v>
       </c>
       <c r="G1366" s="3">
         <v>2</v>
@@ -47200,7 +47201,7 @@
     </row>
     <row r="1367" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1367" s="8" t="s">
-        <v>3025</v>
+        <v>3024</v>
       </c>
       <c r="B1367" s="5" t="s">
         <v>2774</v>
@@ -47227,7 +47228,7 @@
     </row>
     <row r="1368" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1368" s="8" t="s">
-        <v>3025</v>
+        <v>3024</v>
       </c>
       <c r="B1368" s="5" t="s">
         <v>2774</v>
@@ -47242,19 +47243,19 @@
         <v>2779</v>
       </c>
       <c r="F1368" s="3" t="s">
-        <v>3036</v>
+        <v>3035</v>
       </c>
       <c r="G1368" s="3">
         <v>1</v>
       </c>
       <c r="H1368" s="12"/>
       <c r="I1368" s="12" t="s">
-        <v>3027</v>
+        <v>3026</v>
       </c>
     </row>
     <row r="1369" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1369" s="8" t="s">
-        <v>3025</v>
+        <v>3024</v>
       </c>
       <c r="B1369" s="5" t="s">
         <v>2774</v>
@@ -47281,7 +47282,7 @@
     </row>
     <row r="1370" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1370" s="8" t="s">
-        <v>3025</v>
+        <v>3024</v>
       </c>
       <c r="B1370" s="5" t="s">
         <v>2774</v>
@@ -47296,19 +47297,19 @@
         <v>2775</v>
       </c>
       <c r="F1370" s="3" t="s">
-        <v>3037</v>
+        <v>3036</v>
       </c>
       <c r="G1370" s="3">
         <v>3</v>
       </c>
       <c r="H1370" s="12"/>
       <c r="I1370" s="12" t="s">
-        <v>3038</v>
+        <v>3037</v>
       </c>
     </row>
     <row r="1371" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1371" s="8" t="s">
-        <v>3025</v>
+        <v>3024</v>
       </c>
       <c r="B1371" s="5" t="s">
         <v>2774</v>
@@ -47330,12 +47331,12 @@
       </c>
       <c r="H1371" s="12"/>
       <c r="I1371" s="12" t="s">
-        <v>3039</v>
+        <v>3038</v>
       </c>
     </row>
     <row r="1372" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1372" s="8" t="s">
-        <v>3025</v>
+        <v>3024</v>
       </c>
       <c r="B1372" s="5" t="s">
         <v>2774</v>
@@ -47362,7 +47363,7 @@
     </row>
     <row r="1373" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1373" s="8" t="s">
-        <v>3025</v>
+        <v>3024</v>
       </c>
       <c r="B1373" s="5" t="s">
         <v>2774</v>
@@ -47389,7 +47390,7 @@
     </row>
     <row r="1374" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1374" s="8" t="s">
-        <v>3025</v>
+        <v>3024</v>
       </c>
       <c r="B1374" s="5" t="s">
         <v>2774</v>
@@ -47404,7 +47405,7 @@
         <v>2775</v>
       </c>
       <c r="F1374" s="3" t="s">
-        <v>3040</v>
+        <v>3039</v>
       </c>
       <c r="G1374" s="3">
         <v>3</v>
@@ -47414,7 +47415,7 @@
     </row>
     <row r="1375" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1375" s="8" t="s">
-        <v>3025</v>
+        <v>3024</v>
       </c>
       <c r="B1375" s="5" t="s">
         <v>2774</v>
@@ -47441,7 +47442,7 @@
     </row>
     <row r="1376" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1376" s="8" t="s">
-        <v>3025</v>
+        <v>3024</v>
       </c>
       <c r="B1376" s="5" t="s">
         <v>2774</v>
@@ -47456,7 +47457,7 @@
         <v>2775</v>
       </c>
       <c r="F1376" s="3" t="s">
-        <v>3041</v>
+        <v>3040</v>
       </c>
       <c r="G1376" s="3">
         <v>2</v>
@@ -47468,7 +47469,7 @@
     </row>
     <row r="1377" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1377" s="8" t="s">
-        <v>3025</v>
+        <v>3024</v>
       </c>
       <c r="B1377" s="5" t="s">
         <v>2774</v>
@@ -47495,7 +47496,7 @@
     </row>
     <row r="1378" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1378" s="8" t="s">
-        <v>3025</v>
+        <v>3024</v>
       </c>
       <c r="B1378" s="5" t="s">
         <v>2774</v>
@@ -47522,7 +47523,7 @@
     </row>
     <row r="1379" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1379" s="8" t="s">
-        <v>3025</v>
+        <v>3024</v>
       </c>
       <c r="B1379" s="5" t="s">
         <v>2774</v>
@@ -47544,12 +47545,12 @@
       </c>
       <c r="H1379" s="12"/>
       <c r="I1379" s="12" t="s">
-        <v>3039</v>
+        <v>3038</v>
       </c>
     </row>
     <row r="1380" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1380" s="8" t="s">
-        <v>3025</v>
+        <v>3024</v>
       </c>
       <c r="B1380" s="5" t="s">
         <v>2774</v>
@@ -47576,7 +47577,7 @@
     </row>
     <row r="1381" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1381" s="8" t="s">
-        <v>3025</v>
+        <v>3024</v>
       </c>
       <c r="B1381" s="5" t="s">
         <v>2774</v>
@@ -47603,7 +47604,7 @@
     </row>
     <row r="1382" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1382" s="8" t="s">
-        <v>3025</v>
+        <v>3024</v>
       </c>
       <c r="B1382" s="5" t="s">
         <v>2774</v>
@@ -47618,7 +47619,7 @@
         <v>2775</v>
       </c>
       <c r="F1382" s="3" t="s">
-        <v>3042</v>
+        <v>3041</v>
       </c>
       <c r="G1382" s="3">
         <v>3</v>
@@ -47628,7 +47629,7 @@
     </row>
     <row r="1383" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1383" s="8" t="s">
-        <v>3025</v>
+        <v>3024</v>
       </c>
       <c r="B1383" s="5" t="s">
         <v>2774</v>
@@ -47643,19 +47644,19 @@
         <v>2775</v>
       </c>
       <c r="F1383" s="3" t="s">
-        <v>3043</v>
+        <v>3042</v>
       </c>
       <c r="G1383" s="3">
         <v>3</v>
       </c>
       <c r="H1383" s="12"/>
       <c r="I1383" s="12" t="s">
-        <v>3038</v>
+        <v>3037</v>
       </c>
     </row>
     <row r="1384" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1384" s="8" t="s">
-        <v>3025</v>
+        <v>3024</v>
       </c>
       <c r="B1384" s="5" t="s">
         <v>2774</v>
@@ -47670,7 +47671,7 @@
         <v>2775</v>
       </c>
       <c r="F1384" s="3" t="s">
-        <v>3044</v>
+        <v>3043</v>
       </c>
       <c r="G1384" s="3">
         <v>2</v>
@@ -47682,7 +47683,7 @@
     </row>
     <row r="1385" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1385" s="8" t="s">
-        <v>3025</v>
+        <v>3024</v>
       </c>
       <c r="B1385" s="5" t="s">
         <v>2774</v>
@@ -47697,7 +47698,7 @@
         <v>2775</v>
       </c>
       <c r="F1385" s="3" t="s">
-        <v>3045</v>
+        <v>3044</v>
       </c>
       <c r="G1385" s="3">
         <v>2</v>
@@ -47709,7 +47710,7 @@
     </row>
     <row r="1386" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1386" s="8" t="s">
-        <v>3025</v>
+        <v>3024</v>
       </c>
       <c r="B1386" s="5" t="s">
         <v>2774</v>
@@ -47736,7 +47737,7 @@
     </row>
     <row r="1387" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1387" s="8" t="s">
-        <v>3025</v>
+        <v>3024</v>
       </c>
       <c r="B1387" s="5" t="s">
         <v>2774</v>
@@ -47763,7 +47764,7 @@
     </row>
     <row r="1388" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1388" s="8" t="s">
-        <v>3025</v>
+        <v>3024</v>
       </c>
       <c r="B1388" s="5" t="s">
         <v>2774</v>
@@ -47790,7 +47791,7 @@
     </row>
     <row r="1389" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1389" s="8" t="s">
-        <v>3025</v>
+        <v>3024</v>
       </c>
       <c r="B1389" s="5" t="s">
         <v>2774</v>
@@ -47817,7 +47818,7 @@
     </row>
     <row r="1390" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1390" s="8" t="s">
-        <v>3025</v>
+        <v>3024</v>
       </c>
       <c r="B1390" s="5" t="s">
         <v>2774</v>
@@ -47832,19 +47833,19 @@
         <v>2775</v>
       </c>
       <c r="F1390" s="3" t="s">
-        <v>3046</v>
+        <v>3045</v>
       </c>
       <c r="G1390" s="3">
         <v>2</v>
       </c>
       <c r="H1390" s="12"/>
       <c r="I1390" s="12" t="s">
-        <v>3047</v>
+        <v>3046</v>
       </c>
     </row>
     <row r="1391" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1391" s="8" t="s">
-        <v>3025</v>
+        <v>3024</v>
       </c>
       <c r="B1391" s="5" t="s">
         <v>2774</v>
@@ -47859,7 +47860,7 @@
         <v>2775</v>
       </c>
       <c r="F1391" s="3" t="s">
-        <v>3048</v>
+        <v>3047</v>
       </c>
       <c r="G1391" s="3">
         <v>3</v>
@@ -47871,7 +47872,7 @@
     </row>
     <row r="1392" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1392" s="8" t="s">
-        <v>3025</v>
+        <v>3024</v>
       </c>
       <c r="B1392" s="5" t="s">
         <v>2774</v>
@@ -47886,7 +47887,7 @@
         <v>2775</v>
       </c>
       <c r="F1392" s="3" t="s">
-        <v>3049</v>
+        <v>3048</v>
       </c>
       <c r="G1392" s="3">
         <v>3</v>
@@ -47898,7 +47899,7 @@
     </row>
     <row r="1393" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1393" s="8" t="s">
-        <v>3025</v>
+        <v>3024</v>
       </c>
       <c r="B1393" s="5" t="s">
         <v>2774</v>
@@ -47925,7 +47926,7 @@
     </row>
     <row r="1394" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1394" s="8" t="s">
-        <v>3025</v>
+        <v>3024</v>
       </c>
       <c r="B1394" s="5" t="s">
         <v>2774</v>
@@ -47952,7 +47953,7 @@
     </row>
     <row r="1395" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1395" s="8" t="s">
-        <v>3025</v>
+        <v>3024</v>
       </c>
       <c r="B1395" s="5" t="s">
         <v>2774</v>
@@ -47979,7 +47980,7 @@
     </row>
     <row r="1396" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1396" s="8" t="s">
-        <v>3025</v>
+        <v>3024</v>
       </c>
       <c r="B1396" s="5" t="s">
         <v>2774</v>
@@ -47994,7 +47995,7 @@
         <v>2779</v>
       </c>
       <c r="F1396" s="3" t="s">
-        <v>3050</v>
+        <v>3049</v>
       </c>
       <c r="G1396" s="3">
         <v>3</v>
@@ -48006,7 +48007,7 @@
     </row>
     <row r="1397" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1397" s="8" t="s">
-        <v>3025</v>
+        <v>3024</v>
       </c>
       <c r="B1397" s="5" t="s">
         <v>2774</v>
@@ -48033,7 +48034,7 @@
     </row>
     <row r="1398" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1398" s="8" t="s">
-        <v>3025</v>
+        <v>3024</v>
       </c>
       <c r="B1398" s="5" t="s">
         <v>2774</v>
@@ -48060,7 +48061,7 @@
     </row>
     <row r="1399" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1399" s="8" t="s">
-        <v>3025</v>
+        <v>3024</v>
       </c>
       <c r="B1399" s="5" t="s">
         <v>2774</v>
@@ -48087,7 +48088,7 @@
     </row>
     <row r="1400" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1400" s="8" t="s">
-        <v>3025</v>
+        <v>3024</v>
       </c>
       <c r="B1400" s="5" t="s">
         <v>2774</v>
@@ -48114,7 +48115,7 @@
     </row>
     <row r="1401" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1401" s="8" t="s">
-        <v>3025</v>
+        <v>3024</v>
       </c>
       <c r="B1401" s="5" t="s">
         <v>2774</v>
@@ -48129,7 +48130,7 @@
         <v>2775</v>
       </c>
       <c r="F1401" s="3" t="s">
-        <v>3051</v>
+        <v>3050</v>
       </c>
       <c r="G1401" s="3">
         <v>2</v>
@@ -48141,7 +48142,7 @@
     </row>
     <row r="1402" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1402" s="8" t="s">
-        <v>3052</v>
+        <v>3051</v>
       </c>
       <c r="B1402" s="5" t="s">
         <v>2774</v>
@@ -48168,7 +48169,7 @@
     </row>
     <row r="1403" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1403" s="8" t="s">
-        <v>3052</v>
+        <v>3051</v>
       </c>
       <c r="B1403" s="5" t="s">
         <v>2774</v>
@@ -48195,7 +48196,7 @@
     </row>
     <row r="1404" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1404" s="8" t="s">
-        <v>3052</v>
+        <v>3051</v>
       </c>
       <c r="B1404" s="5" t="s">
         <v>2774</v>
@@ -48222,7 +48223,7 @@
     </row>
     <row r="1405" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1405" s="8" t="s">
-        <v>3052</v>
+        <v>3051</v>
       </c>
       <c r="B1405" s="5" t="s">
         <v>2774</v>
@@ -48249,7 +48250,7 @@
     </row>
     <row r="1406" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1406" s="8" t="s">
-        <v>3052</v>
+        <v>3051</v>
       </c>
       <c r="B1406" s="5" t="s">
         <v>2774</v>
@@ -48276,7 +48277,7 @@
     </row>
     <row r="1407" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1407" s="8" t="s">
-        <v>3052</v>
+        <v>3051</v>
       </c>
       <c r="B1407" s="5" t="s">
         <v>2774</v>
@@ -48303,7 +48304,7 @@
     </row>
     <row r="1408" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1408" s="8" t="s">
-        <v>3052</v>
+        <v>3051</v>
       </c>
       <c r="B1408" s="5" t="s">
         <v>2774</v>
@@ -48330,7 +48331,7 @@
     </row>
     <row r="1409" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1409" s="8" t="s">
-        <v>3052</v>
+        <v>3051</v>
       </c>
       <c r="B1409" s="5" t="s">
         <v>2774</v>
@@ -48357,7 +48358,7 @@
     </row>
     <row r="1410" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1410" s="8" t="s">
-        <v>3052</v>
+        <v>3051</v>
       </c>
       <c r="B1410" s="5" t="s">
         <v>2774</v>
@@ -48384,7 +48385,7 @@
     </row>
     <row r="1411" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1411" s="8" t="s">
-        <v>3052</v>
+        <v>3051</v>
       </c>
       <c r="B1411" s="5" t="s">
         <v>2774</v>
@@ -48411,7 +48412,7 @@
     </row>
     <row r="1412" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1412" s="8" t="s">
-        <v>3052</v>
+        <v>3051</v>
       </c>
       <c r="B1412" s="5" t="s">
         <v>2774</v>
@@ -48438,7 +48439,7 @@
     </row>
     <row r="1413" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1413" s="8" t="s">
-        <v>3052</v>
+        <v>3051</v>
       </c>
       <c r="B1413" s="5" t="s">
         <v>2774</v>
@@ -48465,7 +48466,7 @@
     </row>
     <row r="1414" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1414" s="8" t="s">
-        <v>3052</v>
+        <v>3051</v>
       </c>
       <c r="B1414" s="5" t="s">
         <v>2774</v>
@@ -48492,7 +48493,7 @@
     </row>
     <row r="1415" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1415" s="8" t="s">
-        <v>3052</v>
+        <v>3051</v>
       </c>
       <c r="B1415" s="5" t="s">
         <v>2774</v>
@@ -48519,7 +48520,7 @@
     </row>
     <row r="1416" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1416" s="8" t="s">
-        <v>3052</v>
+        <v>3051</v>
       </c>
       <c r="B1416" s="5" t="s">
         <v>2774</v>
@@ -48546,7 +48547,7 @@
     </row>
     <row r="1417" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1417" s="8" t="s">
-        <v>3052</v>
+        <v>3051</v>
       </c>
       <c r="B1417" s="5" t="s">
         <v>2774</v>
@@ -48573,7 +48574,7 @@
     </row>
     <row r="1418" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1418" s="8" t="s">
-        <v>3052</v>
+        <v>3051</v>
       </c>
       <c r="B1418" s="5" t="s">
         <v>2774</v>
@@ -48600,7 +48601,7 @@
     </row>
     <row r="1419" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1419" s="8" t="s">
-        <v>3052</v>
+        <v>3051</v>
       </c>
       <c r="B1419" s="5" t="s">
         <v>2774</v>
@@ -48627,7 +48628,7 @@
     </row>
     <row r="1420" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1420" s="8" t="s">
-        <v>3052</v>
+        <v>3051</v>
       </c>
       <c r="B1420" s="5" t="s">
         <v>2774</v>
@@ -48654,7 +48655,7 @@
     </row>
     <row r="1421" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1421" s="8" t="s">
-        <v>3052</v>
+        <v>3051</v>
       </c>
       <c r="B1421" s="5" t="s">
         <v>2774</v>
@@ -48681,7 +48682,7 @@
     </row>
     <row r="1422" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1422" s="8" t="s">
-        <v>3052</v>
+        <v>3051</v>
       </c>
       <c r="B1422" s="5" t="s">
         <v>2774</v>
@@ -48708,7 +48709,7 @@
     </row>
     <row r="1423" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1423" s="8" t="s">
-        <v>3052</v>
+        <v>3051</v>
       </c>
       <c r="B1423" s="5" t="s">
         <v>2774</v>
@@ -48735,7 +48736,7 @@
     </row>
     <row r="1424" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1424" s="8" t="s">
-        <v>3052</v>
+        <v>3051</v>
       </c>
       <c r="B1424" s="5" t="s">
         <v>2774</v>
@@ -48762,7 +48763,7 @@
     </row>
     <row r="1425" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1425" s="8" t="s">
-        <v>3052</v>
+        <v>3051</v>
       </c>
       <c r="B1425" s="5" t="s">
         <v>2774</v>
@@ -48789,7 +48790,7 @@
     </row>
     <row r="1426" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1426" s="8" t="s">
-        <v>3052</v>
+        <v>3051</v>
       </c>
       <c r="B1426" s="5" t="s">
         <v>2774</v>
@@ -48816,7 +48817,7 @@
     </row>
     <row r="1427" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1427" s="8" t="s">
-        <v>3052</v>
+        <v>3051</v>
       </c>
       <c r="B1427" s="5" t="s">
         <v>2774</v>
@@ -48843,7 +48844,7 @@
     </row>
     <row r="1428" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1428" s="8" t="s">
-        <v>3052</v>
+        <v>3051</v>
       </c>
       <c r="B1428" s="5" t="s">
         <v>2774</v>
@@ -48870,7 +48871,7 @@
     </row>
     <row r="1429" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1429" s="8" t="s">
-        <v>3052</v>
+        <v>3051</v>
       </c>
       <c r="B1429" s="5" t="s">
         <v>2774</v>
@@ -48897,34 +48898,34 @@
     </row>
     <row r="1430" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1430" s="8" t="s">
+        <v>3051</v>
+      </c>
+      <c r="B1430" s="5" t="s">
+        <v>2774</v>
+      </c>
+      <c r="C1430" s="6">
+        <v>3</v>
+      </c>
+      <c r="D1430" s="6">
+        <v>2</v>
+      </c>
+      <c r="E1430" s="7" t="s">
+        <v>2775</v>
+      </c>
+      <c r="F1430" s="3" t="s">
         <v>3052</v>
-      </c>
-      <c r="B1430" s="5" t="s">
-        <v>2774</v>
-      </c>
-      <c r="C1430" s="6">
-        <v>3</v>
-      </c>
-      <c r="D1430" s="6">
-        <v>2</v>
-      </c>
-      <c r="E1430" s="7" t="s">
-        <v>2775</v>
-      </c>
-      <c r="F1430" s="3" t="s">
-        <v>3053</v>
       </c>
       <c r="G1430" s="3">
         <v>3</v>
       </c>
       <c r="H1430" s="12"/>
       <c r="I1430" s="12" t="s">
-        <v>3054</v>
+        <v>3053</v>
       </c>
     </row>
     <row r="1431" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1431" s="8" t="s">
-        <v>3052</v>
+        <v>3051</v>
       </c>
       <c r="B1431" s="5" t="s">
         <v>2774</v>
@@ -48951,7 +48952,7 @@
     </row>
     <row r="1432" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1432" s="8" t="s">
-        <v>3052</v>
+        <v>3051</v>
       </c>
       <c r="B1432" s="5" t="s">
         <v>2774</v>
@@ -48966,19 +48967,19 @@
         <v>2775</v>
       </c>
       <c r="F1432" s="3" t="s">
-        <v>3055</v>
+        <v>3054</v>
       </c>
       <c r="G1432" s="3">
         <v>2</v>
       </c>
       <c r="H1432" s="12"/>
       <c r="I1432" s="12" t="s">
-        <v>3056</v>
+        <v>3055</v>
       </c>
     </row>
     <row r="1433" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1433" s="8" t="s">
-        <v>3052</v>
+        <v>3051</v>
       </c>
       <c r="B1433" s="5" t="s">
         <v>2774</v>
@@ -49005,7 +49006,7 @@
     </row>
     <row r="1434" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1434" s="8" t="s">
-        <v>3052</v>
+        <v>3051</v>
       </c>
       <c r="B1434" s="5" t="s">
         <v>2774</v>
@@ -49032,7 +49033,7 @@
     </row>
     <row r="1435" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1435" s="8" t="s">
-        <v>3052</v>
+        <v>3051</v>
       </c>
       <c r="B1435" s="5" t="s">
         <v>2774</v>
@@ -49059,7 +49060,7 @@
     </row>
     <row r="1436" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1436" s="8" t="s">
-        <v>3052</v>
+        <v>3051</v>
       </c>
       <c r="B1436" s="5" t="s">
         <v>2774</v>
@@ -49074,7 +49075,7 @@
         <v>2775</v>
       </c>
       <c r="F1436" s="3" t="s">
-        <v>3057</v>
+        <v>3056</v>
       </c>
       <c r="G1436" s="3">
         <v>3</v>
@@ -49086,7 +49087,7 @@
     </row>
     <row r="1437" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1437" s="8" t="s">
-        <v>3052</v>
+        <v>3051</v>
       </c>
       <c r="B1437" s="5" t="s">
         <v>2774</v>
@@ -49113,7 +49114,7 @@
     </row>
     <row r="1438" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1438" s="8" t="s">
-        <v>3052</v>
+        <v>3051</v>
       </c>
       <c r="B1438" s="5" t="s">
         <v>2774</v>
@@ -49135,12 +49136,12 @@
       </c>
       <c r="H1438" s="12"/>
       <c r="I1438" s="12" t="s">
-        <v>3058</v>
+        <v>3057</v>
       </c>
     </row>
     <row r="1439" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1439" s="8" t="s">
-        <v>3052</v>
+        <v>3051</v>
       </c>
       <c r="B1439" s="5" t="s">
         <v>2774</v>
@@ -49167,7 +49168,7 @@
     </row>
     <row r="1440" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1440" s="8" t="s">
-        <v>3052</v>
+        <v>3051</v>
       </c>
       <c r="B1440" s="5" t="s">
         <v>2774</v>
@@ -49194,7 +49195,7 @@
     </row>
     <row r="1441" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1441" s="8" t="s">
-        <v>3052</v>
+        <v>3051</v>
       </c>
       <c r="B1441" s="5" t="s">
         <v>2774</v>
@@ -49221,7 +49222,7 @@
     </row>
     <row r="1442" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1442" s="8" t="s">
-        <v>3052</v>
+        <v>3051</v>
       </c>
       <c r="B1442" s="5" t="s">
         <v>2774</v>
@@ -49236,7 +49237,7 @@
         <v>2775</v>
       </c>
       <c r="F1442" s="3" t="s">
-        <v>3059</v>
+        <v>3058</v>
       </c>
       <c r="G1442" s="3">
         <v>3</v>
@@ -49248,7 +49249,7 @@
     </row>
     <row r="1443" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1443" s="8" t="s">
-        <v>3052</v>
+        <v>3051</v>
       </c>
       <c r="B1443" s="5" t="s">
         <v>2774</v>
@@ -49275,7 +49276,7 @@
     </row>
     <row r="1444" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1444" s="8" t="s">
-        <v>3052</v>
+        <v>3051</v>
       </c>
       <c r="B1444" s="5" t="s">
         <v>2774</v>
@@ -49297,12 +49298,12 @@
       </c>
       <c r="H1444" s="12"/>
       <c r="I1444" s="12" t="s">
-        <v>3060</v>
+        <v>3059</v>
       </c>
     </row>
     <row r="1445" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1445" s="8" t="s">
-        <v>3061</v>
+        <v>3060</v>
       </c>
       <c r="B1445" s="5" t="s">
         <v>2774</v>
@@ -49324,12 +49325,12 @@
       </c>
       <c r="H1445" s="12"/>
       <c r="I1445" s="12" t="s">
-        <v>3062</v>
+        <v>3061</v>
       </c>
     </row>
     <row r="1446" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1446" s="8" t="s">
-        <v>3061</v>
+        <v>3060</v>
       </c>
       <c r="B1446" s="5" t="s">
         <v>2774</v>
@@ -49351,12 +49352,12 @@
       </c>
       <c r="H1446" s="12"/>
       <c r="I1446" s="12" t="s">
-        <v>3063</v>
+        <v>3062</v>
       </c>
     </row>
     <row r="1447" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1447" s="8" t="s">
-        <v>3061</v>
+        <v>3060</v>
       </c>
       <c r="B1447" s="5" t="s">
         <v>2774</v>
@@ -49378,12 +49379,12 @@
       </c>
       <c r="H1447" s="12"/>
       <c r="I1447" s="12" t="s">
-        <v>3064</v>
+        <v>3063</v>
       </c>
     </row>
     <row r="1448" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1448" s="8" t="s">
-        <v>3061</v>
+        <v>3060</v>
       </c>
       <c r="B1448" s="5" t="s">
         <v>2774</v>
@@ -49405,12 +49406,12 @@
       </c>
       <c r="H1448" s="12"/>
       <c r="I1448" s="12" t="s">
-        <v>3063</v>
+        <v>3062</v>
       </c>
     </row>
     <row r="1449" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1449" s="8" t="s">
-        <v>3061</v>
+        <v>3060</v>
       </c>
       <c r="B1449" s="5" t="s">
         <v>2774</v>
@@ -49432,12 +49433,12 @@
       </c>
       <c r="H1449" s="12"/>
       <c r="I1449" s="12" t="s">
-        <v>3065</v>
+        <v>3064</v>
       </c>
     </row>
     <row r="1450" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1450" s="8" t="s">
-        <v>3061</v>
+        <v>3060</v>
       </c>
       <c r="B1450" s="5" t="s">
         <v>2774</v>
@@ -49459,12 +49460,12 @@
       </c>
       <c r="H1450" s="12"/>
       <c r="I1450" s="12" t="s">
-        <v>3063</v>
+        <v>3062</v>
       </c>
     </row>
     <row r="1451" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1451" s="8" t="s">
-        <v>3061</v>
+        <v>3060</v>
       </c>
       <c r="B1451" s="5" t="s">
         <v>2774</v>
@@ -49486,12 +49487,12 @@
       </c>
       <c r="H1451" s="12"/>
       <c r="I1451" s="12" t="s">
-        <v>3066</v>
+        <v>3065</v>
       </c>
     </row>
     <row r="1452" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1452" s="8" t="s">
-        <v>3061</v>
+        <v>3060</v>
       </c>
       <c r="B1452" s="5" t="s">
         <v>2774</v>
@@ -49518,7 +49519,7 @@
     </row>
     <row r="1453" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1453" s="8" t="s">
-        <v>3061</v>
+        <v>3060</v>
       </c>
       <c r="B1453" s="5" t="s">
         <v>2774</v>
@@ -49545,7 +49546,7 @@
     </row>
     <row r="1454" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1454" s="8" t="s">
-        <v>3061</v>
+        <v>3060</v>
       </c>
       <c r="B1454" s="5" t="s">
         <v>2774</v>
@@ -49567,12 +49568,12 @@
       </c>
       <c r="H1454" s="12"/>
       <c r="I1454" s="12" t="s">
-        <v>3063</v>
+        <v>3062</v>
       </c>
     </row>
     <row r="1455" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1455" s="8" t="s">
-        <v>3061</v>
+        <v>3060</v>
       </c>
       <c r="B1455" s="5" t="s">
         <v>2774</v>
@@ -49594,12 +49595,12 @@
       </c>
       <c r="H1455" s="12"/>
       <c r="I1455" s="12" t="s">
-        <v>3063</v>
+        <v>3062</v>
       </c>
     </row>
     <row r="1456" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1456" s="8" t="s">
-        <v>3061</v>
+        <v>3060</v>
       </c>
       <c r="B1456" s="5" t="s">
         <v>2774</v>
@@ -49621,12 +49622,12 @@
       </c>
       <c r="H1456" s="12"/>
       <c r="I1456" s="12" t="s">
-        <v>3063</v>
+        <v>3062</v>
       </c>
     </row>
     <row r="1457" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1457" s="8" t="s">
-        <v>3061</v>
+        <v>3060</v>
       </c>
       <c r="B1457" s="5" t="s">
         <v>2774</v>
@@ -49648,12 +49649,12 @@
       </c>
       <c r="H1457" s="12"/>
       <c r="I1457" s="12" t="s">
-        <v>3063</v>
+        <v>3062</v>
       </c>
     </row>
     <row r="1458" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1458" s="8" t="s">
-        <v>3061</v>
+        <v>3060</v>
       </c>
       <c r="B1458" s="5" t="s">
         <v>2774</v>
@@ -49680,7 +49681,7 @@
     </row>
     <row r="1459" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1459" s="8" t="s">
-        <v>3061</v>
+        <v>3060</v>
       </c>
       <c r="B1459" s="5" t="s">
         <v>2774</v>
@@ -49707,7 +49708,7 @@
     </row>
     <row r="1460" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1460" s="8" t="s">
-        <v>3061</v>
+        <v>3060</v>
       </c>
       <c r="B1460" s="5" t="s">
         <v>2774</v>
@@ -49734,7 +49735,7 @@
     </row>
     <row r="1461" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1461" s="8" t="s">
-        <v>3061</v>
+        <v>3060</v>
       </c>
       <c r="B1461" s="5" t="s">
         <v>2774</v>
@@ -49756,12 +49757,12 @@
       </c>
       <c r="H1461" s="12"/>
       <c r="I1461" s="12" t="s">
-        <v>3063</v>
+        <v>3062</v>
       </c>
     </row>
     <row r="1462" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1462" s="8" t="s">
-        <v>3061</v>
+        <v>3060</v>
       </c>
       <c r="B1462" s="5" t="s">
         <v>2774</v>
@@ -49783,12 +49784,12 @@
       </c>
       <c r="H1462" s="12"/>
       <c r="I1462" s="12" t="s">
-        <v>3063</v>
+        <v>3062</v>
       </c>
     </row>
     <row r="1463" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1463" s="8" t="s">
-        <v>3061</v>
+        <v>3060</v>
       </c>
       <c r="B1463" s="5" t="s">
         <v>2774</v>
@@ -49810,12 +49811,12 @@
       </c>
       <c r="H1463" s="12"/>
       <c r="I1463" s="12" t="s">
-        <v>3063</v>
+        <v>3062</v>
       </c>
     </row>
     <row r="1464" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1464" s="8" t="s">
-        <v>3061</v>
+        <v>3060</v>
       </c>
       <c r="B1464" s="5" t="s">
         <v>2774</v>
@@ -49837,12 +49838,12 @@
       </c>
       <c r="H1464" s="12"/>
       <c r="I1464" s="12" t="s">
-        <v>3067</v>
+        <v>3066</v>
       </c>
     </row>
     <row r="1465" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1465" s="8" t="s">
-        <v>3061</v>
+        <v>3060</v>
       </c>
       <c r="B1465" s="5" t="s">
         <v>2774</v>
@@ -49864,12 +49865,12 @@
       </c>
       <c r="H1465" s="12"/>
       <c r="I1465" s="12" t="s">
-        <v>3068</v>
+        <v>3067</v>
       </c>
     </row>
     <row r="1466" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1466" s="8" t="s">
-        <v>3061</v>
+        <v>3060</v>
       </c>
       <c r="B1466" s="5" t="s">
         <v>2774</v>
@@ -49891,12 +49892,12 @@
       </c>
       <c r="H1466" s="12"/>
       <c r="I1466" s="12" t="s">
-        <v>3069</v>
+        <v>3068</v>
       </c>
     </row>
     <row r="1467" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1467" s="8" t="s">
-        <v>3061</v>
+        <v>3060</v>
       </c>
       <c r="B1467" s="5" t="s">
         <v>2774</v>
@@ -49918,12 +49919,12 @@
       </c>
       <c r="H1467" s="12"/>
       <c r="I1467" s="12" t="s">
-        <v>3063</v>
+        <v>3062</v>
       </c>
     </row>
     <row r="1468" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1468" s="8" t="s">
-        <v>3061</v>
+        <v>3060</v>
       </c>
       <c r="B1468" s="5" t="s">
         <v>2774</v>
@@ -49945,12 +49946,12 @@
       </c>
       <c r="H1468" s="12"/>
       <c r="I1468" s="12" t="s">
-        <v>3063</v>
+        <v>3062</v>
       </c>
     </row>
     <row r="1469" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1469" s="8" t="s">
-        <v>3061</v>
+        <v>3060</v>
       </c>
       <c r="B1469" s="5" t="s">
         <v>2774</v>
@@ -49965,19 +49966,19 @@
         <v>2775</v>
       </c>
       <c r="F1469" s="3" t="s">
-        <v>3070</v>
+        <v>3069</v>
       </c>
       <c r="G1469" s="3">
         <v>3</v>
       </c>
       <c r="H1469" s="12"/>
       <c r="I1469" s="12" t="s">
-        <v>3071</v>
+        <v>3070</v>
       </c>
     </row>
     <row r="1470" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1470" s="8" t="s">
-        <v>3061</v>
+        <v>3060</v>
       </c>
       <c r="B1470" s="5" t="s">
         <v>2774</v>
@@ -49992,19 +49993,19 @@
         <v>2775</v>
       </c>
       <c r="F1470" s="3" t="s">
-        <v>3072</v>
+        <v>3071</v>
       </c>
       <c r="G1470" s="3">
         <v>3</v>
       </c>
       <c r="H1470" s="12"/>
       <c r="I1470" s="12" t="s">
-        <v>3073</v>
+        <v>3072</v>
       </c>
     </row>
     <row r="1471" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1471" s="8" t="s">
-        <v>3061</v>
+        <v>3060</v>
       </c>
       <c r="B1471" s="5" t="s">
         <v>2774</v>
@@ -50031,7 +50032,7 @@
     </row>
     <row r="1472" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1472" s="8" t="s">
-        <v>3061</v>
+        <v>3060</v>
       </c>
       <c r="B1472" s="5" t="s">
         <v>2774</v>
@@ -50053,12 +50054,12 @@
       </c>
       <c r="H1472" s="12"/>
       <c r="I1472" s="12" t="s">
-        <v>3063</v>
+        <v>3062</v>
       </c>
     </row>
     <row r="1473" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1473" s="8" t="s">
-        <v>3061</v>
+        <v>3060</v>
       </c>
       <c r="B1473" s="5" t="s">
         <v>2774</v>
@@ -50085,7 +50086,7 @@
     </row>
     <row r="1474" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1474" s="8" t="s">
-        <v>3061</v>
+        <v>3060</v>
       </c>
       <c r="B1474" s="5" t="s">
         <v>2774</v>
@@ -50107,12 +50108,12 @@
       </c>
       <c r="H1474" s="12"/>
       <c r="I1474" s="12" t="s">
-        <v>3074</v>
+        <v>3073</v>
       </c>
     </row>
     <row r="1475" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1475" s="8" t="s">
-        <v>3061</v>
+        <v>3060</v>
       </c>
       <c r="B1475" s="5" t="s">
         <v>2774</v>
@@ -50139,7 +50140,7 @@
     </row>
     <row r="1476" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1476" s="8" t="s">
-        <v>3061</v>
+        <v>3060</v>
       </c>
       <c r="B1476" s="5" t="s">
         <v>2774</v>
@@ -50166,7 +50167,7 @@
     </row>
     <row r="1477" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1477" s="8" t="s">
-        <v>3061</v>
+        <v>3060</v>
       </c>
       <c r="B1477" s="5" t="s">
         <v>2774</v>
@@ -50193,7 +50194,7 @@
     </row>
     <row r="1478" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1478" s="8" t="s">
-        <v>3061</v>
+        <v>3060</v>
       </c>
       <c r="B1478" s="5" t="s">
         <v>2774</v>
@@ -50220,7 +50221,7 @@
     </row>
     <row r="1479" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1479" s="8" t="s">
-        <v>3061</v>
+        <v>3060</v>
       </c>
       <c r="B1479" s="5" t="s">
         <v>2774</v>
@@ -50242,12 +50243,12 @@
       </c>
       <c r="H1479" s="12"/>
       <c r="I1479" s="12" t="s">
-        <v>3075</v>
+        <v>3074</v>
       </c>
     </row>
     <row r="1480" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1480" s="8" t="s">
-        <v>3061</v>
+        <v>3060</v>
       </c>
       <c r="B1480" s="5" t="s">
         <v>2774</v>
@@ -50274,7 +50275,7 @@
     </row>
     <row r="1481" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1481" s="8" t="s">
-        <v>3076</v>
+        <v>3075</v>
       </c>
       <c r="B1481" s="5" t="s">
         <v>2774</v>
@@ -50301,7 +50302,7 @@
     </row>
     <row r="1482" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1482" s="8" t="s">
-        <v>3076</v>
+        <v>3075</v>
       </c>
       <c r="B1482" s="5" t="s">
         <v>2774</v>
@@ -50328,7 +50329,7 @@
     </row>
     <row r="1483" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1483" s="8" t="s">
-        <v>3076</v>
+        <v>3075</v>
       </c>
       <c r="B1483" s="5" t="s">
         <v>2774</v>
@@ -50355,7 +50356,7 @@
     </row>
     <row r="1484" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1484" s="8" t="s">
-        <v>3076</v>
+        <v>3075</v>
       </c>
       <c r="B1484" s="5" t="s">
         <v>2774</v>
@@ -50377,12 +50378,12 @@
       </c>
       <c r="H1484" s="12"/>
       <c r="I1484" s="12" t="s">
-        <v>3077</v>
+        <v>3076</v>
       </c>
     </row>
     <row r="1485" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1485" s="8" t="s">
-        <v>3076</v>
+        <v>3075</v>
       </c>
       <c r="B1485" s="5" t="s">
         <v>2774</v>
@@ -50409,7 +50410,7 @@
     </row>
     <row r="1486" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1486" s="8" t="s">
-        <v>3076</v>
+        <v>3075</v>
       </c>
       <c r="B1486" s="5" t="s">
         <v>2774</v>
@@ -50436,7 +50437,7 @@
     </row>
     <row r="1487" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1487" s="8" t="s">
-        <v>3076</v>
+        <v>3075</v>
       </c>
       <c r="B1487" s="5" t="s">
         <v>2774</v>
@@ -50463,7 +50464,7 @@
     </row>
     <row r="1488" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1488" s="8" t="s">
-        <v>3076</v>
+        <v>3075</v>
       </c>
       <c r="B1488" s="5" t="s">
         <v>2774</v>
@@ -50490,7 +50491,7 @@
     </row>
     <row r="1489" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1489" s="8" t="s">
-        <v>3076</v>
+        <v>3075</v>
       </c>
       <c r="B1489" s="5" t="s">
         <v>2774</v>
@@ -50517,7 +50518,7 @@
     </row>
     <row r="1490" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1490" s="8" t="s">
-        <v>3076</v>
+        <v>3075</v>
       </c>
       <c r="B1490" s="5" t="s">
         <v>2774</v>
@@ -50532,7 +50533,7 @@
         <v>2775</v>
       </c>
       <c r="F1490" s="3" t="s">
-        <v>3078</v>
+        <v>3077</v>
       </c>
       <c r="G1490" s="3">
         <v>3</v>
@@ -50544,7 +50545,7 @@
     </row>
     <row r="1491" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1491" s="8" t="s">
-        <v>3076</v>
+        <v>3075</v>
       </c>
       <c r="B1491" s="5" t="s">
         <v>2774</v>
@@ -50571,7 +50572,7 @@
     </row>
     <row r="1492" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1492" s="8" t="s">
-        <v>3076</v>
+        <v>3075</v>
       </c>
       <c r="B1492" s="5" t="s">
         <v>2774</v>
@@ -50598,7 +50599,7 @@
     </row>
     <row r="1493" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1493" s="8" t="s">
-        <v>3076</v>
+        <v>3075</v>
       </c>
       <c r="B1493" s="5" t="s">
         <v>2774</v>
@@ -50613,19 +50614,19 @@
         <v>2779</v>
       </c>
       <c r="F1493" s="3" t="s">
-        <v>3079</v>
+        <v>3078</v>
       </c>
       <c r="G1493" s="3">
         <v>3</v>
       </c>
       <c r="H1493" s="12"/>
       <c r="I1493" s="12" t="s">
-        <v>3080</v>
+        <v>3079</v>
       </c>
     </row>
     <row r="1494" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1494" s="8" t="s">
-        <v>3076</v>
+        <v>3075</v>
       </c>
       <c r="B1494" s="5" t="s">
         <v>2774</v>
@@ -50652,7 +50653,7 @@
     </row>
     <row r="1495" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1495" s="8" t="s">
-        <v>3076</v>
+        <v>3075</v>
       </c>
       <c r="B1495" s="5" t="s">
         <v>2774</v>
@@ -50679,7 +50680,7 @@
     </row>
     <row r="1496" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1496" s="8" t="s">
-        <v>3076</v>
+        <v>3075</v>
       </c>
       <c r="B1496" s="5" t="s">
         <v>2774</v>
@@ -50706,7 +50707,7 @@
     </row>
     <row r="1497" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1497" s="8" t="s">
-        <v>3076</v>
+        <v>3075</v>
       </c>
       <c r="B1497" s="5" t="s">
         <v>2774</v>
@@ -50721,7 +50722,7 @@
         <v>2779</v>
       </c>
       <c r="F1497" s="3" t="s">
-        <v>3081</v>
+        <v>3080</v>
       </c>
       <c r="G1497" s="3">
         <v>3</v>
@@ -50733,7 +50734,7 @@
     </row>
     <row r="1498" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1498" s="8" t="s">
-        <v>3076</v>
+        <v>3075</v>
       </c>
       <c r="B1498" s="5" t="s">
         <v>2774</v>
@@ -50760,7 +50761,7 @@
     </row>
     <row r="1499" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1499" s="8" t="s">
-        <v>3076</v>
+        <v>3075</v>
       </c>
       <c r="B1499" s="5" t="s">
         <v>2774</v>
@@ -50775,7 +50776,7 @@
         <v>2775</v>
       </c>
       <c r="F1499" s="3" t="s">
-        <v>3082</v>
+        <v>3081</v>
       </c>
       <c r="G1499" s="3">
         <v>3</v>
@@ -50785,7 +50786,7 @@
     </row>
     <row r="1500" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1500" s="8" t="s">
-        <v>3076</v>
+        <v>3075</v>
       </c>
       <c r="B1500" s="5" t="s">
         <v>2774</v>
@@ -50812,7 +50813,7 @@
     </row>
     <row r="1501" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1501" s="8" t="s">
-        <v>3076</v>
+        <v>3075</v>
       </c>
       <c r="B1501" s="5" t="s">
         <v>2774</v>
@@ -50839,7 +50840,7 @@
     </row>
     <row r="1502" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1502" s="8" t="s">
-        <v>3076</v>
+        <v>3075</v>
       </c>
       <c r="B1502" s="5" t="s">
         <v>2774</v>
@@ -50854,19 +50855,19 @@
         <v>2775</v>
       </c>
       <c r="F1502" s="3" t="s">
-        <v>3083</v>
+        <v>3082</v>
       </c>
       <c r="G1502" s="3">
         <v>3</v>
       </c>
       <c r="H1502" s="12"/>
       <c r="I1502" s="12" t="s">
-        <v>3080</v>
+        <v>3079</v>
       </c>
     </row>
     <row r="1503" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1503" s="8" t="s">
-        <v>3076</v>
+        <v>3075</v>
       </c>
       <c r="B1503" s="5" t="s">
         <v>2774</v>
@@ -50881,7 +50882,7 @@
         <v>2775</v>
       </c>
       <c r="F1503" s="3" t="s">
-        <v>3084</v>
+        <v>3083</v>
       </c>
       <c r="G1503" s="3">
         <v>3</v>
@@ -50893,7 +50894,7 @@
     </row>
     <row r="1504" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1504" s="8" t="s">
-        <v>3076</v>
+        <v>3075</v>
       </c>
       <c r="B1504" s="5" t="s">
         <v>2774</v>
@@ -50920,7 +50921,7 @@
     </row>
     <row r="1505" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1505" s="8" t="s">
-        <v>3076</v>
+        <v>3075</v>
       </c>
       <c r="B1505" s="5" t="s">
         <v>2774</v>
@@ -50935,7 +50936,7 @@
         <v>2775</v>
       </c>
       <c r="F1505" s="3" t="s">
-        <v>3085</v>
+        <v>3084</v>
       </c>
       <c r="G1505" s="3">
         <v>3</v>
@@ -50947,7 +50948,7 @@
     </row>
     <row r="1506" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1506" s="8" t="s">
-        <v>3076</v>
+        <v>3075</v>
       </c>
       <c r="B1506" s="5" t="s">
         <v>2774</v>
@@ -50969,12 +50970,12 @@
       </c>
       <c r="H1506" s="12"/>
       <c r="I1506" s="12" t="s">
-        <v>3236</v>
+        <v>3235</v>
       </c>
     </row>
     <row r="1507" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1507" s="8" t="s">
-        <v>3076</v>
+        <v>3075</v>
       </c>
       <c r="B1507" s="5" t="s">
         <v>2774</v>
@@ -51001,7 +51002,7 @@
     </row>
     <row r="1508" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1508" s="8" t="s">
-        <v>3076</v>
+        <v>3075</v>
       </c>
       <c r="B1508" s="5" t="s">
         <v>2774</v>
@@ -51016,19 +51017,19 @@
         <v>2779</v>
       </c>
       <c r="F1508" s="3" t="s">
-        <v>3086</v>
+        <v>3085</v>
       </c>
       <c r="G1508" s="3">
         <v>3</v>
       </c>
       <c r="H1508" s="12"/>
       <c r="I1508" s="12" t="s">
-        <v>3087</v>
+        <v>3086</v>
       </c>
     </row>
     <row r="1509" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1509" s="8" t="s">
-        <v>3076</v>
+        <v>3075</v>
       </c>
       <c r="B1509" s="5" t="s">
         <v>2774</v>
@@ -51055,7 +51056,7 @@
     </row>
     <row r="1510" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1510" s="8" t="s">
-        <v>3076</v>
+        <v>3075</v>
       </c>
       <c r="B1510" s="5" t="s">
         <v>2774</v>
@@ -51070,19 +51071,19 @@
         <v>2775</v>
       </c>
       <c r="F1510" s="3" t="s">
-        <v>3088</v>
+        <v>3087</v>
       </c>
       <c r="G1510" s="3">
         <v>3</v>
       </c>
       <c r="H1510" s="12"/>
       <c r="I1510" s="12" t="s">
-        <v>3089</v>
+        <v>3088</v>
       </c>
     </row>
     <row r="1511" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1511" s="8" t="s">
-        <v>3076</v>
+        <v>3075</v>
       </c>
       <c r="B1511" s="5" t="s">
         <v>2774</v>
@@ -51109,7 +51110,7 @@
     </row>
     <row r="1512" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1512" s="8" t="s">
-        <v>3076</v>
+        <v>3075</v>
       </c>
       <c r="B1512" s="5" t="s">
         <v>2774</v>
@@ -51136,7 +51137,7 @@
     </row>
     <row r="1513" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1513" s="8" t="s">
-        <v>3076</v>
+        <v>3075</v>
       </c>
       <c r="B1513" s="5" t="s">
         <v>2774</v>
@@ -51151,19 +51152,19 @@
         <v>2775</v>
       </c>
       <c r="F1513" s="3" t="s">
-        <v>3090</v>
+        <v>3089</v>
       </c>
       <c r="G1513" s="3">
         <v>3</v>
       </c>
       <c r="H1513" s="12"/>
       <c r="I1513" s="12" t="s">
-        <v>3091</v>
+        <v>3090</v>
       </c>
     </row>
     <row r="1514" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1514" s="8" t="s">
-        <v>3092</v>
+        <v>3091</v>
       </c>
       <c r="B1514" s="5" t="s">
         <v>2774</v>
@@ -51185,12 +51186,12 @@
       </c>
       <c r="H1514" s="12"/>
       <c r="I1514" s="12" t="s">
-        <v>3093</v>
+        <v>3092</v>
       </c>
     </row>
     <row r="1515" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1515" s="8" t="s">
-        <v>3092</v>
+        <v>3091</v>
       </c>
       <c r="B1515" s="5" t="s">
         <v>2774</v>
@@ -51217,7 +51218,7 @@
     </row>
     <row r="1516" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1516" s="8" t="s">
-        <v>3092</v>
+        <v>3091</v>
       </c>
       <c r="B1516" s="5" t="s">
         <v>2774</v>
@@ -51239,12 +51240,12 @@
       </c>
       <c r="H1516" s="12"/>
       <c r="I1516" s="12" t="s">
-        <v>3094</v>
+        <v>3093</v>
       </c>
     </row>
     <row r="1517" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1517" s="8" t="s">
-        <v>3092</v>
+        <v>3091</v>
       </c>
       <c r="B1517" s="5" t="s">
         <v>2774</v>
@@ -51271,7 +51272,7 @@
     </row>
     <row r="1518" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1518" s="8" t="s">
-        <v>3092</v>
+        <v>3091</v>
       </c>
       <c r="B1518" s="5" t="s">
         <v>2774</v>
@@ -51293,12 +51294,12 @@
       </c>
       <c r="H1518" s="12"/>
       <c r="I1518" s="12" t="s">
-        <v>3095</v>
+        <v>3094</v>
       </c>
     </row>
     <row r="1519" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1519" s="8" t="s">
-        <v>3092</v>
+        <v>3091</v>
       </c>
       <c r="B1519" s="5" t="s">
         <v>2774</v>
@@ -51320,12 +51321,12 @@
       </c>
       <c r="H1519" s="12"/>
       <c r="I1519" s="12" t="s">
-        <v>3096</v>
+        <v>3095</v>
       </c>
     </row>
     <row r="1520" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1520" s="8" t="s">
-        <v>3092</v>
+        <v>3091</v>
       </c>
       <c r="B1520" s="5" t="s">
         <v>2774</v>
@@ -51352,7 +51353,7 @@
     </row>
     <row r="1521" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1521" s="8" t="s">
-        <v>3092</v>
+        <v>3091</v>
       </c>
       <c r="B1521" s="5" t="s">
         <v>2774</v>
@@ -51374,12 +51375,12 @@
       </c>
       <c r="H1521" s="12"/>
       <c r="I1521" s="12" t="s">
-        <v>3097</v>
+        <v>3096</v>
       </c>
     </row>
     <row r="1522" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1522" s="8" t="s">
-        <v>3092</v>
+        <v>3091</v>
       </c>
       <c r="B1522" s="5" t="s">
         <v>2774</v>
@@ -51406,7 +51407,7 @@
     </row>
     <row r="1523" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1523" s="8" t="s">
-        <v>3092</v>
+        <v>3091</v>
       </c>
       <c r="B1523" s="5" t="s">
         <v>2774</v>
@@ -51433,7 +51434,7 @@
     </row>
     <row r="1524" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1524" s="8" t="s">
-        <v>3092</v>
+        <v>3091</v>
       </c>
       <c r="B1524" s="5" t="s">
         <v>2774</v>
@@ -51460,7 +51461,7 @@
     </row>
     <row r="1525" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1525" s="8" t="s">
-        <v>3092</v>
+        <v>3091</v>
       </c>
       <c r="B1525" s="5" t="s">
         <v>2774</v>
@@ -51487,7 +51488,7 @@
     </row>
     <row r="1526" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1526" s="8" t="s">
-        <v>3092</v>
+        <v>3091</v>
       </c>
       <c r="B1526" s="5" t="s">
         <v>2774</v>
@@ -51509,12 +51510,12 @@
       </c>
       <c r="H1526" s="12"/>
       <c r="I1526" s="12" t="s">
-        <v>3098</v>
+        <v>3097</v>
       </c>
     </row>
     <row r="1527" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1527" s="8" t="s">
-        <v>3092</v>
+        <v>3091</v>
       </c>
       <c r="B1527" s="5" t="s">
         <v>2774</v>
@@ -51541,7 +51542,7 @@
     </row>
     <row r="1528" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1528" s="8" t="s">
-        <v>3092</v>
+        <v>3091</v>
       </c>
       <c r="B1528" s="5" t="s">
         <v>2774</v>
@@ -51568,7 +51569,7 @@
     </row>
     <row r="1529" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1529" s="8" t="s">
-        <v>3092</v>
+        <v>3091</v>
       </c>
       <c r="B1529" s="5" t="s">
         <v>2774</v>
@@ -51590,12 +51591,12 @@
       </c>
       <c r="H1529" s="12"/>
       <c r="I1529" s="12" t="s">
-        <v>3099</v>
+        <v>3098</v>
       </c>
     </row>
     <row r="1530" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1530" s="8" t="s">
-        <v>3092</v>
+        <v>3091</v>
       </c>
       <c r="B1530" s="5" t="s">
         <v>2774</v>
@@ -51622,7 +51623,7 @@
     </row>
     <row r="1531" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1531" s="8" t="s">
-        <v>3092</v>
+        <v>3091</v>
       </c>
       <c r="B1531" s="5" t="s">
         <v>2774</v>
@@ -51644,12 +51645,12 @@
       </c>
       <c r="H1531" s="12"/>
       <c r="I1531" s="12" t="s">
-        <v>3100</v>
+        <v>3099</v>
       </c>
     </row>
     <row r="1532" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1532" s="8" t="s">
-        <v>3092</v>
+        <v>3091</v>
       </c>
       <c r="B1532" s="5" t="s">
         <v>2774</v>
@@ -51671,12 +51672,12 @@
       </c>
       <c r="H1532" s="12"/>
       <c r="I1532" s="12" t="s">
-        <v>3101</v>
+        <v>3100</v>
       </c>
     </row>
     <row r="1533" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1533" s="8" t="s">
-        <v>3092</v>
+        <v>3091</v>
       </c>
       <c r="B1533" s="5" t="s">
         <v>2774</v>
@@ -51703,7 +51704,7 @@
     </row>
     <row r="1534" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1534" s="8" t="s">
-        <v>3092</v>
+        <v>3091</v>
       </c>
       <c r="B1534" s="5" t="s">
         <v>2774</v>
@@ -51730,7 +51731,7 @@
     </row>
     <row r="1535" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1535" s="8" t="s">
-        <v>3092</v>
+        <v>3091</v>
       </c>
       <c r="B1535" s="5" t="s">
         <v>2774</v>
@@ -51757,7 +51758,7 @@
     </row>
     <row r="1536" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1536" s="8" t="s">
-        <v>3092</v>
+        <v>3091</v>
       </c>
       <c r="B1536" s="5" t="s">
         <v>2774</v>
@@ -51779,12 +51780,12 @@
       </c>
       <c r="H1536" s="12"/>
       <c r="I1536" s="12" t="s">
-        <v>3102</v>
+        <v>3101</v>
       </c>
     </row>
     <row r="1537" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1537" s="8" t="s">
-        <v>3092</v>
+        <v>3091</v>
       </c>
       <c r="B1537" s="5" t="s">
         <v>2774</v>
@@ -51806,12 +51807,12 @@
       </c>
       <c r="H1537" s="12"/>
       <c r="I1537" s="12" t="s">
-        <v>3103</v>
+        <v>3102</v>
       </c>
     </row>
     <row r="1538" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1538" s="8" t="s">
-        <v>3092</v>
+        <v>3091</v>
       </c>
       <c r="B1538" s="5" t="s">
         <v>2774</v>
@@ -51838,7 +51839,7 @@
     </row>
     <row r="1539" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1539" s="8" t="s">
-        <v>3092</v>
+        <v>3091</v>
       </c>
       <c r="B1539" s="5" t="s">
         <v>2774</v>
@@ -51865,7 +51866,7 @@
     </row>
     <row r="1540" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1540" s="8" t="s">
-        <v>3092</v>
+        <v>3091</v>
       </c>
       <c r="B1540" s="5" t="s">
         <v>2774</v>
@@ -51887,12 +51888,12 @@
       </c>
       <c r="H1540" s="12"/>
       <c r="I1540" s="12" t="s">
-        <v>3097</v>
+        <v>3096</v>
       </c>
     </row>
     <row r="1541" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1541" s="8" t="s">
-        <v>3092</v>
+        <v>3091</v>
       </c>
       <c r="B1541" s="5" t="s">
         <v>2774</v>
@@ -51914,12 +51915,12 @@
       </c>
       <c r="H1541" s="12"/>
       <c r="I1541" s="12" t="s">
-        <v>3104</v>
+        <v>3103</v>
       </c>
     </row>
     <row r="1542" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1542" s="8" t="s">
-        <v>3092</v>
+        <v>3091</v>
       </c>
       <c r="B1542" s="5" t="s">
         <v>2774</v>
@@ -51946,7 +51947,7 @@
     </row>
     <row r="1543" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1543" s="8" t="s">
-        <v>3092</v>
+        <v>3091</v>
       </c>
       <c r="B1543" s="5" t="s">
         <v>2774</v>
@@ -51961,19 +51962,19 @@
         <v>2775</v>
       </c>
       <c r="F1543" s="3" t="s">
-        <v>3105</v>
+        <v>3104</v>
       </c>
       <c r="G1543" s="3">
         <v>3</v>
       </c>
       <c r="H1543" s="12"/>
       <c r="I1543" s="12" t="s">
-        <v>3106</v>
+        <v>3105</v>
       </c>
     </row>
     <row r="1544" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1544" s="8" t="s">
-        <v>3092</v>
+        <v>3091</v>
       </c>
       <c r="B1544" s="5" t="s">
         <v>2774</v>
@@ -51995,12 +51996,12 @@
       </c>
       <c r="H1544" s="12"/>
       <c r="I1544" s="12" t="s">
-        <v>3107</v>
+        <v>3106</v>
       </c>
     </row>
     <row r="1545" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1545" s="8" t="s">
-        <v>3092</v>
+        <v>3091</v>
       </c>
       <c r="B1545" s="5" t="s">
         <v>2774</v>
@@ -52022,12 +52023,12 @@
       </c>
       <c r="H1545" s="12"/>
       <c r="I1545" s="12" t="s">
-        <v>3108</v>
+        <v>3107</v>
       </c>
     </row>
     <row r="1546" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1546" s="8" t="s">
-        <v>3092</v>
+        <v>3091</v>
       </c>
       <c r="B1546" s="5" t="s">
         <v>2774</v>
@@ -52049,12 +52050,12 @@
       </c>
       <c r="H1546" s="12"/>
       <c r="I1546" s="12" t="s">
-        <v>3109</v>
+        <v>3108</v>
       </c>
     </row>
     <row r="1547" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1547" s="8" t="s">
-        <v>3092</v>
+        <v>3091</v>
       </c>
       <c r="B1547" s="5" t="s">
         <v>2774</v>
@@ -52076,12 +52077,12 @@
       </c>
       <c r="H1547" s="12"/>
       <c r="I1547" s="12" t="s">
-        <v>3110</v>
+        <v>3109</v>
       </c>
     </row>
     <row r="1548" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1548" s="8" t="s">
-        <v>3111</v>
+        <v>3110</v>
       </c>
       <c r="B1548" s="5" t="s">
         <v>2774</v>
@@ -52108,7 +52109,7 @@
     </row>
     <row r="1549" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1549" s="8" t="s">
-        <v>3111</v>
+        <v>3110</v>
       </c>
       <c r="B1549" s="5" t="s">
         <v>2774</v>
@@ -52130,12 +52131,12 @@
       </c>
       <c r="H1549" s="12"/>
       <c r="I1549" s="12" t="s">
-        <v>3112</v>
+        <v>3111</v>
       </c>
     </row>
     <row r="1550" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1550" s="8" t="s">
-        <v>3111</v>
+        <v>3110</v>
       </c>
       <c r="B1550" s="5" t="s">
         <v>2774</v>
@@ -52162,7 +52163,7 @@
     </row>
     <row r="1551" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1551" s="8" t="s">
-        <v>3111</v>
+        <v>3110</v>
       </c>
       <c r="B1551" s="5" t="s">
         <v>2774</v>
@@ -52189,7 +52190,7 @@
     </row>
     <row r="1552" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1552" s="8" t="s">
-        <v>3111</v>
+        <v>3110</v>
       </c>
       <c r="B1552" s="5" t="s">
         <v>2774</v>
@@ -52216,7 +52217,7 @@
     </row>
     <row r="1553" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1553" s="8" t="s">
-        <v>3111</v>
+        <v>3110</v>
       </c>
       <c r="B1553" s="5" t="s">
         <v>2774</v>
@@ -52238,12 +52239,12 @@
       </c>
       <c r="H1553" s="12"/>
       <c r="I1553" s="12" t="s">
-        <v>3113</v>
+        <v>3112</v>
       </c>
     </row>
     <row r="1554" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1554" s="8" t="s">
-        <v>3111</v>
+        <v>3110</v>
       </c>
       <c r="B1554" s="5" t="s">
         <v>2774</v>
@@ -52270,7 +52271,7 @@
     </row>
     <row r="1555" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1555" s="8" t="s">
-        <v>3111</v>
+        <v>3110</v>
       </c>
       <c r="B1555" s="5" t="s">
         <v>2774</v>
@@ -52297,7 +52298,7 @@
     </row>
     <row r="1556" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1556" s="8" t="s">
-        <v>3111</v>
+        <v>3110</v>
       </c>
       <c r="B1556" s="5" t="s">
         <v>2774</v>
@@ -52324,7 +52325,7 @@
     </row>
     <row r="1557" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1557" s="8" t="s">
-        <v>3111</v>
+        <v>3110</v>
       </c>
       <c r="B1557" s="5" t="s">
         <v>2774</v>
@@ -52351,7 +52352,7 @@
     </row>
     <row r="1558" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1558" s="8" t="s">
-        <v>3111</v>
+        <v>3110</v>
       </c>
       <c r="B1558" s="5" t="s">
         <v>2774</v>
@@ -52378,7 +52379,7 @@
     </row>
     <row r="1559" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1559" s="8" t="s">
-        <v>3111</v>
+        <v>3110</v>
       </c>
       <c r="B1559" s="5" t="s">
         <v>2774</v>
@@ -52405,7 +52406,7 @@
     </row>
     <row r="1560" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1560" s="8" t="s">
-        <v>3111</v>
+        <v>3110</v>
       </c>
       <c r="B1560" s="5" t="s">
         <v>2774</v>
@@ -52432,7 +52433,7 @@
     </row>
     <row r="1561" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1561" s="8" t="s">
-        <v>3111</v>
+        <v>3110</v>
       </c>
       <c r="B1561" s="5" t="s">
         <v>2774</v>
@@ -52459,7 +52460,7 @@
     </row>
     <row r="1562" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1562" s="8" t="s">
-        <v>3111</v>
+        <v>3110</v>
       </c>
       <c r="B1562" s="5" t="s">
         <v>2774</v>
@@ -52486,7 +52487,7 @@
     </row>
     <row r="1563" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1563" s="8" t="s">
-        <v>3111</v>
+        <v>3110</v>
       </c>
       <c r="B1563" s="5" t="s">
         <v>2774</v>
@@ -52513,7 +52514,7 @@
     </row>
     <row r="1564" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1564" s="8" t="s">
-        <v>3111</v>
+        <v>3110</v>
       </c>
       <c r="B1564" s="5" t="s">
         <v>2774</v>
@@ -52540,7 +52541,7 @@
     </row>
     <row r="1565" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1565" s="8" t="s">
-        <v>3111</v>
+        <v>3110</v>
       </c>
       <c r="B1565" s="5" t="s">
         <v>2774</v>
@@ -52567,7 +52568,7 @@
     </row>
     <row r="1566" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1566" s="8" t="s">
-        <v>3111</v>
+        <v>3110</v>
       </c>
       <c r="B1566" s="5" t="s">
         <v>2774</v>
@@ -52594,7 +52595,7 @@
     </row>
     <row r="1567" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1567" s="8" t="s">
-        <v>3111</v>
+        <v>3110</v>
       </c>
       <c r="B1567" s="5" t="s">
         <v>2774</v>
@@ -52621,7 +52622,7 @@
     </row>
     <row r="1568" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1568" s="8" t="s">
-        <v>3111</v>
+        <v>3110</v>
       </c>
       <c r="B1568" s="5" t="s">
         <v>2774</v>
@@ -52648,7 +52649,7 @@
     </row>
     <row r="1569" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1569" s="8" t="s">
-        <v>3111</v>
+        <v>3110</v>
       </c>
       <c r="B1569" s="5" t="s">
         <v>2774</v>
@@ -52675,7 +52676,7 @@
     </row>
     <row r="1570" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1570" s="8" t="s">
-        <v>3111</v>
+        <v>3110</v>
       </c>
       <c r="B1570" s="5" t="s">
         <v>2774</v>
@@ -52702,7 +52703,7 @@
     </row>
     <row r="1571" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1571" s="8" t="s">
-        <v>3111</v>
+        <v>3110</v>
       </c>
       <c r="B1571" s="5" t="s">
         <v>2774</v>
@@ -52729,7 +52730,7 @@
     </row>
     <row r="1572" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1572" s="8" t="s">
-        <v>3111</v>
+        <v>3110</v>
       </c>
       <c r="B1572" s="5" t="s">
         <v>2774</v>
@@ -52756,7 +52757,7 @@
     </row>
     <row r="1573" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1573" s="8" t="s">
-        <v>3111</v>
+        <v>3110</v>
       </c>
       <c r="B1573" s="5" t="s">
         <v>2774</v>
@@ -52783,7 +52784,7 @@
     </row>
     <row r="1574" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1574" s="8" t="s">
-        <v>3111</v>
+        <v>3110</v>
       </c>
       <c r="B1574" s="5" t="s">
         <v>2774</v>
@@ -52805,12 +52806,12 @@
       </c>
       <c r="H1574" s="12"/>
       <c r="I1574" s="12" t="s">
-        <v>3114</v>
+        <v>3113</v>
       </c>
     </row>
     <row r="1575" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1575" s="8" t="s">
-        <v>3111</v>
+        <v>3110</v>
       </c>
       <c r="B1575" s="5" t="s">
         <v>2774</v>
@@ -52837,7 +52838,7 @@
     </row>
     <row r="1576" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1576" s="8" t="s">
-        <v>3111</v>
+        <v>3110</v>
       </c>
       <c r="B1576" s="5" t="s">
         <v>2774</v>
@@ -52864,7 +52865,7 @@
     </row>
     <row r="1577" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1577" s="8" t="s">
-        <v>3111</v>
+        <v>3110</v>
       </c>
       <c r="B1577" s="5" t="s">
         <v>2774</v>
@@ -52891,7 +52892,7 @@
     </row>
     <row r="1578" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1578" s="8" t="s">
-        <v>3111</v>
+        <v>3110</v>
       </c>
       <c r="B1578" s="5" t="s">
         <v>2774</v>
@@ -52913,12 +52914,12 @@
       </c>
       <c r="H1578" s="12"/>
       <c r="I1578" s="12" t="s">
-        <v>3115</v>
+        <v>3114</v>
       </c>
     </row>
     <row r="1579" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1579" s="8" t="s">
-        <v>3111</v>
+        <v>3110</v>
       </c>
       <c r="B1579" s="5" t="s">
         <v>2774</v>
@@ -52940,12 +52941,12 @@
       </c>
       <c r="H1579" s="12"/>
       <c r="I1579" s="12" t="s">
-        <v>3115</v>
+        <v>3114</v>
       </c>
     </row>
     <row r="1580" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1580" s="8" t="s">
-        <v>3111</v>
+        <v>3110</v>
       </c>
       <c r="B1580" s="5" t="s">
         <v>2774</v>
@@ -52967,12 +52968,12 @@
       </c>
       <c r="H1580" s="12"/>
       <c r="I1580" s="12" t="s">
-        <v>3115</v>
+        <v>3114</v>
       </c>
     </row>
     <row r="1581" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1581" s="8" t="s">
-        <v>3111</v>
+        <v>3110</v>
       </c>
       <c r="B1581" s="5" t="s">
         <v>2774</v>
@@ -52999,7 +53000,7 @@
     </row>
     <row r="1582" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1582" s="8" t="s">
-        <v>3111</v>
+        <v>3110</v>
       </c>
       <c r="B1582" s="5" t="s">
         <v>2774</v>
@@ -53026,7 +53027,7 @@
     </row>
     <row r="1583" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1583" s="8" t="s">
-        <v>3111</v>
+        <v>3110</v>
       </c>
       <c r="B1583" s="5" t="s">
         <v>2774</v>
@@ -53053,7 +53054,7 @@
     </row>
     <row r="1584" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1584" s="8" t="s">
-        <v>3111</v>
+        <v>3110</v>
       </c>
       <c r="B1584" s="5" t="s">
         <v>2774</v>
@@ -53080,7 +53081,7 @@
     </row>
     <row r="1585" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1585" s="8" t="s">
-        <v>3111</v>
+        <v>3110</v>
       </c>
       <c r="B1585" s="5" t="s">
         <v>2774</v>
@@ -53107,7 +53108,7 @@
     </row>
     <row r="1586" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1586" s="8" t="s">
-        <v>3111</v>
+        <v>3110</v>
       </c>
       <c r="B1586" s="5" t="s">
         <v>2774</v>
@@ -53129,12 +53130,12 @@
       </c>
       <c r="H1586" s="12"/>
       <c r="I1586" s="12" t="s">
-        <v>3116</v>
+        <v>3115</v>
       </c>
     </row>
     <row r="1587" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1587" s="8" t="s">
-        <v>3117</v>
+        <v>3116</v>
       </c>
       <c r="B1587" s="5" t="s">
         <v>2774</v>
@@ -53161,7 +53162,7 @@
     </row>
     <row r="1588" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1588" s="8" t="s">
-        <v>3117</v>
+        <v>3116</v>
       </c>
       <c r="B1588" s="5" t="s">
         <v>2774</v>
@@ -53188,7 +53189,7 @@
     </row>
     <row r="1589" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1589" s="8" t="s">
-        <v>3117</v>
+        <v>3116</v>
       </c>
       <c r="B1589" s="5" t="s">
         <v>2774</v>
@@ -53210,12 +53211,12 @@
       </c>
       <c r="H1589" s="12"/>
       <c r="I1589" s="12" t="s">
-        <v>3118</v>
+        <v>3117</v>
       </c>
     </row>
     <row r="1590" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1590" s="8" t="s">
-        <v>3117</v>
+        <v>3116</v>
       </c>
       <c r="B1590" s="5" t="s">
         <v>2774</v>
@@ -53242,7 +53243,7 @@
     </row>
     <row r="1591" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1591" s="8" t="s">
-        <v>3117</v>
+        <v>3116</v>
       </c>
       <c r="B1591" s="5" t="s">
         <v>2774</v>
@@ -53257,19 +53258,19 @@
         <v>2775</v>
       </c>
       <c r="F1591" s="3" t="s">
-        <v>3119</v>
+        <v>3118</v>
       </c>
       <c r="G1591" s="3">
         <v>3</v>
       </c>
       <c r="H1591" s="12"/>
       <c r="I1591" s="12" t="s">
-        <v>3120</v>
+        <v>3119</v>
       </c>
     </row>
     <row r="1592" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1592" s="8" t="s">
-        <v>3117</v>
+        <v>3116</v>
       </c>
       <c r="B1592" s="5" t="s">
         <v>2774</v>
@@ -53291,12 +53292,12 @@
       </c>
       <c r="H1592" s="12"/>
       <c r="I1592" s="12" t="s">
-        <v>3121</v>
+        <v>3120</v>
       </c>
     </row>
     <row r="1593" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1593" s="8" t="s">
-        <v>3117</v>
+        <v>3116</v>
       </c>
       <c r="B1593" s="5" t="s">
         <v>2774</v>
@@ -53318,12 +53319,12 @@
       </c>
       <c r="H1593" s="12"/>
       <c r="I1593" s="12" t="s">
-        <v>3122</v>
+        <v>3121</v>
       </c>
     </row>
     <row r="1594" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1594" s="8" t="s">
-        <v>3117</v>
+        <v>3116</v>
       </c>
       <c r="B1594" s="5" t="s">
         <v>2774</v>
@@ -53350,7 +53351,7 @@
     </row>
     <row r="1595" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1595" s="8" t="s">
-        <v>3117</v>
+        <v>3116</v>
       </c>
       <c r="B1595" s="5" t="s">
         <v>2774</v>
@@ -53377,7 +53378,7 @@
     </row>
     <row r="1596" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1596" s="8" t="s">
-        <v>3117</v>
+        <v>3116</v>
       </c>
       <c r="B1596" s="5" t="s">
         <v>2774</v>
@@ -53404,7 +53405,7 @@
     </row>
     <row r="1597" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1597" s="8" t="s">
-        <v>3117</v>
+        <v>3116</v>
       </c>
       <c r="B1597" s="5" t="s">
         <v>2774</v>
@@ -53431,7 +53432,7 @@
     </row>
     <row r="1598" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1598" s="8" t="s">
-        <v>3117</v>
+        <v>3116</v>
       </c>
       <c r="B1598" s="5" t="s">
         <v>2774</v>
@@ -53458,7 +53459,7 @@
     </row>
     <row r="1599" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1599" s="8" t="s">
-        <v>3117</v>
+        <v>3116</v>
       </c>
       <c r="B1599" s="5" t="s">
         <v>2774</v>
@@ -53485,7 +53486,7 @@
     </row>
     <row r="1600" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1600" s="8" t="s">
-        <v>3117</v>
+        <v>3116</v>
       </c>
       <c r="B1600" s="5" t="s">
         <v>2774</v>
@@ -53512,7 +53513,7 @@
     </row>
     <row r="1601" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1601" s="8" t="s">
-        <v>3117</v>
+        <v>3116</v>
       </c>
       <c r="B1601" s="5" t="s">
         <v>2774</v>
@@ -53527,7 +53528,7 @@
         <v>2775</v>
       </c>
       <c r="F1601" s="3" t="s">
-        <v>3123</v>
+        <v>3122</v>
       </c>
       <c r="G1601" s="3">
         <v>3</v>
@@ -53539,7 +53540,7 @@
     </row>
     <row r="1602" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1602" s="8" t="s">
-        <v>3117</v>
+        <v>3116</v>
       </c>
       <c r="B1602" s="5" t="s">
         <v>2774</v>
@@ -53566,7 +53567,7 @@
     </row>
     <row r="1603" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1603" s="8" t="s">
-        <v>3117</v>
+        <v>3116</v>
       </c>
       <c r="B1603" s="5" t="s">
         <v>2774</v>
@@ -53588,12 +53589,12 @@
       </c>
       <c r="H1603" s="12"/>
       <c r="I1603" s="12" t="s">
-        <v>3124</v>
+        <v>3123</v>
       </c>
     </row>
     <row r="1604" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1604" s="8" t="s">
-        <v>3117</v>
+        <v>3116</v>
       </c>
       <c r="B1604" s="5" t="s">
         <v>2774</v>
@@ -53615,12 +53616,12 @@
       </c>
       <c r="H1604" s="12"/>
       <c r="I1604" s="12" t="s">
-        <v>3125</v>
+        <v>3124</v>
       </c>
     </row>
     <row r="1605" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1605" s="8" t="s">
-        <v>3117</v>
+        <v>3116</v>
       </c>
       <c r="B1605" s="5" t="s">
         <v>2774</v>
@@ -53647,7 +53648,7 @@
     </row>
     <row r="1606" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1606" s="8" t="s">
-        <v>3117</v>
+        <v>3116</v>
       </c>
       <c r="B1606" s="5" t="s">
         <v>2774</v>
@@ -53669,12 +53670,12 @@
       </c>
       <c r="H1606" s="12"/>
       <c r="I1606" s="12" t="s">
-        <v>3126</v>
+        <v>3125</v>
       </c>
     </row>
     <row r="1607" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1607" s="8" t="s">
-        <v>3117</v>
+        <v>3116</v>
       </c>
       <c r="B1607" s="5" t="s">
         <v>2774</v>
@@ -53696,12 +53697,12 @@
       </c>
       <c r="H1607" s="12"/>
       <c r="I1607" s="12" t="s">
-        <v>3127</v>
+        <v>3126</v>
       </c>
     </row>
     <row r="1608" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1608" s="8" t="s">
-        <v>3117</v>
+        <v>3116</v>
       </c>
       <c r="B1608" s="5" t="s">
         <v>2774</v>
@@ -53723,12 +53724,12 @@
       </c>
       <c r="H1608" s="12"/>
       <c r="I1608" s="12" t="s">
-        <v>3128</v>
+        <v>3127</v>
       </c>
     </row>
     <row r="1609" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1609" s="8" t="s">
-        <v>3117</v>
+        <v>3116</v>
       </c>
       <c r="B1609" s="5" t="s">
         <v>2774</v>
@@ -53755,7 +53756,7 @@
     </row>
     <row r="1610" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1610" s="8" t="s">
-        <v>3117</v>
+        <v>3116</v>
       </c>
       <c r="B1610" s="5" t="s">
         <v>2774</v>
@@ -53782,7 +53783,7 @@
     </row>
     <row r="1611" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1611" s="8" t="s">
-        <v>3117</v>
+        <v>3116</v>
       </c>
       <c r="B1611" s="5" t="s">
         <v>2774</v>
@@ -53809,7 +53810,7 @@
     </row>
     <row r="1612" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1612" s="8" t="s">
-        <v>3117</v>
+        <v>3116</v>
       </c>
       <c r="B1612" s="5" t="s">
         <v>2774</v>
@@ -53831,12 +53832,12 @@
       </c>
       <c r="H1612" s="12"/>
       <c r="I1612" s="12" t="s">
-        <v>3129</v>
+        <v>3128</v>
       </c>
     </row>
     <row r="1613" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1613" s="8" t="s">
-        <v>3117</v>
+        <v>3116</v>
       </c>
       <c r="B1613" s="5" t="s">
         <v>2774</v>
@@ -53858,12 +53859,12 @@
       </c>
       <c r="H1613" s="12"/>
       <c r="I1613" s="12" t="s">
-        <v>3130</v>
+        <v>3129</v>
       </c>
     </row>
     <row r="1614" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1614" s="8" t="s">
-        <v>3117</v>
+        <v>3116</v>
       </c>
       <c r="B1614" s="5" t="s">
         <v>2774</v>
@@ -53885,12 +53886,12 @@
       </c>
       <c r="H1614" s="12"/>
       <c r="I1614" s="12" t="s">
-        <v>3131</v>
+        <v>3130</v>
       </c>
     </row>
     <row r="1615" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1615" s="8" t="s">
-        <v>3117</v>
+        <v>3116</v>
       </c>
       <c r="B1615" s="5" t="s">
         <v>2774</v>
@@ -53905,19 +53906,19 @@
         <v>2775</v>
       </c>
       <c r="F1615" s="3" t="s">
-        <v>3132</v>
+        <v>3131</v>
       </c>
       <c r="G1615" s="3">
         <v>3</v>
       </c>
       <c r="H1615" s="12"/>
       <c r="I1615" s="12" t="s">
-        <v>3133</v>
+        <v>3132</v>
       </c>
     </row>
     <row r="1616" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1616" s="8" t="s">
-        <v>3117</v>
+        <v>3116</v>
       </c>
       <c r="B1616" s="5" t="s">
         <v>2774</v>
@@ -53939,12 +53940,12 @@
       </c>
       <c r="H1616" s="12"/>
       <c r="I1616" s="12" t="s">
-        <v>3134</v>
+        <v>3133</v>
       </c>
     </row>
     <row r="1617" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1617" s="8" t="s">
-        <v>3117</v>
+        <v>3116</v>
       </c>
       <c r="B1617" s="5" t="s">
         <v>2774</v>
@@ -53971,7 +53972,7 @@
     </row>
     <row r="1618" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1618" s="8" t="s">
-        <v>3117</v>
+        <v>3116</v>
       </c>
       <c r="B1618" s="5" t="s">
         <v>2774</v>
@@ -53993,12 +53994,12 @@
       </c>
       <c r="H1618" s="12"/>
       <c r="I1618" s="12" t="s">
-        <v>3135</v>
+        <v>3134</v>
       </c>
     </row>
     <row r="1619" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1619" s="8" t="s">
-        <v>3117</v>
+        <v>3116</v>
       </c>
       <c r="B1619" s="5" t="s">
         <v>2774</v>
@@ -54025,7 +54026,7 @@
     </row>
     <row r="1620" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1620" s="8" t="s">
-        <v>3117</v>
+        <v>3116</v>
       </c>
       <c r="B1620" s="5" t="s">
         <v>2774</v>
@@ -54040,19 +54041,19 @@
         <v>2775</v>
       </c>
       <c r="F1620" s="3" t="s">
-        <v>3136</v>
+        <v>3135</v>
       </c>
       <c r="G1620" s="3">
         <v>3</v>
       </c>
       <c r="H1620" s="12"/>
       <c r="I1620" s="12" t="s">
-        <v>3137</v>
+        <v>3136</v>
       </c>
     </row>
     <row r="1621" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1621" s="8" t="s">
-        <v>3117</v>
+        <v>3116</v>
       </c>
       <c r="B1621" s="5" t="s">
         <v>2774</v>
@@ -54074,12 +54075,12 @@
       </c>
       <c r="H1621" s="12"/>
       <c r="I1621" s="12" t="s">
-        <v>3138</v>
+        <v>3137</v>
       </c>
     </row>
     <row r="1622" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1622" s="8" t="s">
-        <v>3117</v>
+        <v>3116</v>
       </c>
       <c r="B1622" s="5" t="s">
         <v>2774</v>
@@ -54101,12 +54102,12 @@
       </c>
       <c r="H1622" s="12"/>
       <c r="I1622" s="12" t="s">
-        <v>3139</v>
+        <v>3138</v>
       </c>
     </row>
     <row r="1623" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1623" s="8" t="s">
-        <v>3117</v>
+        <v>3116</v>
       </c>
       <c r="B1623" s="5" t="s">
         <v>2774</v>
@@ -54128,12 +54129,12 @@
       </c>
       <c r="H1623" s="12"/>
       <c r="I1623" s="12" t="s">
-        <v>3131</v>
+        <v>3130</v>
       </c>
     </row>
     <row r="1624" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1624" s="8" t="s">
-        <v>3117</v>
+        <v>3116</v>
       </c>
       <c r="B1624" s="5" t="s">
         <v>2774</v>
@@ -54148,19 +54149,19 @@
         <v>2775</v>
       </c>
       <c r="F1624" s="3" t="s">
-        <v>3140</v>
+        <v>3139</v>
       </c>
       <c r="G1624" s="3">
         <v>3</v>
       </c>
       <c r="H1624" s="12"/>
       <c r="I1624" s="12" t="s">
-        <v>3141</v>
+        <v>3140</v>
       </c>
     </row>
     <row r="1625" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1625" s="8" t="s">
-        <v>3142</v>
+        <v>3141</v>
       </c>
       <c r="B1625" s="5" t="s">
         <v>2774</v>
@@ -54187,7 +54188,7 @@
     </row>
     <row r="1626" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1626" s="8" t="s">
-        <v>3142</v>
+        <v>3141</v>
       </c>
       <c r="B1626" s="5" t="s">
         <v>2774</v>
@@ -54214,7 +54215,7 @@
     </row>
     <row r="1627" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1627" s="8" t="s">
-        <v>3142</v>
+        <v>3141</v>
       </c>
       <c r="B1627" s="5" t="s">
         <v>2774</v>
@@ -54241,7 +54242,7 @@
     </row>
     <row r="1628" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1628" s="8" t="s">
-        <v>3142</v>
+        <v>3141</v>
       </c>
       <c r="B1628" s="5" t="s">
         <v>2774</v>
@@ -54263,12 +54264,12 @@
       </c>
       <c r="H1628" s="12"/>
       <c r="I1628" s="12" t="s">
-        <v>3143</v>
+        <v>3142</v>
       </c>
     </row>
     <row r="1629" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1629" s="8" t="s">
-        <v>3142</v>
+        <v>3141</v>
       </c>
       <c r="B1629" s="5" t="s">
         <v>2774</v>
@@ -54295,7 +54296,7 @@
     </row>
     <row r="1630" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1630" s="8" t="s">
-        <v>3142</v>
+        <v>3141</v>
       </c>
       <c r="B1630" s="5" t="s">
         <v>2774</v>
@@ -54322,7 +54323,7 @@
     </row>
     <row r="1631" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1631" s="8" t="s">
-        <v>3142</v>
+        <v>3141</v>
       </c>
       <c r="B1631" s="5" t="s">
         <v>2774</v>
@@ -54349,7 +54350,7 @@
     </row>
     <row r="1632" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1632" s="8" t="s">
-        <v>3142</v>
+        <v>3141</v>
       </c>
       <c r="B1632" s="5" t="s">
         <v>2774</v>
@@ -54371,12 +54372,12 @@
       </c>
       <c r="H1632" s="12"/>
       <c r="I1632" s="12" t="s">
-        <v>3144</v>
+        <v>3143</v>
       </c>
     </row>
     <row r="1633" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1633" s="8" t="s">
-        <v>3142</v>
+        <v>3141</v>
       </c>
       <c r="B1633" s="5" t="s">
         <v>2774</v>
@@ -54403,7 +54404,7 @@
     </row>
     <row r="1634" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1634" s="8" t="s">
-        <v>3142</v>
+        <v>3141</v>
       </c>
       <c r="B1634" s="5" t="s">
         <v>2774</v>
@@ -54430,7 +54431,7 @@
     </row>
     <row r="1635" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1635" s="8" t="s">
-        <v>3142</v>
+        <v>3141</v>
       </c>
       <c r="B1635" s="5" t="s">
         <v>2774</v>
@@ -54452,12 +54453,12 @@
       </c>
       <c r="H1635" s="12"/>
       <c r="I1635" s="12" t="s">
-        <v>3145</v>
+        <v>3144</v>
       </c>
     </row>
     <row r="1636" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1636" s="8" t="s">
-        <v>3142</v>
+        <v>3141</v>
       </c>
       <c r="B1636" s="5" t="s">
         <v>2774</v>
@@ -54484,7 +54485,7 @@
     </row>
     <row r="1637" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1637" s="8" t="s">
-        <v>3142</v>
+        <v>3141</v>
       </c>
       <c r="B1637" s="5" t="s">
         <v>2774</v>
@@ -54511,7 +54512,7 @@
     </row>
     <row r="1638" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1638" s="8" t="s">
-        <v>3142</v>
+        <v>3141</v>
       </c>
       <c r="B1638" s="5" t="s">
         <v>2774</v>
@@ -54526,7 +54527,7 @@
         <v>2775</v>
       </c>
       <c r="F1638" s="3" t="s">
-        <v>3146</v>
+        <v>3145</v>
       </c>
       <c r="G1638" s="3">
         <v>3</v>
@@ -54538,7 +54539,7 @@
     </row>
     <row r="1639" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1639" s="8" t="s">
-        <v>3142</v>
+        <v>3141</v>
       </c>
       <c r="B1639" s="5" t="s">
         <v>2774</v>
@@ -54560,12 +54561,12 @@
       </c>
       <c r="H1639" s="12"/>
       <c r="I1639" s="12" t="s">
-        <v>3147</v>
+        <v>3146</v>
       </c>
     </row>
     <row r="1640" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1640" s="8" t="s">
-        <v>3142</v>
+        <v>3141</v>
       </c>
       <c r="B1640" s="5" t="s">
         <v>2774</v>
@@ -54592,7 +54593,7 @@
     </row>
     <row r="1641" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1641" s="8" t="s">
-        <v>3142</v>
+        <v>3141</v>
       </c>
       <c r="B1641" s="5" t="s">
         <v>2774</v>
@@ -54619,7 +54620,7 @@
     </row>
     <row r="1642" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1642" s="8" t="s">
-        <v>3142</v>
+        <v>3141</v>
       </c>
       <c r="B1642" s="5" t="s">
         <v>2774</v>
@@ -54646,7 +54647,7 @@
     </row>
     <row r="1643" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1643" s="8" t="s">
-        <v>3142</v>
+        <v>3141</v>
       </c>
       <c r="B1643" s="5" t="s">
         <v>2774</v>
@@ -54661,7 +54662,7 @@
         <v>2779</v>
       </c>
       <c r="F1643" s="3" t="s">
-        <v>3148</v>
+        <v>3147</v>
       </c>
       <c r="G1643" s="3">
         <v>3</v>
@@ -54673,7 +54674,7 @@
     </row>
     <row r="1644" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1644" s="8" t="s">
-        <v>3142</v>
+        <v>3141</v>
       </c>
       <c r="B1644" s="5" t="s">
         <v>2774</v>
@@ -54700,7 +54701,7 @@
     </row>
     <row r="1645" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1645" s="8" t="s">
-        <v>3142</v>
+        <v>3141</v>
       </c>
       <c r="B1645" s="5" t="s">
         <v>2774</v>
@@ -54722,12 +54723,12 @@
       </c>
       <c r="H1645" s="12"/>
       <c r="I1645" s="12" t="s">
-        <v>3149</v>
+        <v>3148</v>
       </c>
     </row>
     <row r="1646" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1646" s="8" t="s">
-        <v>3142</v>
+        <v>3141</v>
       </c>
       <c r="B1646" s="5" t="s">
         <v>2774</v>
@@ -54754,7 +54755,7 @@
     </row>
     <row r="1647" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1647" s="8" t="s">
-        <v>3142</v>
+        <v>3141</v>
       </c>
       <c r="B1647" s="5" t="s">
         <v>2774</v>
@@ -54781,7 +54782,7 @@
     </row>
     <row r="1648" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1648" s="8" t="s">
-        <v>3142</v>
+        <v>3141</v>
       </c>
       <c r="B1648" s="5" t="s">
         <v>2774</v>
@@ -54808,7 +54809,7 @@
     </row>
     <row r="1649" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1649" s="8" t="s">
-        <v>3142</v>
+        <v>3141</v>
       </c>
       <c r="B1649" s="5" t="s">
         <v>2774</v>
@@ -54823,7 +54824,7 @@
         <v>2775</v>
       </c>
       <c r="F1649" s="3" t="s">
-        <v>3150</v>
+        <v>3149</v>
       </c>
       <c r="G1649" s="3">
         <v>3</v>
@@ -54835,7 +54836,7 @@
     </row>
     <row r="1650" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1650" s="8" t="s">
-        <v>3142</v>
+        <v>3141</v>
       </c>
       <c r="B1650" s="5" t="s">
         <v>2774</v>
@@ -54862,7 +54863,7 @@
     </row>
     <row r="1651" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1651" s="8" t="s">
-        <v>3142</v>
+        <v>3141</v>
       </c>
       <c r="B1651" s="5" t="s">
         <v>2774</v>
@@ -54889,7 +54890,7 @@
     </row>
     <row r="1652" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1652" s="8" t="s">
-        <v>3142</v>
+        <v>3141</v>
       </c>
       <c r="B1652" s="5" t="s">
         <v>2774</v>
@@ -54904,19 +54905,19 @@
         <v>2775</v>
       </c>
       <c r="F1652" s="3" t="s">
-        <v>3151</v>
+        <v>3150</v>
       </c>
       <c r="G1652" s="3">
         <v>3</v>
       </c>
       <c r="H1652" s="12"/>
       <c r="I1652" s="12" t="s">
-        <v>3152</v>
+        <v>3151</v>
       </c>
     </row>
     <row r="1653" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1653" s="8" t="s">
-        <v>3142</v>
+        <v>3141</v>
       </c>
       <c r="B1653" s="5" t="s">
         <v>2774</v>
@@ -54931,19 +54932,19 @@
         <v>2775</v>
       </c>
       <c r="F1653" s="3" t="s">
-        <v>3153</v>
+        <v>3152</v>
       </c>
       <c r="G1653" s="3">
         <v>2</v>
       </c>
       <c r="H1653" s="12"/>
       <c r="I1653" s="12" t="s">
-        <v>3154</v>
+        <v>3153</v>
       </c>
     </row>
     <row r="1654" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1654" s="8" t="s">
-        <v>3142</v>
+        <v>3141</v>
       </c>
       <c r="B1654" s="5" t="s">
         <v>2774</v>
@@ -54958,7 +54959,7 @@
         <v>2775</v>
       </c>
       <c r="F1654" s="3" t="s">
-        <v>3155</v>
+        <v>3154</v>
       </c>
       <c r="G1654" s="3">
         <v>2</v>
@@ -54968,7 +54969,7 @@
     </row>
     <row r="1655" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1655" s="8" t="s">
-        <v>3142</v>
+        <v>3141</v>
       </c>
       <c r="B1655" s="5" t="s">
         <v>2774</v>
@@ -54983,19 +54984,19 @@
         <v>2775</v>
       </c>
       <c r="F1655" s="3" t="s">
-        <v>3156</v>
+        <v>3155</v>
       </c>
       <c r="G1655" s="3">
         <v>3</v>
       </c>
       <c r="H1655" s="12"/>
       <c r="I1655" s="12" t="s">
-        <v>3157</v>
+        <v>3156</v>
       </c>
     </row>
     <row r="1656" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1656" s="8" t="s">
-        <v>3142</v>
+        <v>3141</v>
       </c>
       <c r="B1656" s="5" t="s">
         <v>2774</v>
@@ -55022,7 +55023,7 @@
     </row>
     <row r="1657" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1657" s="8" t="s">
-        <v>3142</v>
+        <v>3141</v>
       </c>
       <c r="B1657" s="5" t="s">
         <v>2774</v>
@@ -55049,7 +55050,7 @@
     </row>
     <row r="1658" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1658" s="8" t="s">
-        <v>3142</v>
+        <v>3141</v>
       </c>
       <c r="B1658" s="5" t="s">
         <v>2774</v>
@@ -55076,7 +55077,7 @@
     </row>
     <row r="1659" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1659" s="8" t="s">
-        <v>3142</v>
+        <v>3141</v>
       </c>
       <c r="B1659" s="5" t="s">
         <v>2774</v>
@@ -55098,12 +55099,12 @@
       </c>
       <c r="H1659" s="12"/>
       <c r="I1659" s="12" t="s">
-        <v>3158</v>
+        <v>3157</v>
       </c>
     </row>
     <row r="1660" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1660" s="8" t="s">
-        <v>3142</v>
+        <v>3141</v>
       </c>
       <c r="B1660" s="5" t="s">
         <v>2774</v>
@@ -55130,7 +55131,7 @@
     </row>
     <row r="1661" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1661" s="8" t="s">
-        <v>3142</v>
+        <v>3141</v>
       </c>
       <c r="B1661" s="5" t="s">
         <v>2774</v>
@@ -55145,7 +55146,7 @@
         <v>2775</v>
       </c>
       <c r="F1661" s="3" t="s">
-        <v>3159</v>
+        <v>3158</v>
       </c>
       <c r="G1661" s="3">
         <v>2</v>
@@ -55157,7 +55158,7 @@
     </row>
     <row r="1662" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1662" s="8" t="s">
-        <v>3142</v>
+        <v>3141</v>
       </c>
       <c r="B1662" s="5" t="s">
         <v>2774</v>
@@ -55172,19 +55173,19 @@
         <v>2775</v>
       </c>
       <c r="F1662" s="3" t="s">
-        <v>3160</v>
+        <v>3159</v>
       </c>
       <c r="G1662" s="3">
         <v>3</v>
       </c>
       <c r="H1662" s="12"/>
       <c r="I1662" s="12" t="s">
-        <v>3161</v>
+        <v>3160</v>
       </c>
     </row>
     <row r="1663" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1663" s="8" t="s">
-        <v>3162</v>
+        <v>3161</v>
       </c>
       <c r="B1663" s="5" t="s">
         <v>2774</v>
@@ -55211,7 +55212,7 @@
     </row>
     <row r="1664" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1664" s="8" t="s">
-        <v>3162</v>
+        <v>3161</v>
       </c>
       <c r="B1664" s="5" t="s">
         <v>2774</v>
@@ -55238,7 +55239,7 @@
     </row>
     <row r="1665" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1665" s="8" t="s">
-        <v>3162</v>
+        <v>3161</v>
       </c>
       <c r="B1665" s="5" t="s">
         <v>2774</v>
@@ -55265,7 +55266,7 @@
     </row>
     <row r="1666" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1666" s="8" t="s">
-        <v>3162</v>
+        <v>3161</v>
       </c>
       <c r="B1666" s="5" t="s">
         <v>2774</v>
@@ -55292,7 +55293,7 @@
     </row>
     <row r="1667" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1667" s="8" t="s">
-        <v>3162</v>
+        <v>3161</v>
       </c>
       <c r="B1667" s="5" t="s">
         <v>2774</v>
@@ -55319,7 +55320,7 @@
     </row>
     <row r="1668" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1668" s="8" t="s">
-        <v>3162</v>
+        <v>3161</v>
       </c>
       <c r="B1668" s="5" t="s">
         <v>2774</v>
@@ -55341,12 +55342,12 @@
       </c>
       <c r="H1668" s="12"/>
       <c r="I1668" s="12" t="s">
-        <v>3163</v>
+        <v>3162</v>
       </c>
     </row>
     <row r="1669" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1669" s="8" t="s">
-        <v>3162</v>
+        <v>3161</v>
       </c>
       <c r="B1669" s="5" t="s">
         <v>2774</v>
@@ -55361,7 +55362,7 @@
         <v>2779</v>
       </c>
       <c r="F1669" s="3" t="s">
-        <v>3164</v>
+        <v>3163</v>
       </c>
       <c r="G1669" s="3">
         <v>3</v>
@@ -55373,7 +55374,7 @@
     </row>
     <row r="1670" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1670" s="8" t="s">
-        <v>3162</v>
+        <v>3161</v>
       </c>
       <c r="B1670" s="5" t="s">
         <v>2774</v>
@@ -55388,19 +55389,19 @@
         <v>2775</v>
       </c>
       <c r="F1670" s="3" t="s">
-        <v>3165</v>
+        <v>3164</v>
       </c>
       <c r="G1670" s="3">
         <v>3</v>
       </c>
       <c r="H1670" s="12"/>
       <c r="I1670" s="12" t="s">
-        <v>3166</v>
+        <v>3165</v>
       </c>
     </row>
     <row r="1671" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1671" s="8" t="s">
-        <v>3162</v>
+        <v>3161</v>
       </c>
       <c r="B1671" s="5" t="s">
         <v>2774</v>
@@ -55415,19 +55416,19 @@
         <v>2775</v>
       </c>
       <c r="F1671" s="3" t="s">
-        <v>3167</v>
+        <v>3166</v>
       </c>
       <c r="G1671" s="3">
         <v>3</v>
       </c>
       <c r="H1671" s="12"/>
       <c r="I1671" s="12" t="s">
-        <v>3168</v>
+        <v>3167</v>
       </c>
     </row>
     <row r="1672" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1672" s="8" t="s">
-        <v>3162</v>
+        <v>3161</v>
       </c>
       <c r="B1672" s="5" t="s">
         <v>2774</v>
@@ -55454,7 +55455,7 @@
     </row>
     <row r="1673" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1673" s="8" t="s">
-        <v>3162</v>
+        <v>3161</v>
       </c>
       <c r="B1673" s="5" t="s">
         <v>2774</v>
@@ -55481,7 +55482,7 @@
     </row>
     <row r="1674" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1674" s="8" t="s">
-        <v>3162</v>
+        <v>3161</v>
       </c>
       <c r="B1674" s="5" t="s">
         <v>2774</v>
@@ -55508,7 +55509,7 @@
     </row>
     <row r="1675" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1675" s="8" t="s">
-        <v>3162</v>
+        <v>3161</v>
       </c>
       <c r="B1675" s="5" t="s">
         <v>2774</v>
@@ -55523,19 +55524,19 @@
         <v>2775</v>
       </c>
       <c r="F1675" s="3" t="s">
-        <v>3169</v>
+        <v>3168</v>
       </c>
       <c r="G1675" s="3">
         <v>3</v>
       </c>
       <c r="H1675" s="12"/>
       <c r="I1675" s="12" t="s">
-        <v>3170</v>
+        <v>3169</v>
       </c>
     </row>
     <row r="1676" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1676" s="8" t="s">
-        <v>3162</v>
+        <v>3161</v>
       </c>
       <c r="B1676" s="5" t="s">
         <v>2774</v>
@@ -55550,19 +55551,19 @@
         <v>2775</v>
       </c>
       <c r="F1676" s="3" t="s">
-        <v>3171</v>
+        <v>3170</v>
       </c>
       <c r="G1676" s="3">
         <v>3</v>
       </c>
       <c r="H1676" s="12"/>
       <c r="I1676" s="12" t="s">
-        <v>3172</v>
+        <v>3171</v>
       </c>
     </row>
     <row r="1677" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1677" s="8" t="s">
-        <v>3162</v>
+        <v>3161</v>
       </c>
       <c r="B1677" s="5" t="s">
         <v>2774</v>
@@ -55589,7 +55590,7 @@
     </row>
     <row r="1678" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1678" s="8" t="s">
-        <v>3162</v>
+        <v>3161</v>
       </c>
       <c r="B1678" s="5" t="s">
         <v>2774</v>
@@ -55611,12 +55612,12 @@
       </c>
       <c r="H1678" s="12"/>
       <c r="I1678" s="12" t="s">
-        <v>3173</v>
+        <v>3172</v>
       </c>
     </row>
     <row r="1679" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1679" s="8" t="s">
-        <v>3162</v>
+        <v>3161</v>
       </c>
       <c r="B1679" s="5" t="s">
         <v>2774</v>
@@ -55638,12 +55639,12 @@
       </c>
       <c r="H1679" s="12"/>
       <c r="I1679" s="12" t="s">
-        <v>3174</v>
+        <v>3173</v>
       </c>
     </row>
     <row r="1680" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1680" s="8" t="s">
-        <v>3162</v>
+        <v>3161</v>
       </c>
       <c r="B1680" s="5" t="s">
         <v>2774</v>
@@ -55670,7 +55671,7 @@
     </row>
     <row r="1681" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1681" s="8" t="s">
-        <v>3162</v>
+        <v>3161</v>
       </c>
       <c r="B1681" s="5" t="s">
         <v>2774</v>
@@ -55692,12 +55693,12 @@
       </c>
       <c r="H1681" s="12"/>
       <c r="I1681" s="12" t="s">
-        <v>3175</v>
+        <v>3174</v>
       </c>
     </row>
     <row r="1682" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1682" s="8" t="s">
-        <v>3162</v>
+        <v>3161</v>
       </c>
       <c r="B1682" s="5" t="s">
         <v>2774</v>
@@ -55724,7 +55725,7 @@
     </row>
     <row r="1683" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1683" s="8" t="s">
-        <v>3162</v>
+        <v>3161</v>
       </c>
       <c r="B1683" s="5" t="s">
         <v>2774</v>
@@ -55751,7 +55752,7 @@
     </row>
     <row r="1684" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1684" s="8" t="s">
-        <v>3162</v>
+        <v>3161</v>
       </c>
       <c r="B1684" s="5" t="s">
         <v>2774</v>
@@ -55773,12 +55774,12 @@
       </c>
       <c r="H1684" s="12"/>
       <c r="I1684" s="12" t="s">
-        <v>3176</v>
+        <v>3175</v>
       </c>
     </row>
     <row r="1685" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1685" s="8" t="s">
-        <v>3162</v>
+        <v>3161</v>
       </c>
       <c r="B1685" s="5" t="s">
         <v>2774</v>
@@ -55805,7 +55806,7 @@
     </row>
     <row r="1686" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1686" s="8" t="s">
-        <v>3162</v>
+        <v>3161</v>
       </c>
       <c r="B1686" s="5" t="s">
         <v>2774</v>
@@ -55832,7 +55833,7 @@
     </row>
     <row r="1687" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1687" s="8" t="s">
-        <v>3162</v>
+        <v>3161</v>
       </c>
       <c r="B1687" s="5" t="s">
         <v>2774</v>
@@ -55859,7 +55860,7 @@
     </row>
     <row r="1688" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1688" s="8" t="s">
-        <v>3162</v>
+        <v>3161</v>
       </c>
       <c r="B1688" s="5" t="s">
         <v>2774</v>
@@ -55886,7 +55887,7 @@
     </row>
     <row r="1689" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1689" s="8" t="s">
-        <v>3162</v>
+        <v>3161</v>
       </c>
       <c r="B1689" s="5" t="s">
         <v>2774</v>
@@ -55913,7 +55914,7 @@
     </row>
     <row r="1690" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1690" s="8" t="s">
-        <v>3162</v>
+        <v>3161</v>
       </c>
       <c r="B1690" s="5" t="s">
         <v>2774</v>
@@ -55940,7 +55941,7 @@
     </row>
     <row r="1691" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1691" s="8" t="s">
-        <v>3162</v>
+        <v>3161</v>
       </c>
       <c r="B1691" s="5" t="s">
         <v>2774</v>
@@ -55967,7 +55968,7 @@
     </row>
     <row r="1692" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1692" s="8" t="s">
-        <v>3162</v>
+        <v>3161</v>
       </c>
       <c r="B1692" s="5" t="s">
         <v>2774</v>
@@ -55994,7 +55995,7 @@
     </row>
     <row r="1693" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1693" s="8" t="s">
-        <v>3162</v>
+        <v>3161</v>
       </c>
       <c r="B1693" s="5" t="s">
         <v>2774</v>
@@ -56021,7 +56022,7 @@
     </row>
     <row r="1694" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1694" s="8" t="s">
-        <v>3162</v>
+        <v>3161</v>
       </c>
       <c r="B1694" s="5" t="s">
         <v>2774</v>
@@ -56048,7 +56049,7 @@
     </row>
     <row r="1695" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1695" s="8" t="s">
-        <v>3162</v>
+        <v>3161</v>
       </c>
       <c r="B1695" s="5" t="s">
         <v>2774</v>
@@ -56075,7 +56076,7 @@
     </row>
     <row r="1696" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1696" s="8" t="s">
-        <v>3162</v>
+        <v>3161</v>
       </c>
       <c r="B1696" s="5" t="s">
         <v>2774</v>
@@ -56102,7 +56103,7 @@
     </row>
     <row r="1697" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1697" s="8" t="s">
-        <v>3162</v>
+        <v>3161</v>
       </c>
       <c r="B1697" s="5" t="s">
         <v>2774</v>
@@ -56129,7 +56130,7 @@
     </row>
     <row r="1698" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1698" s="8" t="s">
-        <v>3162</v>
+        <v>3161</v>
       </c>
       <c r="B1698" s="5" t="s">
         <v>2774</v>
@@ -56151,12 +56152,12 @@
       </c>
       <c r="H1698" s="12"/>
       <c r="I1698" s="12" t="s">
-        <v>3177</v>
+        <v>3176</v>
       </c>
     </row>
     <row r="1699" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1699" s="8" t="s">
-        <v>3162</v>
+        <v>3161</v>
       </c>
       <c r="B1699" s="5" t="s">
         <v>2774</v>
@@ -56178,12 +56179,12 @@
       </c>
       <c r="H1699" s="12"/>
       <c r="I1699" s="12" t="s">
-        <v>3178</v>
+        <v>3177</v>
       </c>
     </row>
     <row r="1700" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1700" s="8" t="s">
-        <v>3162</v>
+        <v>3161</v>
       </c>
       <c r="B1700" s="5" t="s">
         <v>2774</v>
@@ -56210,7 +56211,7 @@
     </row>
     <row r="1701" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1701" s="8" t="s">
-        <v>3179</v>
+        <v>3178</v>
       </c>
       <c r="B1701" s="5" t="s">
         <v>2774</v>
@@ -56237,7 +56238,7 @@
     </row>
     <row r="1702" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1702" s="8" t="s">
-        <v>3179</v>
+        <v>3178</v>
       </c>
       <c r="B1702" s="5" t="s">
         <v>2774</v>
@@ -56264,7 +56265,7 @@
     </row>
     <row r="1703" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1703" s="8" t="s">
-        <v>3179</v>
+        <v>3178</v>
       </c>
       <c r="B1703" s="5" t="s">
         <v>2774</v>
@@ -56291,7 +56292,7 @@
     </row>
     <row r="1704" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1704" s="8" t="s">
-        <v>3179</v>
+        <v>3178</v>
       </c>
       <c r="B1704" s="5" t="s">
         <v>2774</v>
@@ -56313,12 +56314,12 @@
       </c>
       <c r="H1704" s="12"/>
       <c r="I1704" s="12" t="s">
-        <v>3180</v>
+        <v>3179</v>
       </c>
     </row>
     <row r="1705" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1705" s="8" t="s">
-        <v>3179</v>
+        <v>3178</v>
       </c>
       <c r="B1705" s="5" t="s">
         <v>2774</v>
@@ -56333,7 +56334,7 @@
         <v>2775</v>
       </c>
       <c r="F1705" s="3" t="s">
-        <v>3181</v>
+        <v>3180</v>
       </c>
       <c r="G1705" s="3">
         <v>3</v>
@@ -56345,7 +56346,7 @@
     </row>
     <row r="1706" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1706" s="8" t="s">
-        <v>3179</v>
+        <v>3178</v>
       </c>
       <c r="B1706" s="5" t="s">
         <v>2774</v>
@@ -56372,7 +56373,7 @@
     </row>
     <row r="1707" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1707" s="8" t="s">
-        <v>3179</v>
+        <v>3178</v>
       </c>
       <c r="B1707" s="5" t="s">
         <v>2774</v>
@@ -56387,19 +56388,19 @@
         <v>2775</v>
       </c>
       <c r="F1707" s="3" t="s">
-        <v>3182</v>
+        <v>3181</v>
       </c>
       <c r="G1707" s="3">
         <v>3</v>
       </c>
       <c r="H1707" s="12"/>
       <c r="I1707" s="12" t="s">
-        <v>3180</v>
+        <v>3179</v>
       </c>
     </row>
     <row r="1708" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1708" s="8" t="s">
-        <v>3179</v>
+        <v>3178</v>
       </c>
       <c r="B1708" s="5" t="s">
         <v>2774</v>
@@ -56426,7 +56427,7 @@
     </row>
     <row r="1709" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1709" s="8" t="s">
-        <v>3179</v>
+        <v>3178</v>
       </c>
       <c r="B1709" s="5" t="s">
         <v>2774</v>
@@ -56453,7 +56454,7 @@
     </row>
     <row r="1710" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1710" s="8" t="s">
-        <v>3179</v>
+        <v>3178</v>
       </c>
       <c r="B1710" s="5" t="s">
         <v>2774</v>
@@ -56480,7 +56481,7 @@
     </row>
     <row r="1711" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1711" s="8" t="s">
-        <v>3179</v>
+        <v>3178</v>
       </c>
       <c r="B1711" s="5" t="s">
         <v>2774</v>
@@ -56507,7 +56508,7 @@
     </row>
     <row r="1712" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1712" s="8" t="s">
-        <v>3179</v>
+        <v>3178</v>
       </c>
       <c r="B1712" s="5" t="s">
         <v>2774</v>
@@ -56522,19 +56523,19 @@
         <v>2775</v>
       </c>
       <c r="F1712" s="3" t="s">
-        <v>3183</v>
+        <v>3182</v>
       </c>
       <c r="G1712" s="3">
         <v>3</v>
       </c>
       <c r="H1712" s="12"/>
       <c r="I1712" s="12" t="s">
-        <v>3184</v>
+        <v>3183</v>
       </c>
     </row>
     <row r="1713" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1713" s="8" t="s">
-        <v>3179</v>
+        <v>3178</v>
       </c>
       <c r="B1713" s="5" t="s">
         <v>2774</v>
@@ -56561,7 +56562,7 @@
     </row>
     <row r="1714" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1714" s="8" t="s">
-        <v>3179</v>
+        <v>3178</v>
       </c>
       <c r="B1714" s="5" t="s">
         <v>2774</v>
@@ -56588,7 +56589,7 @@
     </row>
     <row r="1715" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1715" s="8" t="s">
-        <v>3179</v>
+        <v>3178</v>
       </c>
       <c r="B1715" s="5" t="s">
         <v>2774</v>
@@ -56615,7 +56616,7 @@
     </row>
     <row r="1716" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1716" s="8" t="s">
-        <v>3179</v>
+        <v>3178</v>
       </c>
       <c r="B1716" s="5" t="s">
         <v>2774</v>
@@ -56642,7 +56643,7 @@
     </row>
     <row r="1717" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1717" s="8" t="s">
-        <v>3179</v>
+        <v>3178</v>
       </c>
       <c r="B1717" s="5" t="s">
         <v>2774</v>
@@ -56669,7 +56670,7 @@
     </row>
     <row r="1718" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1718" s="8" t="s">
-        <v>3179</v>
+        <v>3178</v>
       </c>
       <c r="B1718" s="5" t="s">
         <v>2774</v>
@@ -56696,7 +56697,7 @@
     </row>
     <row r="1719" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1719" s="8" t="s">
-        <v>3179</v>
+        <v>3178</v>
       </c>
       <c r="B1719" s="5" t="s">
         <v>2774</v>
@@ -56723,7 +56724,7 @@
     </row>
     <row r="1720" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1720" s="8" t="s">
-        <v>3179</v>
+        <v>3178</v>
       </c>
       <c r="B1720" s="5" t="s">
         <v>2774</v>
@@ -56750,7 +56751,7 @@
     </row>
     <row r="1721" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1721" s="8" t="s">
-        <v>3179</v>
+        <v>3178</v>
       </c>
       <c r="B1721" s="5" t="s">
         <v>2774</v>
@@ -56777,7 +56778,7 @@
     </row>
     <row r="1722" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1722" s="8" t="s">
-        <v>3179</v>
+        <v>3178</v>
       </c>
       <c r="B1722" s="5" t="s">
         <v>2774</v>
@@ -56792,7 +56793,7 @@
         <v>2779</v>
       </c>
       <c r="F1722" s="3" t="s">
-        <v>3185</v>
+        <v>3184</v>
       </c>
       <c r="G1722" s="3">
         <v>3</v>
@@ -56804,7 +56805,7 @@
     </row>
     <row r="1723" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1723" s="8" t="s">
-        <v>3179</v>
+        <v>3178</v>
       </c>
       <c r="B1723" s="5" t="s">
         <v>2774</v>
@@ -56819,19 +56820,19 @@
         <v>2775</v>
       </c>
       <c r="F1723" s="3" t="s">
-        <v>3186</v>
+        <v>3185</v>
       </c>
       <c r="G1723" s="3">
         <v>3</v>
       </c>
       <c r="H1723" s="12"/>
       <c r="I1723" s="12" t="s">
-        <v>3187</v>
+        <v>3186</v>
       </c>
     </row>
     <row r="1724" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1724" s="8" t="s">
-        <v>3179</v>
+        <v>3178</v>
       </c>
       <c r="B1724" s="5" t="s">
         <v>2774</v>
@@ -56858,7 +56859,7 @@
     </row>
     <row r="1725" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1725" s="8" t="s">
-        <v>3179</v>
+        <v>3178</v>
       </c>
       <c r="B1725" s="5" t="s">
         <v>2774</v>
@@ -56885,7 +56886,7 @@
     </row>
     <row r="1726" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1726" s="8" t="s">
-        <v>3179</v>
+        <v>3178</v>
       </c>
       <c r="B1726" s="5" t="s">
         <v>2774</v>
@@ -56912,7 +56913,7 @@
     </row>
     <row r="1727" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1727" s="8" t="s">
-        <v>3179</v>
+        <v>3178</v>
       </c>
       <c r="B1727" s="5" t="s">
         <v>2774</v>
@@ -56939,7 +56940,7 @@
     </row>
     <row r="1728" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1728" s="8" t="s">
-        <v>3179</v>
+        <v>3178</v>
       </c>
       <c r="B1728" s="5" t="s">
         <v>2774</v>
@@ -56966,7 +56967,7 @@
     </row>
     <row r="1729" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1729" s="8" t="s">
-        <v>3179</v>
+        <v>3178</v>
       </c>
       <c r="B1729" s="5" t="s">
         <v>2774</v>
@@ -56993,7 +56994,7 @@
     </row>
     <row r="1730" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1730" s="8" t="s">
-        <v>3179</v>
+        <v>3178</v>
       </c>
       <c r="B1730" s="5" t="s">
         <v>2774</v>
@@ -57015,12 +57016,12 @@
       </c>
       <c r="H1730" s="12"/>
       <c r="I1730" s="12" t="s">
-        <v>3188</v>
+        <v>3187</v>
       </c>
     </row>
     <row r="1731" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1731" s="8" t="s">
-        <v>3179</v>
+        <v>3178</v>
       </c>
       <c r="B1731" s="5" t="s">
         <v>2774</v>
@@ -57047,7 +57048,7 @@
     </row>
     <row r="1732" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1732" s="8" t="s">
-        <v>3179</v>
+        <v>3178</v>
       </c>
       <c r="B1732" s="5" t="s">
         <v>2774</v>
@@ -57074,7 +57075,7 @@
     </row>
     <row r="1733" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1733" s="8" t="s">
-        <v>3179</v>
+        <v>3178</v>
       </c>
       <c r="B1733" s="5" t="s">
         <v>2774</v>
@@ -57101,7 +57102,7 @@
     </row>
     <row r="1734" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1734" s="8" t="s">
-        <v>3179</v>
+        <v>3178</v>
       </c>
       <c r="B1734" s="5" t="s">
         <v>2774</v>
@@ -57116,19 +57117,19 @@
         <v>2775</v>
       </c>
       <c r="F1734" s="3" t="s">
-        <v>3189</v>
+        <v>3188</v>
       </c>
       <c r="G1734" s="3">
         <v>3</v>
       </c>
       <c r="H1734" s="12"/>
       <c r="I1734" s="12" t="s">
-        <v>3190</v>
+        <v>3189</v>
       </c>
     </row>
     <row r="1735" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1735" s="8" t="s">
-        <v>3179</v>
+        <v>3178</v>
       </c>
       <c r="B1735" s="5" t="s">
         <v>2774</v>
@@ -57155,7 +57156,7 @@
     </row>
     <row r="1736" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1736" s="8" t="s">
-        <v>3179</v>
+        <v>3178</v>
       </c>
       <c r="B1736" s="5" t="s">
         <v>2774</v>
@@ -57182,7 +57183,7 @@
     </row>
     <row r="1737" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1737" s="8" t="s">
-        <v>3179</v>
+        <v>3178</v>
       </c>
       <c r="B1737" s="5" t="s">
         <v>2774</v>
@@ -57204,12 +57205,12 @@
       </c>
       <c r="H1737" s="12"/>
       <c r="I1737" s="12" t="s">
-        <v>3191</v>
+        <v>3190</v>
       </c>
     </row>
     <row r="1738" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1738" s="8" t="s">
-        <v>3179</v>
+        <v>3178</v>
       </c>
       <c r="B1738" s="5" t="s">
         <v>2774</v>
@@ -64222,7 +64223,7 @@
       </c>
       <c r="H1997" s="12"/>
       <c r="I1997" s="12" t="s">
-        <v>3267</v>
+        <v>3265</v>
       </c>
     </row>
     <row r="1998" spans="1:9" x14ac:dyDescent="0.3">
@@ -64303,7 +64304,7 @@
       </c>
       <c r="H2000" s="12"/>
       <c r="I2000" s="12" t="s">
-        <v>3269</v>
+        <v>3267</v>
       </c>
     </row>
     <row r="2001" spans="1:9" x14ac:dyDescent="0.3">
@@ -64411,7 +64412,7 @@
       </c>
       <c r="H2004" s="12"/>
       <c r="I2004" s="12" t="s">
-        <v>3268</v>
+        <v>3266</v>
       </c>
     </row>
     <row r="2005" spans="1:9" x14ac:dyDescent="0.3">
@@ -64652,7 +64653,7 @@
       </c>
       <c r="H2013" s="12"/>
       <c r="I2013" s="12" t="s">
-        <v>3270</v>
+        <v>3268</v>
       </c>
     </row>
     <row r="2014" spans="1:9" x14ac:dyDescent="0.3">
@@ -64760,7 +64761,7 @@
       </c>
       <c r="H2017" s="12"/>
       <c r="I2017" s="12" t="s">
-        <v>3271</v>
+        <v>3269</v>
       </c>
     </row>
     <row r="2018" spans="1:9" x14ac:dyDescent="0.3">
@@ -64787,7 +64788,7 @@
       </c>
       <c r="H2018" s="12"/>
       <c r="I2018" s="12" t="s">
-        <v>3272</v>
+        <v>3270</v>
       </c>
     </row>
     <row r="2019" spans="1:9" x14ac:dyDescent="0.3">
@@ -65178,7 +65179,7 @@
       </c>
       <c r="E2034" s="11"/>
       <c r="F2034" s="7" t="s">
-        <v>3222</v>
+        <v>3221</v>
       </c>
       <c r="G2034" s="7">
         <v>3</v>
@@ -65537,7 +65538,7 @@
         <v>1510</v>
       </c>
       <c r="I2048" s="12" t="s">
-        <v>3261</v>
+        <v>3259</v>
       </c>
     </row>
     <row r="2049" spans="1:9" x14ac:dyDescent="0.3">
@@ -65578,7 +65579,7 @@
       </c>
       <c r="E2050" s="11"/>
       <c r="F2050" s="7" t="s">
-        <v>3223</v>
+        <v>3222</v>
       </c>
       <c r="G2050" s="7">
         <v>3</v>
@@ -65803,7 +65804,7 @@
       </c>
       <c r="E2059" s="11"/>
       <c r="F2059" s="7" t="s">
-        <v>3221</v>
+        <v>3220</v>
       </c>
       <c r="G2059" s="7">
         <v>3</v>
@@ -65959,7 +65960,7 @@
         <v>3</v>
       </c>
       <c r="H2065" s="12" t="s">
-        <v>3256</v>
+        <v>3271</v>
       </c>
       <c r="I2065" s="12" t="s">
         <v>2172</v>
@@ -65984,7 +65985,7 @@
         <v>3</v>
       </c>
       <c r="H2066" s="12" t="s">
-        <v>3256</v>
+        <v>3271</v>
       </c>
       <c r="I2066" s="13" t="s">
         <v>1533</v>
@@ -66962,7 +66963,7 @@
         <v>1518</v>
       </c>
       <c r="I2105" s="12" t="s">
-        <v>3262</v>
+        <v>3260</v>
       </c>
     </row>
     <row r="2106" spans="1:9" x14ac:dyDescent="0.3">
@@ -67012,7 +67013,7 @@
         <v>1520</v>
       </c>
       <c r="I2107" s="12" t="s">
-        <v>3263</v>
+        <v>3261</v>
       </c>
     </row>
     <row r="2108" spans="1:9" x14ac:dyDescent="0.3">
@@ -67087,7 +67088,7 @@
         <v>616</v>
       </c>
       <c r="I2110" s="12" t="s">
-        <v>3264</v>
+        <v>3262</v>
       </c>
     </row>
     <row r="2111" spans="1:9" x14ac:dyDescent="0.3">
@@ -67128,7 +67129,7 @@
       </c>
       <c r="E2112" s="11"/>
       <c r="F2112" s="7" t="s">
-        <v>3224</v>
+        <v>3223</v>
       </c>
       <c r="G2112" s="7">
         <v>3</v>
@@ -67137,7 +67138,7 @@
         <v>616</v>
       </c>
       <c r="I2112" s="12" t="s">
-        <v>3225</v>
+        <v>3224</v>
       </c>
     </row>
     <row r="2113" spans="1:9" x14ac:dyDescent="0.3">
@@ -67428,7 +67429,7 @@
       </c>
       <c r="E2124" s="11"/>
       <c r="F2124" s="7" t="s">
-        <v>3220</v>
+        <v>3219</v>
       </c>
       <c r="G2124" s="7">
         <v>3</v>
@@ -67462,7 +67463,7 @@
         <v>776</v>
       </c>
       <c r="I2125" s="12" t="s">
-        <v>3265</v>
+        <v>3263</v>
       </c>
     </row>
     <row r="2126" spans="1:9" x14ac:dyDescent="0.3">
@@ -67484,7 +67485,7 @@
         <v>3</v>
       </c>
       <c r="H2126" s="12" t="s">
-        <v>3243</v>
+        <v>3242</v>
       </c>
       <c r="I2126" s="12" t="s">
         <v>2266</v>
@@ -67509,7 +67510,7 @@
         <v>3</v>
       </c>
       <c r="H2127" s="12" t="s">
-        <v>3243</v>
+        <v>3242</v>
       </c>
       <c r="I2127" s="12" t="s">
         <v>2269</v>
@@ -67662,7 +67663,7 @@
         <v>1519</v>
       </c>
       <c r="I2133" s="12" t="s">
-        <v>3266</v>
+        <v>3264</v>
       </c>
     </row>
     <row r="2134" spans="1:9" x14ac:dyDescent="0.3">
@@ -67684,7 +67685,7 @@
         <v>2</v>
       </c>
       <c r="H2134" s="12" t="s">
-        <v>3258</v>
+        <v>3256</v>
       </c>
       <c r="I2134" s="12" t="s">
         <v>2436</v>
@@ -67709,7 +67710,7 @@
         <v>2</v>
       </c>
       <c r="H2135" s="12" t="s">
-        <v>3258</v>
+        <v>3256</v>
       </c>
       <c r="I2135" s="12" t="s">
         <v>2440</v>
@@ -67734,7 +67735,7 @@
         <v>2</v>
       </c>
       <c r="H2136" s="12" t="s">
-        <v>3258</v>
+        <v>3256</v>
       </c>
       <c r="I2136" s="12" t="s">
         <v>2441</v>
@@ -67759,7 +67760,7 @@
         <v>2</v>
       </c>
       <c r="H2137" s="12" t="s">
-        <v>3258</v>
+        <v>3256</v>
       </c>
       <c r="I2137" s="12" t="s">
         <v>2443</v>
@@ -67784,7 +67785,7 @@
         <v>2</v>
       </c>
       <c r="H2138" s="12" t="s">
-        <v>3258</v>
+        <v>3256</v>
       </c>
       <c r="I2138" s="12" t="s">
         <v>2448</v>
@@ -67809,7 +67810,7 @@
         <v>3</v>
       </c>
       <c r="H2139" s="12" t="s">
-        <v>3255</v>
+        <v>3254</v>
       </c>
       <c r="I2139" s="12" t="s">
         <v>2610</v>
@@ -67834,7 +67835,7 @@
         <v>3</v>
       </c>
       <c r="H2140" s="12" t="s">
-        <v>3255</v>
+        <v>3254</v>
       </c>
       <c r="I2140" s="12" t="s">
         <v>2139</v>
@@ -67859,7 +67860,7 @@
         <v>3</v>
       </c>
       <c r="H2141" s="12" t="s">
-        <v>3259</v>
+        <v>3257</v>
       </c>
       <c r="I2141" s="12" t="s">
         <v>2484</v>
@@ -67878,13 +67879,13 @@
       </c>
       <c r="E2142" s="11"/>
       <c r="F2142" s="7" t="s">
-        <v>3227</v>
+        <v>3226</v>
       </c>
       <c r="G2142" s="7">
         <v>3</v>
       </c>
       <c r="H2142" s="12" t="s">
-        <v>3260</v>
+        <v>3258</v>
       </c>
       <c r="I2142" s="12" t="s">
         <v>2410</v>
@@ -67909,7 +67910,7 @@
         <v>2</v>
       </c>
       <c r="H2143" s="12" t="s">
-        <v>3260</v>
+        <v>3258</v>
       </c>
       <c r="I2143" s="12" t="s">
         <v>2412</v>
@@ -67928,16 +67929,16 @@
       </c>
       <c r="E2144" s="11"/>
       <c r="F2144" s="7" t="s">
-        <v>3228</v>
+        <v>3227</v>
       </c>
       <c r="G2144" s="7">
         <v>2</v>
       </c>
       <c r="H2144" s="12" t="s">
-        <v>3260</v>
+        <v>3258</v>
       </c>
       <c r="I2144" s="12" t="s">
-        <v>3021</v>
+        <v>3020</v>
       </c>
     </row>
     <row r="2145" spans="1:9" x14ac:dyDescent="0.3">
@@ -67959,7 +67960,7 @@
         <v>2</v>
       </c>
       <c r="H2145" s="12" t="s">
-        <v>3260</v>
+        <v>3258</v>
       </c>
       <c r="I2145" s="12" t="s">
         <v>2415</v>
@@ -67984,7 +67985,7 @@
         <v>3</v>
       </c>
       <c r="H2146" s="12" t="s">
-        <v>3260</v>
+        <v>3258</v>
       </c>
       <c r="I2146" s="12" t="s">
         <v>2419</v>
@@ -68009,7 +68010,7 @@
         <v>3</v>
       </c>
       <c r="H2147" s="12" t="s">
-        <v>3260</v>
+        <v>3258</v>
       </c>
       <c r="I2147" s="12" t="s">
         <v>2424</v>
@@ -68034,7 +68035,7 @@
         <v>3</v>
       </c>
       <c r="H2148" s="12" t="s">
-        <v>3257</v>
+        <v>3255</v>
       </c>
       <c r="I2148" s="12" t="s">
         <v>2508</v>
@@ -68059,7 +68060,7 @@
         <v>3</v>
       </c>
       <c r="H2149" s="12" t="s">
-        <v>3257</v>
+        <v>3255</v>
       </c>
       <c r="I2149" s="12" t="s">
         <v>2512</v>
@@ -68084,7 +68085,7 @@
         <v>3</v>
       </c>
       <c r="H2150" s="12" t="s">
-        <v>3257</v>
+        <v>3255</v>
       </c>
       <c r="I2150" s="12" t="s">
         <v>2768</v>
@@ -68109,7 +68110,7 @@
         <v>3</v>
       </c>
       <c r="H2151" s="12" t="s">
-        <v>3257</v>
+        <v>3255</v>
       </c>
       <c r="I2151" s="12" t="s">
         <v>2521</v>
@@ -68117,7 +68118,7 @@
     </row>
     <row r="2152" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2152" s="9" t="s">
-        <v>3192</v>
+        <v>3191</v>
       </c>
       <c r="B2152" s="5" t="s">
         <v>2769</v>
@@ -68128,13 +68129,13 @@
       </c>
       <c r="E2152" s="11"/>
       <c r="F2152" s="7" t="s">
-        <v>3226</v>
+        <v>3225</v>
       </c>
       <c r="G2152" s="7">
         <v>3</v>
       </c>
       <c r="H2152" s="12" t="s">
-        <v>3229</v>
+        <v>3228</v>
       </c>
       <c r="I2152" s="12" t="s">
         <v>1600</v>
@@ -68142,7 +68143,7 @@
     </row>
     <row r="2153" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2153" s="9" t="s">
-        <v>3192</v>
+        <v>3191</v>
       </c>
       <c r="B2153" s="5" t="s">
         <v>2769</v>
@@ -68159,7 +68160,7 @@
         <v>3</v>
       </c>
       <c r="H2153" s="12" t="s">
-        <v>3229</v>
+        <v>3228</v>
       </c>
       <c r="I2153" s="12" t="s">
         <v>1611</v>
@@ -68167,7 +68168,7 @@
     </row>
     <row r="2154" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2154" s="9" t="s">
-        <v>3192</v>
+        <v>3191</v>
       </c>
       <c r="B2154" s="5" t="s">
         <v>2769</v>
@@ -68184,7 +68185,7 @@
         <v>3</v>
       </c>
       <c r="H2154" s="12" t="s">
-        <v>3230</v>
+        <v>3229</v>
       </c>
       <c r="I2154" s="12" t="s">
         <v>2840</v>
@@ -68192,7 +68193,7 @@
     </row>
     <row r="2155" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2155" s="9" t="s">
-        <v>3192</v>
+        <v>3191</v>
       </c>
       <c r="B2155" s="5" t="s">
         <v>2769</v>
@@ -68209,7 +68210,7 @@
         <v>3</v>
       </c>
       <c r="H2155" s="12" t="s">
-        <v>3230</v>
+        <v>3229</v>
       </c>
       <c r="I2155" s="12" t="s">
         <v>2845</v>
@@ -68217,7 +68218,7 @@
     </row>
     <row r="2156" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2156" s="9" t="s">
-        <v>3193</v>
+        <v>3192</v>
       </c>
       <c r="B2156" s="5" t="s">
         <v>2769</v>
@@ -68234,7 +68235,7 @@
         <v>3</v>
       </c>
       <c r="H2156" s="12" t="s">
-        <v>3231</v>
+        <v>3230</v>
       </c>
       <c r="I2156" s="12" t="s">
         <v>2148</v>
@@ -68242,7 +68243,7 @@
     </row>
     <row r="2157" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2157" s="9" t="s">
-        <v>3193</v>
+        <v>3192</v>
       </c>
       <c r="B2157" s="5" t="s">
         <v>2769</v>
@@ -68259,7 +68260,7 @@
         <v>3</v>
       </c>
       <c r="H2157" s="12" t="s">
-        <v>3231</v>
+        <v>3230</v>
       </c>
       <c r="I2157" s="12" t="s">
         <v>2149</v>
@@ -68267,7 +68268,7 @@
     </row>
     <row r="2158" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2158" s="9" t="s">
-        <v>3193</v>
+        <v>3192</v>
       </c>
       <c r="B2158" s="5" t="s">
         <v>2769</v>
@@ -68284,7 +68285,7 @@
         <v>3</v>
       </c>
       <c r="H2158" s="12" t="s">
-        <v>3256</v>
+        <v>3271</v>
       </c>
       <c r="I2158" s="12" t="s">
         <v>2165</v>
@@ -68292,7 +68293,7 @@
     </row>
     <row r="2159" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2159" s="9" t="s">
-        <v>3194</v>
+        <v>3193</v>
       </c>
       <c r="B2159" s="5" t="s">
         <v>2769</v>
@@ -68303,21 +68304,21 @@
       </c>
       <c r="E2159" s="11"/>
       <c r="F2159" s="7" t="s">
-        <v>3210</v>
+        <v>3209</v>
       </c>
       <c r="G2159" s="7">
         <v>3</v>
       </c>
       <c r="H2159" s="12" t="s">
+        <v>3230</v>
+      </c>
+      <c r="I2159" s="12" t="s">
         <v>3231</v>
-      </c>
-      <c r="I2159" s="12" t="s">
-        <v>3232</v>
       </c>
     </row>
     <row r="2160" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2160" s="9" t="s">
-        <v>3194</v>
+        <v>3193</v>
       </c>
       <c r="B2160" s="5" t="s">
         <v>2769</v>
@@ -68334,7 +68335,7 @@
         <v>3</v>
       </c>
       <c r="H2160" s="12" t="s">
-        <v>3231</v>
+        <v>3230</v>
       </c>
       <c r="I2160" s="12" t="s">
         <v>2155</v>
@@ -68342,7 +68343,7 @@
     </row>
     <row r="2161" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2161" s="9" t="s">
-        <v>3194</v>
+        <v>3193</v>
       </c>
       <c r="B2161" s="5" t="s">
         <v>2769</v>
@@ -68359,7 +68360,7 @@
         <v>3</v>
       </c>
       <c r="H2161" s="12" t="s">
-        <v>3256</v>
+        <v>3271</v>
       </c>
       <c r="I2161" s="12" t="s">
         <v>2174</v>
@@ -68367,7 +68368,7 @@
     </row>
     <row r="2162" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2162" s="9" t="s">
-        <v>3195</v>
+        <v>3194</v>
       </c>
       <c r="B2162" s="5" t="s">
         <v>2769</v>
@@ -68384,7 +68385,7 @@
         <v>3</v>
       </c>
       <c r="H2162" s="12" t="s">
-        <v>3248</v>
+        <v>3247</v>
       </c>
       <c r="I2162" s="12" t="s">
         <v>1911</v>
@@ -68392,7 +68393,7 @@
     </row>
     <row r="2163" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2163" s="9" t="s">
-        <v>3195</v>
+        <v>3194</v>
       </c>
       <c r="B2163" s="5" t="s">
         <v>2769</v>
@@ -68409,7 +68410,7 @@
         <v>3</v>
       </c>
       <c r="H2163" s="12" t="s">
-        <v>3248</v>
+        <v>3247</v>
       </c>
       <c r="I2163" s="12" t="s">
         <v>1900</v>
@@ -68417,7 +68418,7 @@
     </row>
     <row r="2164" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2164" s="9" t="s">
-        <v>3195</v>
+        <v>3194</v>
       </c>
       <c r="B2164" s="5" t="s">
         <v>2769</v>
@@ -68434,7 +68435,7 @@
         <v>3</v>
       </c>
       <c r="H2164" s="12" t="s">
-        <v>3248</v>
+        <v>3247</v>
       </c>
       <c r="I2164" s="12" t="s">
         <v>1768</v>
@@ -68442,7 +68443,7 @@
     </row>
     <row r="2165" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2165" s="9" t="s">
-        <v>3195</v>
+        <v>3194</v>
       </c>
       <c r="B2165" s="5" t="s">
         <v>2769</v>
@@ -68459,7 +68460,7 @@
         <v>3</v>
       </c>
       <c r="H2165" s="12" t="s">
-        <v>3248</v>
+        <v>3247</v>
       </c>
       <c r="I2165" s="12" t="s">
         <v>1897</v>
@@ -68467,7 +68468,7 @@
     </row>
     <row r="2166" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2166" s="9" t="s">
-        <v>3196</v>
+        <v>3195</v>
       </c>
       <c r="B2166" s="5" t="s">
         <v>2769</v>
@@ -68484,7 +68485,7 @@
         <v>3</v>
       </c>
       <c r="H2166" s="12" t="s">
-        <v>3249</v>
+        <v>3248</v>
       </c>
       <c r="I2166" s="12" t="s">
         <v>2811</v>
@@ -68492,7 +68493,7 @@
     </row>
     <row r="2167" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2167" s="9" t="s">
-        <v>3196</v>
+        <v>3195</v>
       </c>
       <c r="B2167" s="5" t="s">
         <v>2769</v>
@@ -68509,7 +68510,7 @@
         <v>3</v>
       </c>
       <c r="H2167" s="12" t="s">
-        <v>3249</v>
+        <v>3248</v>
       </c>
       <c r="I2167" s="12" t="s">
         <v>2564</v>
@@ -68517,7 +68518,7 @@
     </row>
     <row r="2168" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2168" s="9" t="s">
-        <v>3196</v>
+        <v>3195</v>
       </c>
       <c r="B2168" s="5" t="s">
         <v>2769</v>
@@ -68534,15 +68535,15 @@
         <v>3</v>
       </c>
       <c r="H2168" s="12" t="s">
-        <v>3249</v>
+        <v>3248</v>
       </c>
       <c r="I2168" s="12" t="s">
-        <v>3130</v>
+        <v>3129</v>
       </c>
     </row>
     <row r="2169" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2169" s="9" t="s">
-        <v>3196</v>
+        <v>3195</v>
       </c>
       <c r="B2169" s="5" t="s">
         <v>2769</v>
@@ -68553,21 +68554,21 @@
       </c>
       <c r="E2169" s="11"/>
       <c r="F2169" s="7" t="s">
-        <v>3211</v>
+        <v>3210</v>
       </c>
       <c r="G2169" s="7">
         <v>3</v>
       </c>
       <c r="H2169" s="12" t="s">
-        <v>3249</v>
+        <v>3248</v>
       </c>
       <c r="I2169" s="12" t="s">
-        <v>3233</v>
+        <v>3232</v>
       </c>
     </row>
     <row r="2170" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2170" s="9" t="s">
-        <v>3197</v>
+        <v>3196</v>
       </c>
       <c r="B2170" s="5" t="s">
         <v>2769</v>
@@ -68584,15 +68585,15 @@
         <v>2</v>
       </c>
       <c r="H2170" s="12" t="s">
-        <v>3250</v>
+        <v>3249</v>
       </c>
       <c r="I2170" s="12" t="s">
-        <v>3236</v>
+        <v>3235</v>
       </c>
     </row>
     <row r="2171" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2171" s="9" t="s">
-        <v>3197</v>
+        <v>3196</v>
       </c>
       <c r="B2171" s="5" t="s">
         <v>2769</v>
@@ -68603,21 +68604,21 @@
       </c>
       <c r="E2171" s="11"/>
       <c r="F2171" s="7" t="s">
-        <v>3212</v>
+        <v>3211</v>
       </c>
       <c r="G2171" s="7">
         <v>3</v>
       </c>
       <c r="H2171" s="12" t="s">
-        <v>3250</v>
+        <v>3249</v>
       </c>
       <c r="I2171" s="12" t="s">
-        <v>3234</v>
+        <v>3233</v>
       </c>
     </row>
     <row r="2172" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2172" s="9" t="s">
-        <v>3197</v>
+        <v>3196</v>
       </c>
       <c r="B2172" s="5" t="s">
         <v>2769</v>
@@ -68628,21 +68629,21 @@
       </c>
       <c r="E2172" s="11"/>
       <c r="F2172" s="7" t="s">
-        <v>3213</v>
+        <v>3212</v>
       </c>
       <c r="G2172" s="7">
         <v>3</v>
       </c>
       <c r="H2172" s="12" t="s">
-        <v>3250</v>
+        <v>3249</v>
       </c>
       <c r="I2172" s="12" t="s">
-        <v>3235</v>
+        <v>3234</v>
       </c>
     </row>
     <row r="2173" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2173" s="9" t="s">
-        <v>3198</v>
+        <v>3197</v>
       </c>
       <c r="B2173" s="5" t="s">
         <v>2769</v>
@@ -68659,7 +68660,7 @@
         <v>3</v>
       </c>
       <c r="H2173" s="12" t="s">
-        <v>3251</v>
+        <v>3250</v>
       </c>
       <c r="I2173" s="12" t="s">
         <v>2544</v>
@@ -68667,7 +68668,7 @@
     </row>
     <row r="2174" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2174" s="9" t="s">
-        <v>3198</v>
+        <v>3197</v>
       </c>
       <c r="B2174" s="5" t="s">
         <v>2769</v>
@@ -68684,7 +68685,7 @@
         <v>3</v>
       </c>
       <c r="H2174" s="12" t="s">
-        <v>3251</v>
+        <v>3250</v>
       </c>
       <c r="I2174" s="12" t="s">
         <v>2544</v>
@@ -68692,7 +68693,7 @@
     </row>
     <row r="2175" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2175" s="9" t="s">
-        <v>3198</v>
+        <v>3197</v>
       </c>
       <c r="B2175" s="5" t="s">
         <v>2769</v>
@@ -68709,7 +68710,7 @@
         <v>3</v>
       </c>
       <c r="H2175" s="12" t="s">
-        <v>3251</v>
+        <v>3250</v>
       </c>
       <c r="I2175" s="12" t="s">
         <v>2544</v>
@@ -68717,7 +68718,7 @@
     </row>
     <row r="2176" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2176" s="9" t="s">
-        <v>3199</v>
+        <v>3198</v>
       </c>
       <c r="B2176" s="5" t="s">
         <v>2769</v>
@@ -68734,7 +68735,7 @@
         <v>3</v>
       </c>
       <c r="H2176" s="12" t="s">
-        <v>3252</v>
+        <v>3251</v>
       </c>
       <c r="I2176" s="12" t="s">
         <v>1705</v>
@@ -68742,7 +68743,7 @@
     </row>
     <row r="2177" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2177" s="9" t="s">
-        <v>3199</v>
+        <v>3198</v>
       </c>
       <c r="B2177" s="5" t="s">
         <v>2769</v>
@@ -68759,7 +68760,7 @@
         <v>3</v>
       </c>
       <c r="H2177" s="12" t="s">
-        <v>3252</v>
+        <v>3251</v>
       </c>
       <c r="I2177" s="12" t="s">
         <v>1719</v>
@@ -68767,7 +68768,7 @@
     </row>
     <row r="2178" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2178" s="9" t="s">
-        <v>3199</v>
+        <v>3198</v>
       </c>
       <c r="B2178" s="5" t="s">
         <v>2769</v>
@@ -68784,7 +68785,7 @@
         <v>3</v>
       </c>
       <c r="H2178" s="12" t="s">
-        <v>3252</v>
+        <v>3251</v>
       </c>
       <c r="I2178" s="12" t="s">
         <v>1713</v>
@@ -68792,7 +68793,7 @@
     </row>
     <row r="2179" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2179" s="9" t="s">
-        <v>3199</v>
+        <v>3198</v>
       </c>
       <c r="B2179" s="5" t="s">
         <v>2769</v>
@@ -68809,7 +68810,7 @@
         <v>3</v>
       </c>
       <c r="H2179" s="12" t="s">
-        <v>3252</v>
+        <v>3251</v>
       </c>
       <c r="I2179" s="12" t="s">
         <v>2878</v>
@@ -68817,7 +68818,7 @@
     </row>
     <row r="2180" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2180" s="9" t="s">
-        <v>3200</v>
+        <v>3199</v>
       </c>
       <c r="B2180" s="5" t="s">
         <v>2769</v>
@@ -68834,7 +68835,7 @@
         <v>3</v>
       </c>
       <c r="H2180" s="12" t="s">
-        <v>3252</v>
+        <v>3251</v>
       </c>
       <c r="I2180" s="12" t="s">
         <v>2880</v>
@@ -68842,7 +68843,7 @@
     </row>
     <row r="2181" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2181" s="9" t="s">
-        <v>3200</v>
+        <v>3199</v>
       </c>
       <c r="B2181" s="5" t="s">
         <v>2769</v>
@@ -68859,7 +68860,7 @@
         <v>3</v>
       </c>
       <c r="H2181" s="12" t="s">
-        <v>3252</v>
+        <v>3251</v>
       </c>
       <c r="I2181" s="12" t="s">
         <v>1729</v>
@@ -68867,7 +68868,7 @@
     </row>
     <row r="2182" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2182" s="9" t="s">
-        <v>3200</v>
+        <v>3199</v>
       </c>
       <c r="B2182" s="5" t="s">
         <v>2769</v>
@@ -68884,7 +68885,7 @@
         <v>3</v>
       </c>
       <c r="H2182" s="12" t="s">
-        <v>3252</v>
+        <v>3251</v>
       </c>
       <c r="I2182" s="12" t="s">
         <v>1709</v>
@@ -68892,7 +68893,7 @@
     </row>
     <row r="2183" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2183" s="9" t="s">
-        <v>3200</v>
+        <v>3199</v>
       </c>
       <c r="B2183" s="5" t="s">
         <v>2769</v>
@@ -68909,7 +68910,7 @@
         <v>3</v>
       </c>
       <c r="H2183" s="12" t="s">
-        <v>3252</v>
+        <v>3251</v>
       </c>
       <c r="I2183" s="12" t="s">
         <v>2889</v>
@@ -68917,7 +68918,7 @@
     </row>
     <row r="2184" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2184" s="9" t="s">
-        <v>3201</v>
+        <v>3200</v>
       </c>
       <c r="B2184" s="5" t="s">
         <v>2769</v>
@@ -68934,7 +68935,7 @@
         <v>3</v>
       </c>
       <c r="H2184" s="12" t="s">
-        <v>3247</v>
+        <v>3246</v>
       </c>
       <c r="I2184" s="12" t="s">
         <v>2239</v>
@@ -68942,7 +68943,7 @@
     </row>
     <row r="2185" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2185" s="9" t="s">
-        <v>3201</v>
+        <v>3200</v>
       </c>
       <c r="B2185" s="5" t="s">
         <v>2769</v>
@@ -68959,7 +68960,7 @@
         <v>3</v>
       </c>
       <c r="H2185" s="12" t="s">
-        <v>3247</v>
+        <v>3246</v>
       </c>
       <c r="I2185" s="12" t="s">
         <v>2248</v>
@@ -68967,7 +68968,7 @@
     </row>
     <row r="2186" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2186" s="9" t="s">
-        <v>3201</v>
+        <v>3200</v>
       </c>
       <c r="B2186" s="5" t="s">
         <v>2769</v>
@@ -68978,21 +68979,21 @@
       </c>
       <c r="E2186" s="11"/>
       <c r="F2186" s="7" t="s">
-        <v>3214</v>
+        <v>3213</v>
       </c>
       <c r="G2186" s="7">
         <v>3</v>
       </c>
       <c r="H2186" s="12" t="s">
-        <v>3247</v>
+        <v>3246</v>
       </c>
       <c r="I2186" s="12" t="s">
-        <v>3237</v>
+        <v>3236</v>
       </c>
     </row>
     <row r="2187" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2187" s="9" t="s">
-        <v>3209</v>
+        <v>3208</v>
       </c>
       <c r="B2187" s="5" t="s">
         <v>2769</v>
@@ -69009,7 +69010,7 @@
         <v>3</v>
       </c>
       <c r="H2187" s="12" t="s">
-        <v>3255</v>
+        <v>3254</v>
       </c>
       <c r="I2187" s="12" t="s">
         <v>2621</v>
@@ -69017,7 +69018,7 @@
     </row>
     <row r="2188" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2188" s="9" t="s">
-        <v>3209</v>
+        <v>3208</v>
       </c>
       <c r="B2188" s="5" t="s">
         <v>2769</v>
@@ -69034,7 +69035,7 @@
         <v>3</v>
       </c>
       <c r="H2188" s="12" t="s">
-        <v>3255</v>
+        <v>3254</v>
       </c>
       <c r="I2188" s="12" t="s">
         <v>2626</v>
@@ -69042,7 +69043,7 @@
     </row>
     <row r="2189" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2189" s="9" t="s">
-        <v>3209</v>
+        <v>3208</v>
       </c>
       <c r="B2189" s="5" t="s">
         <v>2769</v>
@@ -69059,7 +69060,7 @@
         <v>3</v>
       </c>
       <c r="H2189" s="12" t="s">
-        <v>3255</v>
+        <v>3254</v>
       </c>
       <c r="I2189" s="12" t="s">
         <v>2629</v>
@@ -69067,7 +69068,7 @@
     </row>
     <row r="2190" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2190" s="9" t="s">
-        <v>3202</v>
+        <v>3201</v>
       </c>
       <c r="B2190" s="5" t="s">
         <v>2769</v>
@@ -69084,7 +69085,7 @@
         <v>3</v>
       </c>
       <c r="H2190" s="12" t="s">
-        <v>3246</v>
+        <v>3245</v>
       </c>
       <c r="I2190" s="12" t="s">
         <v>1545</v>
@@ -69092,7 +69093,7 @@
     </row>
     <row r="2191" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2191" s="9" t="s">
-        <v>3202</v>
+        <v>3201</v>
       </c>
       <c r="B2191" s="5" t="s">
         <v>2769</v>
@@ -69109,7 +69110,7 @@
         <v>3</v>
       </c>
       <c r="H2191" s="12" t="s">
-        <v>3246</v>
+        <v>3245</v>
       </c>
       <c r="I2191" s="12" t="s">
         <v>2213</v>
@@ -69117,7 +69118,7 @@
     </row>
     <row r="2192" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2192" s="9" t="s">
-        <v>3202</v>
+        <v>3201</v>
       </c>
       <c r="B2192" s="5" t="s">
         <v>2769</v>
@@ -69134,7 +69135,7 @@
         <v>3</v>
       </c>
       <c r="H2192" s="12" t="s">
-        <v>3246</v>
+        <v>3245</v>
       </c>
       <c r="I2192" s="12" t="s">
         <v>2226</v>
@@ -69142,7 +69143,7 @@
     </row>
     <row r="2193" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2193" s="9" t="s">
-        <v>3203</v>
+        <v>3202</v>
       </c>
       <c r="B2193" s="5" t="s">
         <v>2769</v>
@@ -69167,7 +69168,7 @@
     </row>
     <row r="2194" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2194" s="9" t="s">
-        <v>3203</v>
+        <v>3202</v>
       </c>
       <c r="B2194" s="5" t="s">
         <v>2769</v>
@@ -69192,7 +69193,7 @@
     </row>
     <row r="2195" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2195" s="9" t="s">
-        <v>3203</v>
+        <v>3202</v>
       </c>
       <c r="B2195" s="5" t="s">
         <v>2769</v>
@@ -69217,7 +69218,7 @@
     </row>
     <row r="2196" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2196" s="9" t="s">
-        <v>3203</v>
+        <v>3202</v>
       </c>
       <c r="B2196" s="5" t="s">
         <v>2769</v>
@@ -69242,7 +69243,7 @@
     </row>
     <row r="2197" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2197" s="9" t="s">
-        <v>3204</v>
+        <v>3203</v>
       </c>
       <c r="B2197" s="5" t="s">
         <v>2769</v>
@@ -69259,7 +69260,7 @@
         <v>3</v>
       </c>
       <c r="H2197" s="12" t="s">
-        <v>3254</v>
+        <v>3253</v>
       </c>
       <c r="I2197" s="12" t="s">
         <v>2569</v>
@@ -69267,7 +69268,7 @@
     </row>
     <row r="2198" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2198" s="9" t="s">
-        <v>3204</v>
+        <v>3203</v>
       </c>
       <c r="B2198" s="5" t="s">
         <v>2769</v>
@@ -69284,7 +69285,7 @@
         <v>3</v>
       </c>
       <c r="H2198" s="12" t="s">
-        <v>3254</v>
+        <v>3253</v>
       </c>
       <c r="I2198" s="12" t="s">
         <v>2570</v>
@@ -69292,7 +69293,7 @@
     </row>
     <row r="2199" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2199" s="9" t="s">
-        <v>3204</v>
+        <v>3203</v>
       </c>
       <c r="B2199" s="5" t="s">
         <v>2769</v>
@@ -69309,7 +69310,7 @@
         <v>3</v>
       </c>
       <c r="H2199" s="12" t="s">
-        <v>3254</v>
+        <v>3253</v>
       </c>
       <c r="I2199" s="12" t="s">
         <v>2572</v>
@@ -69317,7 +69318,7 @@
     </row>
     <row r="2200" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2200" s="9" t="s">
-        <v>3204</v>
+        <v>3203</v>
       </c>
       <c r="B2200" s="5" t="s">
         <v>2769</v>
@@ -69334,7 +69335,7 @@
         <v>3</v>
       </c>
       <c r="H2200" s="12" t="s">
-        <v>3254</v>
+        <v>3253</v>
       </c>
       <c r="I2200" s="12" t="s">
         <v>2576</v>
@@ -69342,7 +69343,7 @@
     </row>
     <row r="2201" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2201" s="9" t="s">
-        <v>3205</v>
+        <v>3204</v>
       </c>
       <c r="B2201" s="5" t="s">
         <v>2769</v>
@@ -69359,7 +69360,7 @@
         <v>3</v>
       </c>
       <c r="H2201" s="12" t="s">
-        <v>3238</v>
+        <v>3237</v>
       </c>
       <c r="I2201" s="12" t="s">
         <v>1832</v>
@@ -69367,7 +69368,7 @@
     </row>
     <row r="2202" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2202" s="9" t="s">
-        <v>3205</v>
+        <v>3204</v>
       </c>
       <c r="B2202" s="5" t="s">
         <v>2769</v>
@@ -69384,7 +69385,7 @@
         <v>3</v>
       </c>
       <c r="H2202" s="12" t="s">
-        <v>3238</v>
+        <v>3237</v>
       </c>
       <c r="I2202" s="12" t="s">
         <v>1830</v>
@@ -69392,7 +69393,7 @@
     </row>
     <row r="2203" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2203" s="9" t="s">
-        <v>3205</v>
+        <v>3204</v>
       </c>
       <c r="B2203" s="5" t="s">
         <v>2769</v>
@@ -69409,7 +69410,7 @@
         <v>3</v>
       </c>
       <c r="H2203" s="12" t="s">
-        <v>3238</v>
+        <v>3237</v>
       </c>
       <c r="I2203" s="12" t="s">
         <v>1847</v>
@@ -69417,7 +69418,7 @@
     </row>
     <row r="2204" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2204" s="9" t="s">
-        <v>3205</v>
+        <v>3204</v>
       </c>
       <c r="B2204" s="5" t="s">
         <v>2769</v>
@@ -69434,7 +69435,7 @@
         <v>3</v>
       </c>
       <c r="H2204" s="12" t="s">
-        <v>3238</v>
+        <v>3237</v>
       </c>
       <c r="I2204" s="12" t="s">
         <v>1855</v>
@@ -69442,7 +69443,7 @@
     </row>
     <row r="2205" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2205" s="9" t="s">
-        <v>3206</v>
+        <v>3205</v>
       </c>
       <c r="B2205" s="5" t="s">
         <v>2769</v>
@@ -69453,21 +69454,21 @@
       </c>
       <c r="E2205" s="11"/>
       <c r="F2205" s="7" t="s">
-        <v>3215</v>
+        <v>3214</v>
       </c>
       <c r="G2205" s="7">
         <v>3</v>
       </c>
       <c r="H2205" s="12" t="s">
-        <v>3253</v>
+        <v>3252</v>
       </c>
       <c r="I2205" s="12" t="s">
-        <v>3239</v>
+        <v>3238</v>
       </c>
     </row>
     <row r="2206" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2206" s="9" t="s">
-        <v>3206</v>
+        <v>3205</v>
       </c>
       <c r="B2206" s="5" t="s">
         <v>2769</v>
@@ -69478,21 +69479,21 @@
       </c>
       <c r="E2206" s="11"/>
       <c r="F2206" s="7" t="s">
-        <v>3216</v>
+        <v>3215</v>
       </c>
       <c r="G2206" s="7">
         <v>3</v>
       </c>
       <c r="H2206" s="12" t="s">
-        <v>3253</v>
+        <v>3252</v>
       </c>
       <c r="I2206" s="12" t="s">
-        <v>3240</v>
+        <v>3239</v>
       </c>
     </row>
     <row r="2207" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2207" s="9" t="s">
-        <v>3206</v>
+        <v>3205</v>
       </c>
       <c r="B2207" s="5" t="s">
         <v>2769</v>
@@ -69503,21 +69504,21 @@
       </c>
       <c r="E2207" s="11"/>
       <c r="F2207" s="7" t="s">
-        <v>3217</v>
+        <v>3216</v>
       </c>
       <c r="G2207" s="7">
         <v>3</v>
       </c>
       <c r="H2207" s="12" t="s">
-        <v>3253</v>
+        <v>3252</v>
       </c>
       <c r="I2207" s="12" t="s">
-        <v>3241</v>
+        <v>3240</v>
       </c>
     </row>
     <row r="2208" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2208" s="9" t="s">
-        <v>3206</v>
+        <v>3205</v>
       </c>
       <c r="B2208" s="5" t="s">
         <v>2769</v>
@@ -69528,21 +69529,21 @@
       </c>
       <c r="E2208" s="11"/>
       <c r="F2208" s="7" t="s">
-        <v>3218</v>
+        <v>3217</v>
       </c>
       <c r="G2208" s="7">
         <v>3</v>
       </c>
       <c r="H2208" s="12" t="s">
-        <v>3253</v>
+        <v>3252</v>
       </c>
       <c r="I2208" s="12" t="s">
-        <v>3242</v>
+        <v>3241</v>
       </c>
     </row>
     <row r="2209" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2209" s="9" t="s">
-        <v>3207</v>
+        <v>3206</v>
       </c>
       <c r="B2209" s="5" t="s">
         <v>2769</v>
@@ -69559,7 +69560,7 @@
         <v>3</v>
       </c>
       <c r="H2209" s="12" t="s">
-        <v>3243</v>
+        <v>3242</v>
       </c>
       <c r="I2209" s="12" t="s">
         <v>2269</v>
@@ -69567,7 +69568,7 @@
     </row>
     <row r="2210" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2210" s="9" t="s">
-        <v>3207</v>
+        <v>3206</v>
       </c>
       <c r="B2210" s="5" t="s">
         <v>2769</v>
@@ -69578,21 +69579,21 @@
       </c>
       <c r="E2210" s="11"/>
       <c r="F2210" s="7" t="s">
-        <v>3219</v>
+        <v>3218</v>
       </c>
       <c r="G2210" s="7">
         <v>3</v>
       </c>
       <c r="H2210" s="12" t="s">
+        <v>3242</v>
+      </c>
+      <c r="I2210" s="12" t="s">
         <v>3243</v>
-      </c>
-      <c r="I2210" s="12" t="s">
-        <v>3244</v>
       </c>
     </row>
     <row r="2211" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2211" s="9" t="s">
-        <v>3207</v>
+        <v>3206</v>
       </c>
       <c r="B2211" s="5" t="s">
         <v>2769</v>
@@ -69603,21 +69604,21 @@
       </c>
       <c r="E2211" s="11"/>
       <c r="F2211" s="7" t="s">
+        <v>2996</v>
+      </c>
+      <c r="G2211" s="7">
+        <v>3</v>
+      </c>
+      <c r="H2211" s="12" t="s">
+        <v>3242</v>
+      </c>
+      <c r="I2211" s="12" t="s">
         <v>2997</v>
-      </c>
-      <c r="G2211" s="7">
-        <v>3</v>
-      </c>
-      <c r="H2211" s="12" t="s">
-        <v>3243</v>
-      </c>
-      <c r="I2211" s="12" t="s">
-        <v>2998</v>
       </c>
     </row>
     <row r="2212" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2212" s="9" t="s">
-        <v>3208</v>
+        <v>3207</v>
       </c>
       <c r="B2212" s="5" t="s">
         <v>2769</v>
@@ -69634,7 +69635,7 @@
         <v>3</v>
       </c>
       <c r="H2212" s="12" t="s">
-        <v>3245</v>
+        <v>3244</v>
       </c>
       <c r="I2212" s="12" t="s">
         <v>2072</v>
@@ -69642,7 +69643,7 @@
     </row>
     <row r="2213" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2213" s="9" t="s">
-        <v>3208</v>
+        <v>3207</v>
       </c>
       <c r="B2213" s="5" t="s">
         <v>2769</v>
@@ -69659,7 +69660,7 @@
         <v>3</v>
       </c>
       <c r="H2213" s="12" t="s">
-        <v>3245</v>
+        <v>3244</v>
       </c>
       <c r="I2213" s="12" t="s">
         <v>2106</v>
@@ -69667,7 +69668,7 @@
     </row>
     <row r="2214" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2214" s="9" t="s">
-        <v>3208</v>
+        <v>3207</v>
       </c>
       <c r="B2214" s="5" t="s">
         <v>2769</v>
@@ -69684,7 +69685,7 @@
         <v>3</v>
       </c>
       <c r="H2214" s="12" t="s">
-        <v>3245</v>
+        <v>3244</v>
       </c>
       <c r="I2214" s="12" t="s">
         <v>2102</v>
@@ -69692,7 +69693,7 @@
     </row>
     <row r="2215" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2215" s="9" t="s">
-        <v>3208</v>
+        <v>3207</v>
       </c>
       <c r="B2215" s="5" t="s">
         <v>2769</v>
@@ -69709,7 +69710,7 @@
         <v>3</v>
       </c>
       <c r="H2215" s="12" t="s">
-        <v>3245</v>
+        <v>3244</v>
       </c>
       <c r="I2215" s="12" t="s">
         <v>2111</v>
